--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08C417B9-89D8-4756-9559-D237BCF6F12E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{07BD3B65-21B0-432D-AD63-D31A83DFED33}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="110">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -127,30 +127,30 @@
     <t>Deposito NQN</t>
   </si>
   <si>
+    <t>391-2884-021P</t>
+  </si>
+  <si>
+    <t>SELLO GOMA SQUARE GASKET 50-25</t>
+  </si>
+  <si>
+    <t>SOL - 2384</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>C5OX-24-20F</t>
+  </si>
+  <si>
+    <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
+  </si>
+  <si>
     <t>391-2882-051</t>
   </si>
   <si>
     <t>CUERDA P30 Y P50</t>
   </si>
   <si>
-    <t>SOL - 2384</t>
-  </si>
-  <si>
-    <t>2026-07</t>
-  </si>
-  <si>
-    <t>391-2884-021P</t>
-  </si>
-  <si>
-    <t>SELLO GOMA SQUARE GASKET 50-25</t>
-  </si>
-  <si>
-    <t>C5OX-24-20F</t>
-  </si>
-  <si>
-    <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
-  </si>
-  <si>
     <t>RACORDS Y CAMISAS</t>
   </si>
   <si>
@@ -181,10 +181,10 @@
     <t>SOL - 2489</t>
   </si>
   <si>
-    <t>46511385</t>
-  </si>
-  <si>
-    <t>MANGUERA GATES SAE100 R12 3/4"  12EFG4K X LL</t>
+    <t>FILT-D-AB-2</t>
+  </si>
+  <si>
+    <t>FILTRO AIRE RESP DESECANTE</t>
   </si>
   <si>
     <t>SOL - 2493</t>
@@ -214,18 +214,18 @@
     <t>TORRINGTON P50</t>
   </si>
   <si>
-    <t>2500-3500-375B</t>
-  </si>
-  <si>
-    <t>POLYPAK 88.90 x 101.60 x 9.52</t>
-  </si>
-  <si>
     <t>FT 221/1-14</t>
   </si>
   <si>
     <t>VALVULA ESFERICA DE 2 VIAS, ALTA PRESION 1/4"</t>
   </si>
   <si>
+    <t>MA-310</t>
+  </si>
+  <si>
+    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
+  </si>
+  <si>
     <t>AC02G-90</t>
   </si>
   <si>
@@ -238,126 +238,6 @@
     <t>ALEMITE RECTO DE 1/8" GAS</t>
   </si>
   <si>
-    <t>MA-310</t>
-  </si>
-  <si>
-    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
-  </si>
-  <si>
-    <t>PFQ723ZRR1R11</t>
-  </si>
-  <si>
-    <t>MANOMETRO SERIE PFQ-ZR 4", 0/15.000 PSI - 0/1.000 bar, 1/2" NPT INFERIOR</t>
-  </si>
-  <si>
-    <t>PFQ905R3R1</t>
-  </si>
-  <si>
-    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-10 BAR C/GLICERINA</t>
-  </si>
-  <si>
-    <t>PFQ908R3R1</t>
-  </si>
-  <si>
-    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-40 BAR C/GLICERINA</t>
-  </si>
-  <si>
-    <t>PFQ918R3R1</t>
-  </si>
-  <si>
-    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-600 BAR C/GLICERINA</t>
-  </si>
-  <si>
-    <t>FILT-D-AB-2</t>
-  </si>
-  <si>
-    <t>FILTRO AIRE RESP DESECANTE</t>
-  </si>
-  <si>
-    <t>TAPA-3/4" S3000</t>
-  </si>
-  <si>
-    <t>TAPA HEMBRA 3/4" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>TAPON-1" S3000</t>
-  </si>
-  <si>
-    <t>TAPON MACHO 1" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>TAPON-1/4" S3000</t>
-  </si>
-  <si>
-    <t>TAPON MACHO 1/4" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>TAPON-3/4" S3000</t>
-  </si>
-  <si>
-    <t>TAPON MACHO 3/4" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>TAPON-3/8" S3000</t>
-  </si>
-  <si>
-    <t>TAPON MACHO 3/8" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>TEE-1/2" S3000</t>
-  </si>
-  <si>
-    <t>TEE H x H x H 1/2" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>BUJE RED-2"x1.1/2" S3000</t>
-  </si>
-  <si>
-    <t>BUJE DE RED 2" NPT x 1.1/2" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>CUPLA-1/2" S3000</t>
-  </si>
-  <si>
-    <t>CUPLA 1/2" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>CUPLA-1/4" S3000</t>
-  </si>
-  <si>
-    <t>CUPLA 1/4" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>ENTRER-1" S3000</t>
-  </si>
-  <si>
-    <t>ENTRERROSCA 1" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>ENTRER-1.1/4" S3000</t>
-  </si>
-  <si>
-    <t>ENTRERROSCA 1.1/4" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>ENTRER-1/2" S3000</t>
-  </si>
-  <si>
-    <t>ENTRERROSCA 1/2" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>ENTRER-1/4" S3000</t>
-  </si>
-  <si>
-    <t>ENTRERROSCA 1/4" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>ENTRER-3/4" S3000</t>
-  </si>
-  <si>
-    <t>ENTRERROSCA 3/4" NPT SERIE 3000</t>
-  </si>
-  <si>
     <t>AFS-102N</t>
   </si>
   <si>
@@ -424,16 +304,52 @@
     <t>ADAP CODO 90° FORJADO HG JIC 9/16" UNF x MF 1/4" NPT</t>
   </si>
   <si>
-    <t>VALVULA NEUMATICA</t>
-  </si>
-  <si>
-    <t>VALVULA NEUMATICA - GENERICO</t>
-  </si>
-  <si>
-    <t>SOL - 2506</t>
-  </si>
-  <si>
-    <t>01046</t>
+    <t>BH VALVULA C5</t>
+  </si>
+  <si>
+    <t>VALVULA DIRECCIONAL DE CONTROL CAMBIO AUTOMATICA CETOP 5</t>
+  </si>
+  <si>
+    <t>SOL - 2527</t>
+  </si>
+  <si>
+    <t>01006</t>
+  </si>
+  <si>
+    <t>HIDROIL SRL</t>
+  </si>
+  <si>
+    <t>Deposito</t>
+  </si>
+  <si>
+    <t>FILTRO HIDRAULICO</t>
+  </si>
+  <si>
+    <t>FILTRO HIDRAULICO - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2528</t>
+  </si>
+  <si>
+    <t>01007</t>
+  </si>
+  <si>
+    <t>FT 221/1-100</t>
+  </si>
+  <si>
+    <t>VALVULA ESFERICA DE 2 VIAS, ALTA PRESION 1"</t>
+  </si>
+  <si>
+    <t>SOL - 2529</t>
+  </si>
+  <si>
+    <t>01008</t>
+  </si>
+  <si>
+    <t>FT 221/1-12</t>
+  </si>
+  <si>
+    <t>VALVULA ESFERICA DE 2 VIAS, ALTA PRESION 1/2"</t>
   </si>
 </sst>
 </file>
@@ -785,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R52"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -858,7 +774,7 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
@@ -867,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I2" t="s">
         <v>22</v>
@@ -1026,7 +942,7 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
@@ -1035,7 +951,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
         <v>22</v>
@@ -1194,7 +1110,7 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -1203,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
@@ -1250,7 +1166,7 @@
         <v>21</v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -1259,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
@@ -1306,7 +1222,7 @@
         <v>21</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -1315,7 +1231,7 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I10" t="s">
         <v>22</v>
@@ -1474,7 +1390,7 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>1200</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1483,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>1200</v>
+        <v>6</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
@@ -1810,7 +1726,7 @@
         <v>21</v>
       </c>
       <c r="E19">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F19" t="s">
         <v>21</v>
@@ -1819,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
@@ -1972,13 +1888,13 @@
         <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
         <v>21</v>
       </c>
       <c r="E22">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F22" t="s">
         <v>21</v>
@@ -1987,13 +1903,13 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I22" t="s">
         <v>22</v>
       </c>
       <c r="J22" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="K22" t="s">
         <v>24</v>
@@ -2022,34 +1938,34 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" t="s">
         <v>74</v>
       </c>
-      <c r="B23" t="s">
+      <c r="D23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23">
+        <v>5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>5</v>
+      </c>
+      <c r="I23" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" t="s">
         <v>75</v>
-      </c>
-      <c r="C23" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
-      <c r="F23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>2</v>
-      </c>
-      <c r="I23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J23" t="s">
-        <v>47</v>
       </c>
       <c r="K23" t="s">
         <v>24</v>
@@ -2078,19 +1994,19 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
         <v>21</v>
       </c>
       <c r="E24">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F24" t="s">
         <v>21</v>
@@ -2099,13 +2015,13 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
       </c>
       <c r="J24" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="K24" t="s">
         <v>24</v>
@@ -2134,19 +2050,19 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D25" t="s">
         <v>21</v>
       </c>
       <c r="E25">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F25" t="s">
         <v>21</v>
@@ -2155,13 +2071,13 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I25" t="s">
         <v>22</v>
       </c>
       <c r="J25" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="K25" t="s">
         <v>24</v>
@@ -2190,13 +2106,13 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s">
         <v>21</v>
@@ -2217,7 +2133,7 @@
         <v>22</v>
       </c>
       <c r="J26" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="K26" t="s">
         <v>24</v>
@@ -2246,19 +2162,19 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D27" t="s">
         <v>21</v>
       </c>
       <c r="E27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
         <v>21</v>
@@ -2267,13 +2183,13 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I27" t="s">
         <v>22</v>
       </c>
       <c r="J27" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="K27" t="s">
         <v>24</v>
@@ -2302,19 +2218,19 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
         <v>21</v>
       </c>
       <c r="E28">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
         <v>21</v>
@@ -2323,13 +2239,13 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I28" t="s">
         <v>22</v>
       </c>
       <c r="J28" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="K28" t="s">
         <v>24</v>
@@ -2358,19 +2274,19 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D29" t="s">
         <v>21</v>
       </c>
       <c r="E29">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F29" t="s">
         <v>21</v>
@@ -2379,13 +2295,13 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I29" t="s">
         <v>22</v>
       </c>
       <c r="J29" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="K29" t="s">
         <v>24</v>
@@ -2414,19 +2330,19 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D30" t="s">
         <v>21</v>
       </c>
       <c r="E30">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
         <v>21</v>
@@ -2435,13 +2351,13 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I30" t="s">
         <v>22</v>
       </c>
       <c r="J30" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="K30" t="s">
         <v>24</v>
@@ -2470,19 +2386,19 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D31" t="s">
         <v>21</v>
       </c>
       <c r="E31">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F31" t="s">
         <v>21</v>
@@ -2491,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="I31" t="s">
         <v>22</v>
       </c>
       <c r="J31" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="K31" t="s">
         <v>24</v>
@@ -2526,19 +2442,19 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="E32">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F32" t="s">
         <v>21</v>
@@ -2547,22 +2463,22 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I32" t="s">
         <v>22</v>
       </c>
       <c r="J32" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="K32" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L32" t="s">
         <v>25</v>
       </c>
       <c r="M32" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="N32" t="s">
         <v>21</v>
@@ -2582,19 +2498,19 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="E33">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F33" t="s">
         <v>21</v>
@@ -2603,22 +2519,22 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I33" t="s">
         <v>22</v>
       </c>
       <c r="J33" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="K33" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L33" t="s">
         <v>25</v>
       </c>
       <c r="M33" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="N33" t="s">
         <v>21</v>
@@ -2638,19 +2554,19 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="D34" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E34">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F34" t="s">
         <v>21</v>
@@ -2659,22 +2575,22 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I34" t="s">
         <v>22</v>
       </c>
       <c r="J34" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="K34" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L34" t="s">
         <v>25</v>
       </c>
       <c r="M34" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="N34" t="s">
         <v>21</v>
@@ -2694,43 +2610,43 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35">
+        <v>6</v>
+      </c>
+      <c r="F35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>6</v>
+      </c>
+      <c r="I35" t="s">
+        <v>22</v>
+      </c>
+      <c r="J35" t="s">
+        <v>75</v>
+      </c>
+      <c r="K35" t="s">
         <v>98</v>
       </c>
-      <c r="B35" t="s">
+      <c r="L35" t="s">
+        <v>25</v>
+      </c>
+      <c r="M35" t="s">
         <v>99</v>
-      </c>
-      <c r="C35" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35">
-        <v>150</v>
-      </c>
-      <c r="F35" t="s">
-        <v>21</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>150</v>
-      </c>
-      <c r="I35" t="s">
-        <v>22</v>
-      </c>
-      <c r="J35" t="s">
-        <v>47</v>
-      </c>
-      <c r="K35" t="s">
-        <v>24</v>
-      </c>
-      <c r="L35" t="s">
-        <v>25</v>
-      </c>
-      <c r="M35" t="s">
-        <v>26</v>
       </c>
       <c r="N35" t="s">
         <v>21</v>
@@ -2750,19 +2666,19 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="B36" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="C36" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="D36" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E36">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="F36" t="s">
         <v>21</v>
@@ -2771,22 +2687,22 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="I36" t="s">
         <v>22</v>
       </c>
       <c r="J36" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="K36" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L36" t="s">
         <v>25</v>
       </c>
       <c r="M36" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="N36" t="s">
         <v>21</v>
@@ -2801,902 +2717,6 @@
         <v>21</v>
       </c>
       <c r="R36" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>102</v>
-      </c>
-      <c r="B37" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" t="s">
-        <v>55</v>
-      </c>
-      <c r="D37" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37">
-        <v>100</v>
-      </c>
-      <c r="F37" t="s">
-        <v>21</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>100</v>
-      </c>
-      <c r="I37" t="s">
-        <v>22</v>
-      </c>
-      <c r="J37" t="s">
-        <v>47</v>
-      </c>
-      <c r="K37" t="s">
-        <v>24</v>
-      </c>
-      <c r="L37" t="s">
-        <v>25</v>
-      </c>
-      <c r="M37" t="s">
-        <v>26</v>
-      </c>
-      <c r="N37" t="s">
-        <v>21</v>
-      </c>
-      <c r="O37" t="s">
-        <v>21</v>
-      </c>
-      <c r="P37" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>21</v>
-      </c>
-      <c r="R37" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>104</v>
-      </c>
-      <c r="B38" t="s">
-        <v>105</v>
-      </c>
-      <c r="C38" t="s">
-        <v>55</v>
-      </c>
-      <c r="D38" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38">
-        <v>20</v>
-      </c>
-      <c r="F38" t="s">
-        <v>21</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <v>20</v>
-      </c>
-      <c r="I38" t="s">
-        <v>22</v>
-      </c>
-      <c r="J38" t="s">
-        <v>47</v>
-      </c>
-      <c r="K38" t="s">
-        <v>24</v>
-      </c>
-      <c r="L38" t="s">
-        <v>25</v>
-      </c>
-      <c r="M38" t="s">
-        <v>26</v>
-      </c>
-      <c r="N38" t="s">
-        <v>21</v>
-      </c>
-      <c r="O38" t="s">
-        <v>21</v>
-      </c>
-      <c r="P38" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>21</v>
-      </c>
-      <c r="R38" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>106</v>
-      </c>
-      <c r="B39" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39" t="s">
-        <v>55</v>
-      </c>
-      <c r="D39" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39">
-        <v>200</v>
-      </c>
-      <c r="F39" t="s">
-        <v>21</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>200</v>
-      </c>
-      <c r="I39" t="s">
-        <v>22</v>
-      </c>
-      <c r="J39" t="s">
-        <v>47</v>
-      </c>
-      <c r="K39" t="s">
-        <v>24</v>
-      </c>
-      <c r="L39" t="s">
-        <v>25</v>
-      </c>
-      <c r="M39" t="s">
-        <v>26</v>
-      </c>
-      <c r="N39" t="s">
-        <v>21</v>
-      </c>
-      <c r="O39" t="s">
-        <v>21</v>
-      </c>
-      <c r="P39" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>21</v>
-      </c>
-      <c r="R39" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>108</v>
-      </c>
-      <c r="B40" t="s">
-        <v>109</v>
-      </c>
-      <c r="C40" t="s">
-        <v>55</v>
-      </c>
-      <c r="D40" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40">
-        <v>150</v>
-      </c>
-      <c r="F40" t="s">
-        <v>21</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>150</v>
-      </c>
-      <c r="I40" t="s">
-        <v>22</v>
-      </c>
-      <c r="J40" t="s">
-        <v>47</v>
-      </c>
-      <c r="K40" t="s">
-        <v>24</v>
-      </c>
-      <c r="L40" t="s">
-        <v>25</v>
-      </c>
-      <c r="M40" t="s">
-        <v>26</v>
-      </c>
-      <c r="N40" t="s">
-        <v>21</v>
-      </c>
-      <c r="O40" t="s">
-        <v>21</v>
-      </c>
-      <c r="P40" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>21</v>
-      </c>
-      <c r="R40" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>110</v>
-      </c>
-      <c r="B41" t="s">
-        <v>111</v>
-      </c>
-      <c r="C41" t="s">
-        <v>55</v>
-      </c>
-      <c r="D41" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41">
-        <v>50</v>
-      </c>
-      <c r="F41" t="s">
-        <v>21</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>50</v>
-      </c>
-      <c r="I41" t="s">
-        <v>22</v>
-      </c>
-      <c r="J41" t="s">
-        <v>47</v>
-      </c>
-      <c r="K41" t="s">
-        <v>24</v>
-      </c>
-      <c r="L41" t="s">
-        <v>25</v>
-      </c>
-      <c r="M41" t="s">
-        <v>26</v>
-      </c>
-      <c r="N41" t="s">
-        <v>21</v>
-      </c>
-      <c r="O41" t="s">
-        <v>21</v>
-      </c>
-      <c r="P41" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>21</v>
-      </c>
-      <c r="R41" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>112</v>
-      </c>
-      <c r="B42" t="s">
-        <v>113</v>
-      </c>
-      <c r="C42" t="s">
-        <v>114</v>
-      </c>
-      <c r="D42" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42">
-        <v>3</v>
-      </c>
-      <c r="F42" t="s">
-        <v>21</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>3</v>
-      </c>
-      <c r="I42" t="s">
-        <v>22</v>
-      </c>
-      <c r="J42" t="s">
-        <v>115</v>
-      </c>
-      <c r="K42" t="s">
-        <v>24</v>
-      </c>
-      <c r="L42" t="s">
-        <v>25</v>
-      </c>
-      <c r="M42" t="s">
-        <v>26</v>
-      </c>
-      <c r="N42" t="s">
-        <v>21</v>
-      </c>
-      <c r="O42" t="s">
-        <v>21</v>
-      </c>
-      <c r="P42" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>21</v>
-      </c>
-      <c r="R42" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>116</v>
-      </c>
-      <c r="B43" t="s">
-        <v>117</v>
-      </c>
-      <c r="C43" t="s">
-        <v>114</v>
-      </c>
-      <c r="D43" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43">
-        <v>5</v>
-      </c>
-      <c r="F43" t="s">
-        <v>21</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>5</v>
-      </c>
-      <c r="I43" t="s">
-        <v>22</v>
-      </c>
-      <c r="J43" t="s">
-        <v>115</v>
-      </c>
-      <c r="K43" t="s">
-        <v>24</v>
-      </c>
-      <c r="L43" t="s">
-        <v>25</v>
-      </c>
-      <c r="M43" t="s">
-        <v>26</v>
-      </c>
-      <c r="N43" t="s">
-        <v>21</v>
-      </c>
-      <c r="O43" t="s">
-        <v>21</v>
-      </c>
-      <c r="P43" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>21</v>
-      </c>
-      <c r="R43" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>118</v>
-      </c>
-      <c r="B44" t="s">
-        <v>119</v>
-      </c>
-      <c r="C44" t="s">
-        <v>114</v>
-      </c>
-      <c r="D44" t="s">
-        <v>21</v>
-      </c>
-      <c r="E44">
-        <v>5</v>
-      </c>
-      <c r="F44" t="s">
-        <v>21</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>5</v>
-      </c>
-      <c r="I44" t="s">
-        <v>22</v>
-      </c>
-      <c r="J44" t="s">
-        <v>115</v>
-      </c>
-      <c r="K44" t="s">
-        <v>24</v>
-      </c>
-      <c r="L44" t="s">
-        <v>25</v>
-      </c>
-      <c r="M44" t="s">
-        <v>26</v>
-      </c>
-      <c r="N44" t="s">
-        <v>21</v>
-      </c>
-      <c r="O44" t="s">
-        <v>21</v>
-      </c>
-      <c r="P44" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>21</v>
-      </c>
-      <c r="R44" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>120</v>
-      </c>
-      <c r="B45" t="s">
-        <v>121</v>
-      </c>
-      <c r="C45" t="s">
-        <v>114</v>
-      </c>
-      <c r="D45" t="s">
-        <v>21</v>
-      </c>
-      <c r="E45">
-        <v>5</v>
-      </c>
-      <c r="F45" t="s">
-        <v>21</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>5</v>
-      </c>
-      <c r="I45" t="s">
-        <v>22</v>
-      </c>
-      <c r="J45" t="s">
-        <v>115</v>
-      </c>
-      <c r="K45" t="s">
-        <v>24</v>
-      </c>
-      <c r="L45" t="s">
-        <v>25</v>
-      </c>
-      <c r="M45" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" t="s">
-        <v>21</v>
-      </c>
-      <c r="O45" t="s">
-        <v>21</v>
-      </c>
-      <c r="P45" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>21</v>
-      </c>
-      <c r="R45" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>122</v>
-      </c>
-      <c r="B46" t="s">
-        <v>123</v>
-      </c>
-      <c r="C46" t="s">
-        <v>114</v>
-      </c>
-      <c r="D46" t="s">
-        <v>21</v>
-      </c>
-      <c r="E46">
-        <v>10</v>
-      </c>
-      <c r="F46" t="s">
-        <v>21</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>10</v>
-      </c>
-      <c r="I46" t="s">
-        <v>22</v>
-      </c>
-      <c r="J46" t="s">
-        <v>115</v>
-      </c>
-      <c r="K46" t="s">
-        <v>24</v>
-      </c>
-      <c r="L46" t="s">
-        <v>25</v>
-      </c>
-      <c r="M46" t="s">
-        <v>26</v>
-      </c>
-      <c r="N46" t="s">
-        <v>21</v>
-      </c>
-      <c r="O46" t="s">
-        <v>21</v>
-      </c>
-      <c r="P46" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>21</v>
-      </c>
-      <c r="R46" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>124</v>
-      </c>
-      <c r="B47" t="s">
-        <v>125</v>
-      </c>
-      <c r="C47" t="s">
-        <v>114</v>
-      </c>
-      <c r="D47" t="s">
-        <v>21</v>
-      </c>
-      <c r="E47">
-        <v>10</v>
-      </c>
-      <c r="F47" t="s">
-        <v>21</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>10</v>
-      </c>
-      <c r="I47" t="s">
-        <v>22</v>
-      </c>
-      <c r="J47" t="s">
-        <v>115</v>
-      </c>
-      <c r="K47" t="s">
-        <v>24</v>
-      </c>
-      <c r="L47" t="s">
-        <v>25</v>
-      </c>
-      <c r="M47" t="s">
-        <v>26</v>
-      </c>
-      <c r="N47" t="s">
-        <v>21</v>
-      </c>
-      <c r="O47" t="s">
-        <v>21</v>
-      </c>
-      <c r="P47" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>21</v>
-      </c>
-      <c r="R47" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>126</v>
-      </c>
-      <c r="B48" t="s">
-        <v>127</v>
-      </c>
-      <c r="C48" t="s">
-        <v>114</v>
-      </c>
-      <c r="D48" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48">
-        <v>10</v>
-      </c>
-      <c r="F48" t="s">
-        <v>21</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>10</v>
-      </c>
-      <c r="I48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J48" t="s">
-        <v>115</v>
-      </c>
-      <c r="K48" t="s">
-        <v>24</v>
-      </c>
-      <c r="L48" t="s">
-        <v>25</v>
-      </c>
-      <c r="M48" t="s">
-        <v>26</v>
-      </c>
-      <c r="N48" t="s">
-        <v>21</v>
-      </c>
-      <c r="O48" t="s">
-        <v>21</v>
-      </c>
-      <c r="P48" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>21</v>
-      </c>
-      <c r="R48" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>128</v>
-      </c>
-      <c r="B49" t="s">
-        <v>129</v>
-      </c>
-      <c r="C49" t="s">
-        <v>114</v>
-      </c>
-      <c r="D49" t="s">
-        <v>21</v>
-      </c>
-      <c r="E49">
-        <v>10</v>
-      </c>
-      <c r="F49" t="s">
-        <v>21</v>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>10</v>
-      </c>
-      <c r="I49" t="s">
-        <v>22</v>
-      </c>
-      <c r="J49" t="s">
-        <v>115</v>
-      </c>
-      <c r="K49" t="s">
-        <v>24</v>
-      </c>
-      <c r="L49" t="s">
-        <v>25</v>
-      </c>
-      <c r="M49" t="s">
-        <v>26</v>
-      </c>
-      <c r="N49" t="s">
-        <v>21</v>
-      </c>
-      <c r="O49" t="s">
-        <v>21</v>
-      </c>
-      <c r="P49" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>21</v>
-      </c>
-      <c r="R49" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>130</v>
-      </c>
-      <c r="B50" t="s">
-        <v>131</v>
-      </c>
-      <c r="C50" t="s">
-        <v>114</v>
-      </c>
-      <c r="D50" t="s">
-        <v>21</v>
-      </c>
-      <c r="E50">
-        <v>10</v>
-      </c>
-      <c r="F50" t="s">
-        <v>21</v>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>10</v>
-      </c>
-      <c r="I50" t="s">
-        <v>22</v>
-      </c>
-      <c r="J50" t="s">
-        <v>115</v>
-      </c>
-      <c r="K50" t="s">
-        <v>24</v>
-      </c>
-      <c r="L50" t="s">
-        <v>25</v>
-      </c>
-      <c r="M50" t="s">
-        <v>26</v>
-      </c>
-      <c r="N50" t="s">
-        <v>21</v>
-      </c>
-      <c r="O50" t="s">
-        <v>21</v>
-      </c>
-      <c r="P50" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>21</v>
-      </c>
-      <c r="R50" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>132</v>
-      </c>
-      <c r="B51" t="s">
-        <v>133</v>
-      </c>
-      <c r="C51" t="s">
-        <v>114</v>
-      </c>
-      <c r="D51" t="s">
-        <v>21</v>
-      </c>
-      <c r="E51">
-        <v>15</v>
-      </c>
-      <c r="F51" t="s">
-        <v>21</v>
-      </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51">
-        <v>15</v>
-      </c>
-      <c r="I51" t="s">
-        <v>22</v>
-      </c>
-      <c r="J51" t="s">
-        <v>115</v>
-      </c>
-      <c r="K51" t="s">
-        <v>24</v>
-      </c>
-      <c r="L51" t="s">
-        <v>25</v>
-      </c>
-      <c r="M51" t="s">
-        <v>26</v>
-      </c>
-      <c r="N51" t="s">
-        <v>21</v>
-      </c>
-      <c r="O51" t="s">
-        <v>21</v>
-      </c>
-      <c r="P51" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>21</v>
-      </c>
-      <c r="R51" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>134</v>
-      </c>
-      <c r="B52" t="s">
-        <v>135</v>
-      </c>
-      <c r="C52" t="s">
-        <v>136</v>
-      </c>
-      <c r="D52" t="s">
-        <v>137</v>
-      </c>
-      <c r="E52">
-        <v>5</v>
-      </c>
-      <c r="F52" t="s">
-        <v>21</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52">
-        <v>5</v>
-      </c>
-      <c r="I52" t="s">
-        <v>22</v>
-      </c>
-      <c r="J52" t="s">
-        <v>115</v>
-      </c>
-      <c r="K52" t="s">
-        <v>33</v>
-      </c>
-      <c r="L52" t="s">
-        <v>25</v>
-      </c>
-      <c r="M52" t="s">
-        <v>34</v>
-      </c>
-      <c r="N52" t="s">
-        <v>21</v>
-      </c>
-      <c r="O52" t="s">
-        <v>21</v>
-      </c>
-      <c r="P52" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>21</v>
-      </c>
-      <c r="R52" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07BD3B65-21B0-432D-AD63-D31A83DFED33}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE8356A3-5589-40A8-9C24-7C195FEFC53B}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="90">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -127,30 +127,30 @@
     <t>Deposito NQN</t>
   </si>
   <si>
+    <t>391-2882-051</t>
+  </si>
+  <si>
+    <t>CUERDA P30 Y P50</t>
+  </si>
+  <si>
+    <t>SOL - 2384</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>C5OX-24-20F</t>
+  </si>
+  <si>
+    <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
+  </si>
+  <si>
     <t>391-2884-021P</t>
   </si>
   <si>
     <t>SELLO GOMA SQUARE GASKET 50-25</t>
   </si>
   <si>
-    <t>SOL - 2384</t>
-  </si>
-  <si>
-    <t>2026-07</t>
-  </si>
-  <si>
-    <t>C5OX-24-20F</t>
-  </si>
-  <si>
-    <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
-  </si>
-  <si>
-    <t>391-2882-051</t>
-  </si>
-  <si>
-    <t>CUERDA P30 Y P50</t>
-  </si>
-  <si>
     <t>RACORDS Y CAMISAS</t>
   </si>
   <si>
@@ -190,58 +190,58 @@
     <t>SOL - 2493</t>
   </si>
   <si>
+    <t>313-1135-194</t>
+  </si>
+  <si>
+    <t>EJE POSTIZO P50 Z14</t>
+  </si>
+  <si>
+    <t>313-5037-202</t>
+  </si>
+  <si>
+    <t>TROMPA P50 DE 5" X 4</t>
+  </si>
+  <si>
+    <t>391-0381-905</t>
+  </si>
+  <si>
+    <t>TORRINGTON P50</t>
+  </si>
+  <si>
+    <t>FT 221/1-14</t>
+  </si>
+  <si>
+    <t>VALVULA ESFERICA DE 2 VIAS, ALTA PRESION 1/4"</t>
+  </si>
+  <si>
+    <t>MA-310</t>
+  </si>
+  <si>
+    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
+  </si>
+  <si>
+    <t>AC02G-90</t>
+  </si>
+  <si>
+    <t>ALEMITE GAS 90° 1/8"</t>
+  </si>
+  <si>
+    <t>AR02G</t>
+  </si>
+  <si>
+    <t>ALEMITE RECTO DE 1/8" GAS</t>
+  </si>
+  <si>
     <t>391-2883-119P</t>
   </si>
   <si>
     <t>RETEN M-30 P/EJE ENTERIZO</t>
   </si>
   <si>
-    <t>313-1135-194</t>
-  </si>
-  <si>
-    <t>EJE POSTIZO P50 Z14</t>
-  </si>
-  <si>
-    <t>313-5037-202</t>
-  </si>
-  <si>
-    <t>TROMPA P50 DE 5" X 4</t>
-  </si>
-  <si>
-    <t>391-0381-905</t>
-  </si>
-  <si>
-    <t>TORRINGTON P50</t>
-  </si>
-  <si>
-    <t>FT 221/1-14</t>
-  </si>
-  <si>
-    <t>VALVULA ESFERICA DE 2 VIAS, ALTA PRESION 1/4"</t>
-  </si>
-  <si>
-    <t>MA-310</t>
-  </si>
-  <si>
-    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
-  </si>
-  <si>
-    <t>AC02G-90</t>
-  </si>
-  <si>
-    <t>ALEMITE GAS 90° 1/8"</t>
-  </si>
-  <si>
-    <t>AR02G</t>
-  </si>
-  <si>
-    <t>ALEMITE RECTO DE 1/8" GAS</t>
-  </si>
-  <si>
-    <t>AFS-102N</t>
-  </si>
-  <si>
-    <t>BRIDA SAE 1" PARA 3000 PSI</t>
+    <t>F5OG-10-1/2P</t>
+  </si>
+  <si>
+    <t>ADAP RECTO MF 7/8" UNF AS ORING X HEMBRA FIJA 1/2" NPT</t>
   </si>
   <si>
     <t>SOL - 2504</t>
@@ -250,18 +250,6 @@
     <t>2026-09</t>
   </si>
   <si>
-    <t>AFS-106N</t>
-  </si>
-  <si>
-    <t>BRIDA SAE 1.1/2" NPT PARA 3000 PSI</t>
-  </si>
-  <si>
-    <t>F5OG-10-1/2P</t>
-  </si>
-  <si>
-    <t>ADAP RECTO MF 7/8" UNF AS ORING X HEMBRA FIJA 1/2" NPT</t>
-  </si>
-  <si>
     <t>F5OG-12-3/4P</t>
   </si>
   <si>
@@ -302,54 +290,6 @@
   </si>
   <si>
     <t>ADAP CODO 90° FORJADO HG JIC 9/16" UNF x MF 1/4" NPT</t>
-  </si>
-  <si>
-    <t>BH VALVULA C5</t>
-  </si>
-  <si>
-    <t>VALVULA DIRECCIONAL DE CONTROL CAMBIO AUTOMATICA CETOP 5</t>
-  </si>
-  <si>
-    <t>SOL - 2527</t>
-  </si>
-  <si>
-    <t>01006</t>
-  </si>
-  <si>
-    <t>HIDROIL SRL</t>
-  </si>
-  <si>
-    <t>Deposito</t>
-  </si>
-  <si>
-    <t>FILTRO HIDRAULICO</t>
-  </si>
-  <si>
-    <t>FILTRO HIDRAULICO - GENERICO</t>
-  </si>
-  <si>
-    <t>SOL - 2528</t>
-  </si>
-  <si>
-    <t>01007</t>
-  </si>
-  <si>
-    <t>FT 221/1-100</t>
-  </si>
-  <si>
-    <t>VALVULA ESFERICA DE 2 VIAS, ALTA PRESION 1"</t>
-  </si>
-  <si>
-    <t>SOL - 2529</t>
-  </si>
-  <si>
-    <t>01008</t>
-  </si>
-  <si>
-    <t>FT 221/1-12</t>
-  </si>
-  <si>
-    <t>VALVULA ESFERICA DE 2 VIAS, ALTA PRESION 1/2"</t>
   </si>
 </sst>
 </file>
@@ -701,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1110,7 +1050,7 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -1119,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
@@ -1222,7 +1162,7 @@
         <v>21</v>
       </c>
       <c r="E10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -1231,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I10" t="s">
         <v>22</v>
@@ -1502,7 +1442,7 @@
         <v>21</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1511,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
@@ -1558,7 +1498,7 @@
         <v>21</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
@@ -1567,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
@@ -1614,7 +1554,7 @@
         <v>21</v>
       </c>
       <c r="E17">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
         <v>21</v>
@@ -1623,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
@@ -1670,7 +1610,7 @@
         <v>21</v>
       </c>
       <c r="E18">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F18" t="s">
         <v>21</v>
@@ -1679,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I18" t="s">
         <v>22</v>
@@ -1726,7 +1666,7 @@
         <v>21</v>
       </c>
       <c r="E19">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F19" t="s">
         <v>21</v>
@@ -1735,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
@@ -1782,7 +1722,7 @@
         <v>21</v>
       </c>
       <c r="E20">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -1791,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
@@ -1838,7 +1778,7 @@
         <v>21</v>
       </c>
       <c r="E21">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="F21" t="s">
         <v>21</v>
@@ -1847,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
@@ -1894,7 +1834,7 @@
         <v>21</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
         <v>21</v>
@@ -1903,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I22" t="s">
         <v>22</v>
@@ -2006,7 +1946,7 @@
         <v>21</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
         <v>21</v>
@@ -2015,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
@@ -2062,7 +2002,7 @@
         <v>21</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
         <v>21</v>
@@ -2071,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I25" t="s">
         <v>22</v>
@@ -2286,7 +2226,7 @@
         <v>21</v>
       </c>
       <c r="E29">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F29" t="s">
         <v>21</v>
@@ -2295,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I29" t="s">
         <v>22</v>
@@ -2325,398 +2265,6 @@
         <v>21</v>
       </c>
       <c r="R29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>90</v>
-      </c>
-      <c r="B30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>74</v>
-      </c>
-      <c r="D30" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>10</v>
-      </c>
-      <c r="I30" t="s">
-        <v>22</v>
-      </c>
-      <c r="J30" t="s">
-        <v>75</v>
-      </c>
-      <c r="K30" t="s">
-        <v>24</v>
-      </c>
-      <c r="L30" t="s">
-        <v>25</v>
-      </c>
-      <c r="M30" t="s">
-        <v>26</v>
-      </c>
-      <c r="N30" t="s">
-        <v>21</v>
-      </c>
-      <c r="O30" t="s">
-        <v>21</v>
-      </c>
-      <c r="P30" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>21</v>
-      </c>
-      <c r="R30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>92</v>
-      </c>
-      <c r="B31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" t="s">
-        <v>74</v>
-      </c>
-      <c r="D31" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31">
-        <v>15</v>
-      </c>
-      <c r="F31" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>15</v>
-      </c>
-      <c r="I31" t="s">
-        <v>22</v>
-      </c>
-      <c r="J31" t="s">
-        <v>75</v>
-      </c>
-      <c r="K31" t="s">
-        <v>24</v>
-      </c>
-      <c r="L31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M31" t="s">
-        <v>26</v>
-      </c>
-      <c r="N31" t="s">
-        <v>21</v>
-      </c>
-      <c r="O31" t="s">
-        <v>21</v>
-      </c>
-      <c r="P31" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>21</v>
-      </c>
-      <c r="R31" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32" t="s">
-        <v>96</v>
-      </c>
-      <c r="D32" t="s">
-        <v>97</v>
-      </c>
-      <c r="E32">
-        <v>1</v>
-      </c>
-      <c r="F32" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>1</v>
-      </c>
-      <c r="I32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" t="s">
-        <v>75</v>
-      </c>
-      <c r="K32" t="s">
-        <v>98</v>
-      </c>
-      <c r="L32" t="s">
-        <v>25</v>
-      </c>
-      <c r="M32" t="s">
-        <v>99</v>
-      </c>
-      <c r="N32" t="s">
-        <v>21</v>
-      </c>
-      <c r="O32" t="s">
-        <v>21</v>
-      </c>
-      <c r="P32" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>21</v>
-      </c>
-      <c r="R32" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>100</v>
-      </c>
-      <c r="B33" t="s">
-        <v>101</v>
-      </c>
-      <c r="C33" t="s">
-        <v>102</v>
-      </c>
-      <c r="D33" t="s">
-        <v>103</v>
-      </c>
-      <c r="E33">
-        <v>12</v>
-      </c>
-      <c r="F33" t="s">
-        <v>21</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>12</v>
-      </c>
-      <c r="I33" t="s">
-        <v>22</v>
-      </c>
-      <c r="J33" t="s">
-        <v>75</v>
-      </c>
-      <c r="K33" t="s">
-        <v>98</v>
-      </c>
-      <c r="L33" t="s">
-        <v>25</v>
-      </c>
-      <c r="M33" t="s">
-        <v>99</v>
-      </c>
-      <c r="N33" t="s">
-        <v>21</v>
-      </c>
-      <c r="O33" t="s">
-        <v>21</v>
-      </c>
-      <c r="P33" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>21</v>
-      </c>
-      <c r="R33" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" t="s">
-        <v>105</v>
-      </c>
-      <c r="C34" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" t="s">
-        <v>107</v>
-      </c>
-      <c r="E34">
-        <v>4</v>
-      </c>
-      <c r="F34" t="s">
-        <v>21</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>4</v>
-      </c>
-      <c r="I34" t="s">
-        <v>22</v>
-      </c>
-      <c r="J34" t="s">
-        <v>75</v>
-      </c>
-      <c r="K34" t="s">
-        <v>98</v>
-      </c>
-      <c r="L34" t="s">
-        <v>25</v>
-      </c>
-      <c r="M34" t="s">
-        <v>99</v>
-      </c>
-      <c r="N34" t="s">
-        <v>21</v>
-      </c>
-      <c r="O34" t="s">
-        <v>21</v>
-      </c>
-      <c r="P34" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>21</v>
-      </c>
-      <c r="R34" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>108</v>
-      </c>
-      <c r="B35" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" t="s">
-        <v>106</v>
-      </c>
-      <c r="D35" t="s">
-        <v>107</v>
-      </c>
-      <c r="E35">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>21</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>6</v>
-      </c>
-      <c r="I35" t="s">
-        <v>22</v>
-      </c>
-      <c r="J35" t="s">
-        <v>75</v>
-      </c>
-      <c r="K35" t="s">
-        <v>98</v>
-      </c>
-      <c r="L35" t="s">
-        <v>25</v>
-      </c>
-      <c r="M35" t="s">
-        <v>99</v>
-      </c>
-      <c r="N35" t="s">
-        <v>21</v>
-      </c>
-      <c r="O35" t="s">
-        <v>21</v>
-      </c>
-      <c r="P35" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>21</v>
-      </c>
-      <c r="R35" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>64</v>
-      </c>
-      <c r="B36" t="s">
-        <v>65</v>
-      </c>
-      <c r="C36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D36" t="s">
-        <v>107</v>
-      </c>
-      <c r="E36">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>21</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>6</v>
-      </c>
-      <c r="I36" t="s">
-        <v>22</v>
-      </c>
-      <c r="J36" t="s">
-        <v>75</v>
-      </c>
-      <c r="K36" t="s">
-        <v>98</v>
-      </c>
-      <c r="L36" t="s">
-        <v>25</v>
-      </c>
-      <c r="M36" t="s">
-        <v>99</v>
-      </c>
-      <c r="N36" t="s">
-        <v>21</v>
-      </c>
-      <c r="O36" t="s">
-        <v>21</v>
-      </c>
-      <c r="P36" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>21</v>
-      </c>
-      <c r="R36" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE8356A3-5589-40A8-9C24-7C195FEFC53B}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{384F2381-4C95-498B-AA12-03D12D4AD233}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,19 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{384F2381-4C95-498B-AA12-03D12D4AD233}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{304DDB10-52A9-46DE-80B1-651FE81F9FF0}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="79">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -127,60 +134,42 @@
     <t>Deposito NQN</t>
   </si>
   <si>
+    <t>C5OX-24-20F</t>
+  </si>
+  <si>
+    <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
+  </si>
+  <si>
+    <t>SOL - 2384</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
     <t>391-2882-051</t>
   </si>
   <si>
     <t>CUERDA P30 Y P50</t>
   </si>
   <si>
-    <t>SOL - 2384</t>
-  </si>
-  <si>
-    <t>2026-07</t>
-  </si>
-  <si>
-    <t>C5OX-24-20F</t>
-  </si>
-  <si>
-    <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
-  </si>
-  <si>
     <t>391-2884-021P</t>
   </si>
   <si>
     <t>SELLO GOMA SQUARE GASKET 50-25</t>
   </si>
   <si>
-    <t>RACORDS Y CAMISAS</t>
-  </si>
-  <si>
-    <t>RACORDS Y CAMISAS ALTA/BAJA PRESION - GENERICO</t>
-  </si>
-  <si>
-    <t>SOL - 2465</t>
-  </si>
-  <si>
-    <t>0007-00000158</t>
+    <t>RD200EZ</t>
+  </si>
+  <si>
+    <t>ACOPLE TIPO CAMLOCK 2" EZ CUERPO X HEMBRA AISI 316 DIXON</t>
+  </si>
+  <si>
+    <t>SOL - 2489</t>
   </si>
   <si>
     <t>2026-08</t>
   </si>
   <si>
-    <t>SAN JULIAN</t>
-  </si>
-  <si>
-    <t>OPERACIONES SAN JULIAN</t>
-  </si>
-  <si>
-    <t>RD200EZ</t>
-  </si>
-  <si>
-    <t>ACOPLE TIPO CAMLOCK 2" EZ CUERPO X HEMBRA AISI 316 DIXON</t>
-  </si>
-  <si>
-    <t>SOL - 2489</t>
-  </si>
-  <si>
     <t>FILT-D-AB-2</t>
   </si>
   <si>
@@ -190,106 +179,91 @@
     <t>SOL - 2493</t>
   </si>
   <si>
+    <t>MA-310</t>
+  </si>
+  <si>
+    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
+  </si>
+  <si>
+    <t>AC02G-90</t>
+  </si>
+  <si>
+    <t>ALEMITE GAS 90° 1/8"</t>
+  </si>
+  <si>
+    <t>AR02G</t>
+  </si>
+  <si>
+    <t>ALEMITE RECTO DE 1/8" GAS</t>
+  </si>
+  <si>
+    <t>SOL - 2537</t>
+  </si>
+  <si>
+    <t>01049</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>Deposito Nqn 2</t>
+  </si>
+  <si>
     <t>313-1135-194</t>
   </si>
   <si>
     <t>EJE POSTIZO P50 Z14</t>
   </si>
   <si>
+    <t>313-2825-000</t>
+  </si>
+  <si>
+    <t>ENGRANAJE P50 DE 2 1/2"</t>
+  </si>
+  <si>
     <t>313-5037-202</t>
   </si>
   <si>
     <t>TROMPA P50 DE 5" X 4</t>
   </si>
   <si>
-    <t>391-0381-905</t>
-  </si>
-  <si>
-    <t>TORRINGTON P50</t>
-  </si>
-  <si>
-    <t>FT 221/1-14</t>
-  </si>
-  <si>
-    <t>VALVULA ESFERICA DE 2 VIAS, ALTA PRESION 1/4"</t>
-  </si>
-  <si>
-    <t>MA-310</t>
-  </si>
-  <si>
-    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
-  </si>
-  <si>
-    <t>AC02G-90</t>
-  </si>
-  <si>
-    <t>ALEMITE GAS 90° 1/8"</t>
-  </si>
-  <si>
-    <t>AR02G</t>
-  </si>
-  <si>
-    <t>ALEMITE RECTO DE 1/8" GAS</t>
-  </si>
-  <si>
-    <t>391-2883-119P</t>
-  </si>
-  <si>
-    <t>RETEN M-30 P/EJE ENTERIZO</t>
-  </si>
-  <si>
-    <t>F5OG-10-1/2P</t>
-  </si>
-  <si>
-    <t>ADAP RECTO MF 7/8" UNF AS ORING X HEMBRA FIJA 1/2" NPT</t>
-  </si>
-  <si>
-    <t>SOL - 2504</t>
-  </si>
-  <si>
-    <t>2026-09</t>
-  </si>
-  <si>
-    <t>F5OG-12-3/4P</t>
-  </si>
-  <si>
-    <t>ADAP RECTO MF 1.1/16" UNF AS ORING X HEMBRA FIJA 3/4" NPT</t>
-  </si>
-  <si>
-    <t>G6X-06</t>
-  </si>
-  <si>
-    <t>ADAP RECTO HG JIC 9/16" X HF NPT 1/4"</t>
-  </si>
-  <si>
-    <t>G6X-06-06</t>
-  </si>
-  <si>
-    <t>ADAP RECTO HG JIC 9/16" X HF NPT 3/8"</t>
-  </si>
-  <si>
-    <t>G6X-08</t>
-  </si>
-  <si>
-    <t>ADAP RECTO HG JIC 3/4" X HF NPT 3/8"</t>
-  </si>
-  <si>
-    <t>G6X-08-08</t>
-  </si>
-  <si>
-    <t>ADAP RECTO HG JIC 3/4" X HF NPT 1/2"</t>
-  </si>
-  <si>
-    <t>G6X-10</t>
-  </si>
-  <si>
-    <t>ADAP RECTO HG JIC 7/8" X HF NPT 1/2"</t>
-  </si>
-  <si>
-    <t>X6EF-06F</t>
-  </si>
-  <si>
-    <t>ADAP CODO 90° FORJADO HG JIC 9/16" UNF x MF 1/4" NPT</t>
+    <t>313-8225-100</t>
+  </si>
+  <si>
+    <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
+  </si>
+  <si>
+    <t>SA-WLA632-3306F</t>
+  </si>
+  <si>
+    <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
+  </si>
+  <si>
+    <t>SA-632-7800A</t>
+  </si>
+  <si>
+    <t>BOMBA PRECARGA SAUER SERIE 90-75 - 14cc</t>
+  </si>
+  <si>
+    <t>V6X-06F</t>
+  </si>
+  <si>
+    <t>ADAP CODO 45° MF x HG JIC 9/16" UNF</t>
+  </si>
+  <si>
+    <t>SOL - 2550</t>
+  </si>
+  <si>
+    <t>R902095526</t>
+  </si>
+  <si>
+    <t>SEAL KIT A4VG90HD/EP/EZ/DA/32</t>
+  </si>
+  <si>
+    <t>SOL - 2551</t>
+  </si>
+  <si>
+    <t>01060</t>
   </si>
 </sst>
 </file>
@@ -641,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1050,7 +1024,7 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -1059,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
@@ -1106,7 +1080,7 @@
         <v>21</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -1115,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
@@ -1215,34 +1189,34 @@
         <v>45</v>
       </c>
       <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>10</v>
+      </c>
+      <c r="I11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" t="s">
         <v>46</v>
       </c>
-      <c r="E11">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>6</v>
-      </c>
-      <c r="I11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" t="s">
-        <v>47</v>
-      </c>
       <c r="K11" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="L11" t="s">
         <v>25</v>
       </c>
       <c r="M11" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N11" t="s">
         <v>21</v>
@@ -1262,19 +1236,19 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
         <v>21</v>
       </c>
       <c r="E12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1283,13 +1257,13 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
       </c>
       <c r="J12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K12" t="s">
         <v>24</v>
@@ -1318,19 +1292,19 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
         <v>21</v>
       </c>
       <c r="E13">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1339,13 +1313,13 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
       </c>
       <c r="J13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K13" t="s">
         <v>24</v>
@@ -1374,19 +1348,19 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
         <v>21</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1395,13 +1369,13 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
       </c>
       <c r="J14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K14" t="s">
         <v>24</v>
@@ -1430,19 +1404,19 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
         <v>21</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1451,13 +1425,13 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
       </c>
       <c r="J15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K15" t="s">
         <v>24</v>
@@ -1486,19 +1460,19 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="E16">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
@@ -1507,22 +1481,22 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
       </c>
       <c r="J16" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="K16" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L16" t="s">
         <v>25</v>
       </c>
       <c r="M16" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="N16" t="s">
         <v>21</v>
@@ -1542,16 +1516,16 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="E17">
         <v>10</v>
@@ -1569,16 +1543,16 @@
         <v>22</v>
       </c>
       <c r="J17" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="K17" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L17" t="s">
         <v>25</v>
       </c>
       <c r="M17" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="N17" t="s">
         <v>21</v>
@@ -1598,19 +1572,19 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
         <v>21</v>
@@ -1619,22 +1593,22 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I18" t="s">
         <v>22</v>
       </c>
       <c r="J18" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="K18" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L18" t="s">
         <v>25</v>
       </c>
       <c r="M18" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="N18" t="s">
         <v>21</v>
@@ -1654,19 +1628,19 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="E19">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
         <v>21</v>
@@ -1675,22 +1649,22 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
       </c>
       <c r="J19" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="K19" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L19" t="s">
         <v>25</v>
       </c>
       <c r="M19" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="N19" t="s">
         <v>21</v>
@@ -1710,19 +1684,19 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="E20">
-        <v>300</v>
+        <v>12</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -1731,22 +1705,22 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>300</v>
+        <v>12</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
       </c>
       <c r="J20" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="K20" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L20" t="s">
         <v>25</v>
       </c>
       <c r="M20" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="N20" t="s">
         <v>21</v>
@@ -1766,19 +1740,19 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="E21">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F21" t="s">
         <v>21</v>
@@ -1787,22 +1761,22 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
       </c>
       <c r="J21" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="K21" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L21" t="s">
         <v>25</v>
       </c>
       <c r="M21" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="N21" t="s">
         <v>21</v>
@@ -1822,16 +1796,16 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="D22" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="E22">
         <v>5</v>
@@ -1849,16 +1823,16 @@
         <v>22</v>
       </c>
       <c r="J22" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="K22" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L22" t="s">
         <v>25</v>
       </c>
       <c r="M22" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="N22" t="s">
         <v>21</v>
@@ -1878,10 +1852,10 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
         <v>74</v>
@@ -1890,7 +1864,7 @@
         <v>21</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
         <v>21</v>
@@ -1899,13 +1873,13 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="I23" t="s">
         <v>22</v>
       </c>
       <c r="J23" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="K23" t="s">
         <v>24</v>
@@ -1934,19 +1908,19 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" t="s">
         <v>78</v>
       </c>
-      <c r="B24" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" t="s">
-        <v>74</v>
-      </c>
-      <c r="D24" t="s">
-        <v>21</v>
-      </c>
       <c r="E24">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F24" t="s">
         <v>21</v>
@@ -1955,22 +1929,22 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
       </c>
       <c r="J24" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="K24" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L24" t="s">
         <v>25</v>
       </c>
       <c r="M24" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="N24" t="s">
         <v>21</v>
@@ -1985,286 +1959,6 @@
         <v>21</v>
       </c>
       <c r="R24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>10</v>
-      </c>
-      <c r="I25" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" t="s">
-        <v>75</v>
-      </c>
-      <c r="K25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L25" t="s">
-        <v>25</v>
-      </c>
-      <c r="M25" t="s">
-        <v>26</v>
-      </c>
-      <c r="N25" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" t="s">
-        <v>21</v>
-      </c>
-      <c r="P25" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>21</v>
-      </c>
-      <c r="R25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>82</v>
-      </c>
-      <c r="B26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>10</v>
-      </c>
-      <c r="I26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" t="s">
-        <v>75</v>
-      </c>
-      <c r="K26" t="s">
-        <v>24</v>
-      </c>
-      <c r="L26" t="s">
-        <v>25</v>
-      </c>
-      <c r="M26" t="s">
-        <v>26</v>
-      </c>
-      <c r="N26" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" t="s">
-        <v>21</v>
-      </c>
-      <c r="P26" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>21</v>
-      </c>
-      <c r="R26" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>10</v>
-      </c>
-      <c r="I27" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" t="s">
-        <v>75</v>
-      </c>
-      <c r="K27" t="s">
-        <v>24</v>
-      </c>
-      <c r="L27" t="s">
-        <v>25</v>
-      </c>
-      <c r="M27" t="s">
-        <v>26</v>
-      </c>
-      <c r="N27" t="s">
-        <v>21</v>
-      </c>
-      <c r="O27" t="s">
-        <v>21</v>
-      </c>
-      <c r="P27" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>21</v>
-      </c>
-      <c r="R27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" t="s">
-        <v>74</v>
-      </c>
-      <c r="D28" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>10</v>
-      </c>
-      <c r="I28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J28" t="s">
-        <v>75</v>
-      </c>
-      <c r="K28" t="s">
-        <v>24</v>
-      </c>
-      <c r="L28" t="s">
-        <v>25</v>
-      </c>
-      <c r="M28" t="s">
-        <v>26</v>
-      </c>
-      <c r="N28" t="s">
-        <v>21</v>
-      </c>
-      <c r="O28" t="s">
-        <v>21</v>
-      </c>
-      <c r="P28" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>21</v>
-      </c>
-      <c r="R28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>88</v>
-      </c>
-      <c r="B29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29">
-        <v>15</v>
-      </c>
-      <c r="F29" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>15</v>
-      </c>
-      <c r="I29" t="s">
-        <v>22</v>
-      </c>
-      <c r="J29" t="s">
-        <v>75</v>
-      </c>
-      <c r="K29" t="s">
-        <v>24</v>
-      </c>
-      <c r="L29" t="s">
-        <v>25</v>
-      </c>
-      <c r="M29" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" t="s">
-        <v>21</v>
-      </c>
-      <c r="O29" t="s">
-        <v>21</v>
-      </c>
-      <c r="P29" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>21</v>
-      </c>
-      <c r="R29" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{304DDB10-52A9-46DE-80B1-651FE81F9FF0}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0C35DCD-2BF9-45B0-857E-9CFBDCEF53AE}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="110">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -185,18 +185,6 @@
     <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
   </si>
   <si>
-    <t>AC02G-90</t>
-  </si>
-  <si>
-    <t>ALEMITE GAS 90° 1/8"</t>
-  </si>
-  <si>
-    <t>AR02G</t>
-  </si>
-  <si>
-    <t>ALEMITE RECTO DE 1/8" GAS</t>
-  </si>
-  <si>
     <t>SOL - 2537</t>
   </si>
   <si>
@@ -209,6 +197,18 @@
     <t>Deposito Nqn 2</t>
   </si>
   <si>
+    <t>SA-632-7800A</t>
+  </si>
+  <si>
+    <t>BOMBA PRECARGA SAUER SERIE 90-75 - 14cc</t>
+  </si>
+  <si>
+    <t>SA-WLA632-3306F</t>
+  </si>
+  <si>
+    <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
+  </si>
+  <si>
     <t>313-1135-194</t>
   </si>
   <si>
@@ -233,18 +233,6 @@
     <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
   </si>
   <si>
-    <t>SA-WLA632-3306F</t>
-  </si>
-  <si>
-    <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
-  </si>
-  <si>
-    <t>SA-632-7800A</t>
-  </si>
-  <si>
-    <t>BOMBA PRECARGA SAUER SERIE 90-75 - 14cc</t>
-  </si>
-  <si>
     <t>V6X-06F</t>
   </si>
   <si>
@@ -254,16 +242,121 @@
     <t>SOL - 2550</t>
   </si>
   <si>
-    <t>R902095526</t>
-  </si>
-  <si>
-    <t>SEAL KIT A4VG90HD/EP/EZ/DA/32</t>
-  </si>
-  <si>
-    <t>SOL - 2551</t>
-  </si>
-  <si>
-    <t>01060</t>
+    <t>SA-634-1100C</t>
+  </si>
+  <si>
+    <t>BLOCK CILINDROS SAUER SERIE 90-130</t>
+  </si>
+  <si>
+    <t>SOL - 2555</t>
+  </si>
+  <si>
+    <t>SA-634-5256</t>
+  </si>
+  <si>
+    <t>CANASTO PORTA RODILLO SAUER 90-130 SET</t>
+  </si>
+  <si>
+    <t>SA-634-5257A</t>
+  </si>
+  <si>
+    <t>CUNA SAUER SERIE 90-130 (UNITARIO) MN - 148.7x29.8x51</t>
+  </si>
+  <si>
+    <t>SA-634-2200</t>
+  </si>
+  <si>
+    <t>PISTON SAUER SERIE 90-130</t>
+  </si>
+  <si>
+    <t>SA-640-5256</t>
+  </si>
+  <si>
+    <t>CANASTO PORTA RODILLO SAUER SERIE 90-100</t>
+  </si>
+  <si>
+    <t>SA-640-5251</t>
+  </si>
+  <si>
+    <t>CUNA SAUER GRUESA SERIE 90-100 MV</t>
+  </si>
+  <si>
+    <t>SA-632-1100C</t>
+  </si>
+  <si>
+    <t>BLOCK CILINDROS SAUER SERIE 90-75</t>
+  </si>
+  <si>
+    <t>SA-639-5256</t>
+  </si>
+  <si>
+    <t>CANASTO PORTA RODILLO SAUER SERIE 90-75</t>
+  </si>
+  <si>
+    <t>SA-631-3306F</t>
+  </si>
+  <si>
+    <t>KIT SELLOS BOMBA SAUER 90-55</t>
+  </si>
+  <si>
+    <t>SA-638-4701</t>
+  </si>
+  <si>
+    <t>PLACA FRICCION SAUER 90-55</t>
+  </si>
+  <si>
+    <t>SA-638-3306F</t>
+  </si>
+  <si>
+    <t>KIT SELLOS MOTOR SAUER 90-55</t>
+  </si>
+  <si>
+    <t>SA-638-5256</t>
+  </si>
+  <si>
+    <t>CANASTO PORTA RODILLO SAUER 90-55</t>
+  </si>
+  <si>
+    <t>SA-631-4301</t>
+  </si>
+  <si>
+    <t>PLACA VALV. MOTOR SAUER SERIE 90-55</t>
+  </si>
+  <si>
+    <t>SA-631-4501</t>
+  </si>
+  <si>
+    <t>PLACA VALV. LH/RH SAUER SERIE 90-55</t>
+  </si>
+  <si>
+    <t>SA-631-1100C</t>
+  </si>
+  <si>
+    <t>BLOCK CILINDROS SAUER SERIE 90-55 - 8510363</t>
+  </si>
+  <si>
+    <t>SA-631-2100C</t>
+  </si>
+  <si>
+    <t>PISTON SAUER SERIE 90-55</t>
+  </si>
+  <si>
+    <t>SA-634-5221</t>
+  </si>
+  <si>
+    <t>BASCULANTE SAUER SERIE 90-130 BOMBA - VERSION VIEJA</t>
+  </si>
+  <si>
+    <t>SA-505410</t>
+  </si>
+  <si>
+    <t>BOMBA DE CARGA DANFOSS 90 PV250 65 CC/REV</t>
+  </si>
+  <si>
+    <t>SA-11012275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EJE DANFOSS Z=14 MF90-055 12/24 (S1) </t>
   </si>
 </sst>
 </file>
@@ -615,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -688,7 +781,7 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
@@ -697,7 +790,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
         <v>22</v>
@@ -744,7 +837,7 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
@@ -753,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
@@ -856,7 +949,7 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
@@ -865,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I5" t="s">
         <v>22</v>
@@ -912,7 +1005,7 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
@@ -921,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I6" t="s">
         <v>22</v>
@@ -1348,16 +1441,16 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" t="s">
         <v>52</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
         <v>53</v>
-      </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" t="s">
-        <v>21</v>
       </c>
       <c r="E14">
         <v>100</v>
@@ -1375,16 +1468,16 @@
         <v>22</v>
       </c>
       <c r="J14" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K14" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L14" t="s">
         <v>25</v>
       </c>
       <c r="M14" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="N14" t="s">
         <v>21</v>
@@ -1404,43 +1497,43 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>5</v>
+      </c>
+      <c r="I15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" t="s">
         <v>54</v>
       </c>
-      <c r="B15" t="s">
+      <c r="K15" t="s">
+        <v>33</v>
+      </c>
+      <c r="L15" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" t="s">
         <v>55</v>
-      </c>
-      <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15">
-        <v>300</v>
-      </c>
-      <c r="F15" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>300</v>
-      </c>
-      <c r="I15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" t="s">
-        <v>46</v>
-      </c>
-      <c r="K15" t="s">
-        <v>24</v>
-      </c>
-      <c r="L15" t="s">
-        <v>25</v>
-      </c>
-      <c r="M15" t="s">
-        <v>26</v>
       </c>
       <c r="N15" t="s">
         <v>21</v>
@@ -1460,19 +1553,19 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E16">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
@@ -1481,13 +1574,13 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
       </c>
       <c r="J16" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K16" t="s">
         <v>33</v>
@@ -1496,7 +1589,7 @@
         <v>25</v>
       </c>
       <c r="M16" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="N16" t="s">
         <v>21</v>
@@ -1522,10 +1615,10 @@
         <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E17">
         <v>10</v>
@@ -1543,7 +1636,7 @@
         <v>22</v>
       </c>
       <c r="J17" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K17" t="s">
         <v>33</v>
@@ -1552,7 +1645,7 @@
         <v>25</v>
       </c>
       <c r="M17" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="N17" t="s">
         <v>21</v>
@@ -1578,10 +1671,10 @@
         <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E18">
         <v>6</v>
@@ -1599,7 +1692,7 @@
         <v>22</v>
       </c>
       <c r="J18" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K18" t="s">
         <v>33</v>
@@ -1608,7 +1701,7 @@
         <v>25</v>
       </c>
       <c r="M18" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="N18" t="s">
         <v>21</v>
@@ -1634,10 +1727,10 @@
         <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E19">
         <v>6</v>
@@ -1655,7 +1748,7 @@
         <v>22</v>
       </c>
       <c r="J19" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K19" t="s">
         <v>33</v>
@@ -1664,7 +1757,7 @@
         <v>25</v>
       </c>
       <c r="M19" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="N19" t="s">
         <v>21</v>
@@ -1690,10 +1783,10 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E20">
         <v>12</v>
@@ -1711,7 +1804,7 @@
         <v>22</v>
       </c>
       <c r="J20" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K20" t="s">
         <v>33</v>
@@ -1720,7 +1813,7 @@
         <v>25</v>
       </c>
       <c r="M20" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="N20" t="s">
         <v>21</v>
@@ -1746,13 +1839,13 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F21" t="s">
         <v>21</v>
@@ -1761,22 +1854,22 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
       </c>
       <c r="J21" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K21" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L21" t="s">
         <v>25</v>
       </c>
       <c r="M21" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="N21" t="s">
         <v>21</v>
@@ -1796,19 +1889,19 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F22" t="s">
         <v>21</v>
@@ -1817,22 +1910,22 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I22" t="s">
         <v>22</v>
       </c>
       <c r="J22" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K22" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L22" t="s">
         <v>25</v>
       </c>
       <c r="M22" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="N22" t="s">
         <v>21</v>
@@ -1852,19 +1945,19 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" t="s">
         <v>73</v>
       </c>
-      <c r="C23" t="s">
-        <v>74</v>
-      </c>
       <c r="D23" t="s">
         <v>21</v>
       </c>
       <c r="E23">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="F23" t="s">
         <v>21</v>
@@ -1873,13 +1966,13 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="I23" t="s">
         <v>22</v>
       </c>
       <c r="J23" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K23" t="s">
         <v>24</v>
@@ -1908,57 +2001,953 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" t="s">
+        <v>54</v>
+      </c>
+      <c r="K24" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" t="s">
+        <v>25</v>
+      </c>
+      <c r="M24" t="s">
+        <v>26</v>
+      </c>
+      <c r="N24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O24" t="s">
+        <v>21</v>
+      </c>
+      <c r="P24" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>21</v>
+      </c>
+      <c r="R24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>78</v>
       </c>
-      <c r="E24">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>5</v>
-      </c>
-      <c r="I24" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" t="s">
-        <v>58</v>
-      </c>
-      <c r="K24" t="s">
-        <v>33</v>
-      </c>
-      <c r="L24" t="s">
-        <v>25</v>
-      </c>
-      <c r="M24" t="s">
-        <v>34</v>
-      </c>
-      <c r="N24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O24" t="s">
-        <v>21</v>
-      </c>
-      <c r="P24" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>21</v>
-      </c>
-      <c r="R24" t="s">
+      <c r="B25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>9</v>
+      </c>
+      <c r="I25" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" t="s">
+        <v>54</v>
+      </c>
+      <c r="K25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O25" t="s">
+        <v>21</v>
+      </c>
+      <c r="P25" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" t="s">
+        <v>54</v>
+      </c>
+      <c r="K26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M26" t="s">
+        <v>26</v>
+      </c>
+      <c r="N26" t="s">
+        <v>21</v>
+      </c>
+      <c r="O26" t="s">
+        <v>21</v>
+      </c>
+      <c r="P26" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>21</v>
+      </c>
+      <c r="R26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>2</v>
+      </c>
+      <c r="I27" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" t="s">
+        <v>54</v>
+      </c>
+      <c r="K27" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" t="s">
+        <v>25</v>
+      </c>
+      <c r="M27" t="s">
+        <v>26</v>
+      </c>
+      <c r="N27" t="s">
+        <v>21</v>
+      </c>
+      <c r="O27" t="s">
+        <v>21</v>
+      </c>
+      <c r="P27" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>21</v>
+      </c>
+      <c r="R27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" t="s">
+        <v>54</v>
+      </c>
+      <c r="K28" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" t="s">
+        <v>25</v>
+      </c>
+      <c r="M28" t="s">
+        <v>26</v>
+      </c>
+      <c r="N28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O28" t="s">
+        <v>21</v>
+      </c>
+      <c r="P28" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>21</v>
+      </c>
+      <c r="R28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29">
+        <v>3</v>
+      </c>
+      <c r="F29" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>3</v>
+      </c>
+      <c r="I29" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" t="s">
+        <v>54</v>
+      </c>
+      <c r="K29" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" t="s">
+        <v>25</v>
+      </c>
+      <c r="M29" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" t="s">
+        <v>21</v>
+      </c>
+      <c r="O29" t="s">
+        <v>21</v>
+      </c>
+      <c r="P29" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>21</v>
+      </c>
+      <c r="R29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" t="s">
+        <v>54</v>
+      </c>
+      <c r="K30" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" t="s">
+        <v>25</v>
+      </c>
+      <c r="M30" t="s">
+        <v>26</v>
+      </c>
+      <c r="N30" t="s">
+        <v>21</v>
+      </c>
+      <c r="O30" t="s">
+        <v>21</v>
+      </c>
+      <c r="P30" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>21</v>
+      </c>
+      <c r="R30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31" t="s">
+        <v>22</v>
+      </c>
+      <c r="J31" t="s">
+        <v>54</v>
+      </c>
+      <c r="K31" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" t="s">
+        <v>25</v>
+      </c>
+      <c r="M31" t="s">
+        <v>26</v>
+      </c>
+      <c r="N31" t="s">
+        <v>21</v>
+      </c>
+      <c r="O31" t="s">
+        <v>21</v>
+      </c>
+      <c r="P31" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>21</v>
+      </c>
+      <c r="R31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" t="s">
+        <v>73</v>
+      </c>
+      <c r="D32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" t="s">
+        <v>54</v>
+      </c>
+      <c r="K32" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" t="s">
+        <v>25</v>
+      </c>
+      <c r="M32" t="s">
+        <v>26</v>
+      </c>
+      <c r="N32" t="s">
+        <v>21</v>
+      </c>
+      <c r="O32" t="s">
+        <v>21</v>
+      </c>
+      <c r="P32" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>21</v>
+      </c>
+      <c r="R32" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" t="s">
+        <v>54</v>
+      </c>
+      <c r="K33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" t="s">
+        <v>25</v>
+      </c>
+      <c r="M33" t="s">
+        <v>26</v>
+      </c>
+      <c r="N33" t="s">
+        <v>21</v>
+      </c>
+      <c r="O33" t="s">
+        <v>21</v>
+      </c>
+      <c r="P33" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>21</v>
+      </c>
+      <c r="R33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34" t="s">
+        <v>22</v>
+      </c>
+      <c r="J34" t="s">
+        <v>54</v>
+      </c>
+      <c r="K34" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" t="s">
+        <v>25</v>
+      </c>
+      <c r="M34" t="s">
+        <v>26</v>
+      </c>
+      <c r="N34" t="s">
+        <v>21</v>
+      </c>
+      <c r="O34" t="s">
+        <v>21</v>
+      </c>
+      <c r="P34" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>21</v>
+      </c>
+      <c r="R34" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" t="s">
+        <v>99</v>
+      </c>
+      <c r="C35" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35" t="s">
+        <v>22</v>
+      </c>
+      <c r="J35" t="s">
+        <v>54</v>
+      </c>
+      <c r="K35" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" t="s">
+        <v>25</v>
+      </c>
+      <c r="M35" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" t="s">
+        <v>21</v>
+      </c>
+      <c r="O35" t="s">
+        <v>21</v>
+      </c>
+      <c r="P35" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>21</v>
+      </c>
+      <c r="R35" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36">
+        <v>2</v>
+      </c>
+      <c r="F36" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>2</v>
+      </c>
+      <c r="I36" t="s">
+        <v>22</v>
+      </c>
+      <c r="J36" t="s">
+        <v>54</v>
+      </c>
+      <c r="K36" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" t="s">
+        <v>25</v>
+      </c>
+      <c r="M36" t="s">
+        <v>26</v>
+      </c>
+      <c r="N36" t="s">
+        <v>21</v>
+      </c>
+      <c r="O36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P36" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>21</v>
+      </c>
+      <c r="R36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" t="s">
+        <v>103</v>
+      </c>
+      <c r="C37" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37">
+        <v>18</v>
+      </c>
+      <c r="F37" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>18</v>
+      </c>
+      <c r="I37" t="s">
+        <v>22</v>
+      </c>
+      <c r="J37" t="s">
+        <v>54</v>
+      </c>
+      <c r="K37" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" t="s">
+        <v>25</v>
+      </c>
+      <c r="M37" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" t="s">
+        <v>21</v>
+      </c>
+      <c r="O37" t="s">
+        <v>21</v>
+      </c>
+      <c r="P37" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R37" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>104</v>
+      </c>
+      <c r="B38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>22</v>
+      </c>
+      <c r="J38" t="s">
+        <v>54</v>
+      </c>
+      <c r="K38" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" t="s">
+        <v>25</v>
+      </c>
+      <c r="M38" t="s">
+        <v>26</v>
+      </c>
+      <c r="N38" t="s">
+        <v>21</v>
+      </c>
+      <c r="O38" t="s">
+        <v>21</v>
+      </c>
+      <c r="P38" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>21</v>
+      </c>
+      <c r="R38" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" t="s">
+        <v>107</v>
+      </c>
+      <c r="C39" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39">
+        <v>3</v>
+      </c>
+      <c r="F39" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>3</v>
+      </c>
+      <c r="I39" t="s">
+        <v>22</v>
+      </c>
+      <c r="J39" t="s">
+        <v>54</v>
+      </c>
+      <c r="K39" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" t="s">
+        <v>25</v>
+      </c>
+      <c r="M39" t="s">
+        <v>26</v>
+      </c>
+      <c r="N39" t="s">
+        <v>21</v>
+      </c>
+      <c r="O39" t="s">
+        <v>21</v>
+      </c>
+      <c r="P39" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>21</v>
+      </c>
+      <c r="R39" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" t="s">
+        <v>109</v>
+      </c>
+      <c r="C40" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40" t="s">
+        <v>22</v>
+      </c>
+      <c r="J40" t="s">
+        <v>54</v>
+      </c>
+      <c r="K40" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" t="s">
+        <v>25</v>
+      </c>
+      <c r="M40" t="s">
+        <v>26</v>
+      </c>
+      <c r="N40" t="s">
+        <v>21</v>
+      </c>
+      <c r="O40" t="s">
+        <v>21</v>
+      </c>
+      <c r="P40" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>21</v>
+      </c>
+      <c r="R40" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0C35DCD-2BF9-45B0-857E-9CFBDCEF53AE}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03D10498-183F-4904-8D70-E439E8E04F48}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="114">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -170,19 +170,25 @@
     <t>2026-08</t>
   </si>
   <si>
+    <t>MA-310</t>
+  </si>
+  <si>
+    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
+  </si>
+  <si>
+    <t>SOL - 2493</t>
+  </si>
+  <si>
     <t>FILT-D-AB-2</t>
   </si>
   <si>
     <t>FILTRO AIRE RESP DESECANTE</t>
   </si>
   <si>
-    <t>SOL - 2493</t>
-  </si>
-  <si>
-    <t>MA-310</t>
-  </si>
-  <si>
-    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
+    <t>313-1135-194</t>
+  </si>
+  <si>
+    <t>EJE POSTIZO P50 Z14</t>
   </si>
   <si>
     <t>SOL - 2537</t>
@@ -197,6 +203,24 @@
     <t>Deposito Nqn 2</t>
   </si>
   <si>
+    <t>313-2825-000</t>
+  </si>
+  <si>
+    <t>ENGRANAJE P50 DE 2 1/2"</t>
+  </si>
+  <si>
+    <t>313-5037-202</t>
+  </si>
+  <si>
+    <t>TROMPA P50 DE 5" X 4</t>
+  </si>
+  <si>
+    <t>313-8225-100</t>
+  </si>
+  <si>
+    <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
+  </si>
+  <si>
     <t>SA-632-7800A</t>
   </si>
   <si>
@@ -209,37 +233,73 @@
     <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
   </si>
   <si>
-    <t>313-1135-194</t>
-  </si>
-  <si>
-    <t>EJE POSTIZO P50 Z14</t>
-  </si>
-  <si>
-    <t>313-2825-000</t>
-  </si>
-  <si>
-    <t>ENGRANAJE P50 DE 2 1/2"</t>
-  </si>
-  <si>
-    <t>313-5037-202</t>
-  </si>
-  <si>
-    <t>TROMPA P50 DE 5" X 4</t>
-  </si>
-  <si>
-    <t>313-8225-100</t>
-  </si>
-  <si>
-    <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
-  </si>
-  <si>
-    <t>V6X-06F</t>
-  </si>
-  <si>
-    <t>ADAP CODO 45° MF x HG JIC 9/16" UNF</t>
-  </si>
-  <si>
-    <t>SOL - 2550</t>
+    <t>SA-631-3306F</t>
+  </si>
+  <si>
+    <t>KIT SELLOS BOMBA SAUER 90-55</t>
+  </si>
+  <si>
+    <t>SOL - 2555</t>
+  </si>
+  <si>
+    <t>SA-638-4701</t>
+  </si>
+  <si>
+    <t>PLACA FRICCION SAUER 90-55</t>
+  </si>
+  <si>
+    <t>SA-638-3306F</t>
+  </si>
+  <si>
+    <t>KIT SELLOS MOTOR SAUER 90-55</t>
+  </si>
+  <si>
+    <t>SA-638-5256</t>
+  </si>
+  <si>
+    <t>CANASTO PORTA RODILLO SAUER 90-55</t>
+  </si>
+  <si>
+    <t>SA-631-4301</t>
+  </si>
+  <si>
+    <t>PLACA VALV. MOTOR SAUER SERIE 90-55</t>
+  </si>
+  <si>
+    <t>SA-631-4501</t>
+  </si>
+  <si>
+    <t>PLACA VALV. LH/RH SAUER SERIE 90-55</t>
+  </si>
+  <si>
+    <t>SA-631-1100C</t>
+  </si>
+  <si>
+    <t>BLOCK CILINDROS SAUER SERIE 90-55 - 8510363</t>
+  </si>
+  <si>
+    <t>SA-631-2100C</t>
+  </si>
+  <si>
+    <t>PISTON SAUER SERIE 90-55</t>
+  </si>
+  <si>
+    <t>SA-634-5221</t>
+  </si>
+  <si>
+    <t>BASCULANTE SAUER SERIE 90-130 BOMBA - VERSION VIEJA</t>
+  </si>
+  <si>
+    <t>SA-505410</t>
+  </si>
+  <si>
+    <t>BOMBA DE CARGA DANFOSS 90 PV250 65 CC/REV</t>
+  </si>
+  <si>
+    <t>SA-11012275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EJE DANFOSS Z=14 MF90-055 12/24 (S1) </t>
   </si>
   <si>
     <t>SA-634-1100C</t>
@@ -248,9 +308,6 @@
     <t>BLOCK CILINDROS SAUER SERIE 90-130</t>
   </si>
   <si>
-    <t>SOL - 2555</t>
-  </si>
-  <si>
     <t>SA-634-5256</t>
   </si>
   <si>
@@ -293,70 +350,25 @@
     <t>CANASTO PORTA RODILLO SAUER SERIE 90-75</t>
   </si>
   <si>
-    <t>SA-631-3306F</t>
-  </si>
-  <si>
-    <t>KIT SELLOS BOMBA SAUER 90-55</t>
-  </si>
-  <si>
-    <t>SA-638-4701</t>
-  </si>
-  <si>
-    <t>PLACA FRICCION SAUER 90-55</t>
-  </si>
-  <si>
-    <t>SA-638-3306F</t>
-  </si>
-  <si>
-    <t>KIT SELLOS MOTOR SAUER 90-55</t>
-  </si>
-  <si>
-    <t>SA-638-5256</t>
-  </si>
-  <si>
-    <t>CANASTO PORTA RODILLO SAUER 90-55</t>
-  </si>
-  <si>
-    <t>SA-631-4301</t>
-  </si>
-  <si>
-    <t>PLACA VALV. MOTOR SAUER SERIE 90-55</t>
-  </si>
-  <si>
-    <t>SA-631-4501</t>
-  </si>
-  <si>
-    <t>PLACA VALV. LH/RH SAUER SERIE 90-55</t>
-  </si>
-  <si>
-    <t>SA-631-1100C</t>
-  </si>
-  <si>
-    <t>BLOCK CILINDROS SAUER SERIE 90-55 - 8510363</t>
-  </si>
-  <si>
-    <t>SA-631-2100C</t>
-  </si>
-  <si>
-    <t>PISTON SAUER SERIE 90-55</t>
-  </si>
-  <si>
-    <t>SA-634-5221</t>
-  </si>
-  <si>
-    <t>BASCULANTE SAUER SERIE 90-130 BOMBA - VERSION VIEJA</t>
-  </si>
-  <si>
-    <t>SA-505410</t>
-  </si>
-  <si>
-    <t>BOMBA DE CARGA DANFOSS 90 PV250 65 CC/REV</t>
-  </si>
-  <si>
-    <t>SA-11012275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EJE DANFOSS Z=14 MF90-055 12/24 (S1) </t>
+    <t>SA-632-2100C</t>
+  </si>
+  <si>
+    <t>PISTON SAUER SERIE 90-75</t>
+  </si>
+  <si>
+    <t>SOL - 2564</t>
+  </si>
+  <si>
+    <t>FILT-10MZ10</t>
+  </si>
+  <si>
+    <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 10"</t>
+  </si>
+  <si>
+    <t>FILT-MZ10</t>
+  </si>
+  <si>
+    <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 7"</t>
   </si>
 </sst>
 </file>
@@ -708,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R40"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -781,7 +793,7 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
@@ -790,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I2" t="s">
         <v>22</v>
@@ -837,7 +849,7 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
@@ -846,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
@@ -949,7 +961,7 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
@@ -958,7 +970,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
         <v>22</v>
@@ -1005,7 +1017,7 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
@@ -1014,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
         <v>22</v>
@@ -1341,7 +1353,7 @@
         <v>21</v>
       </c>
       <c r="E12">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1350,7 +1362,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
@@ -1397,7 +1409,7 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1406,7 +1418,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
@@ -1441,19 +1453,19 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1462,13 +1474,13 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
       </c>
       <c r="J14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K14" t="s">
         <v>33</v>
@@ -1477,7 +1489,7 @@
         <v>25</v>
       </c>
       <c r="M14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N14" t="s">
         <v>21</v>
@@ -1497,34 +1509,34 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15">
+        <v>6</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>6</v>
+      </c>
+      <c r="I15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" t="s">
         <v>56</v>
-      </c>
-      <c r="B15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>5</v>
-      </c>
-      <c r="I15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" t="s">
-        <v>54</v>
       </c>
       <c r="K15" t="s">
         <v>33</v>
@@ -1533,7 +1545,7 @@
         <v>25</v>
       </c>
       <c r="M15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N15" t="s">
         <v>21</v>
@@ -1553,19 +1565,19 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
@@ -1574,13 +1586,13 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
       </c>
       <c r="J16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K16" t="s">
         <v>33</v>
@@ -1589,7 +1601,7 @@
         <v>25</v>
       </c>
       <c r="M16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N16" t="s">
         <v>21</v>
@@ -1609,19 +1621,19 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F17" t="s">
         <v>21</v>
@@ -1630,13 +1642,13 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
       </c>
       <c r="J17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K17" t="s">
         <v>33</v>
@@ -1645,7 +1657,7 @@
         <v>25</v>
       </c>
       <c r="M17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N17" t="s">
         <v>21</v>
@@ -1665,19 +1677,19 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E18">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="F18" t="s">
         <v>21</v>
@@ -1686,13 +1698,13 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="I18" t="s">
         <v>22</v>
       </c>
       <c r="J18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K18" t="s">
         <v>33</v>
@@ -1701,7 +1713,7 @@
         <v>25</v>
       </c>
       <c r="M18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N18" t="s">
         <v>21</v>
@@ -1727,13 +1739,13 @@
         <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
         <v>21</v>
@@ -1742,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
       </c>
       <c r="J19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K19" t="s">
         <v>33</v>
@@ -1757,7 +1769,7 @@
         <v>25</v>
       </c>
       <c r="M19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N19" t="s">
         <v>21</v>
@@ -1783,13 +1795,13 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E20">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -1798,13 +1810,13 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
       </c>
       <c r="J20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K20" t="s">
         <v>33</v>
@@ -1813,7 +1825,7 @@
         <v>25</v>
       </c>
       <c r="M20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N20" t="s">
         <v>21</v>
@@ -1845,7 +1857,7 @@
         <v>21</v>
       </c>
       <c r="E21">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F21" t="s">
         <v>21</v>
@@ -1854,13 +1866,13 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
       </c>
       <c r="J21" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K21" t="s">
         <v>24</v>
@@ -1895,7 +1907,7 @@
         <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
         <v>21</v>
@@ -1916,7 +1928,7 @@
         <v>22</v>
       </c>
       <c r="J22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K22" t="s">
         <v>24</v>
@@ -1945,19 +1957,19 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" t="s">
         <v>74</v>
       </c>
-      <c r="B23" t="s">
-        <v>75</v>
-      </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D23" t="s">
         <v>21</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" t="s">
         <v>21</v>
@@ -1966,13 +1978,13 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I23" t="s">
         <v>22</v>
       </c>
       <c r="J23" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K23" t="s">
         <v>24</v>
@@ -2001,19 +2013,19 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" t="s">
         <v>76</v>
       </c>
-      <c r="B24" t="s">
-        <v>77</v>
-      </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D24" t="s">
         <v>21</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24" t="s">
         <v>21</v>
@@ -2022,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
       </c>
       <c r="J24" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K24" t="s">
         <v>24</v>
@@ -2057,19 +2069,19 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" t="s">
         <v>78</v>
       </c>
-      <c r="B25" t="s">
-        <v>79</v>
-      </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D25" t="s">
         <v>21</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F25" t="s">
         <v>21</v>
@@ -2078,13 +2090,13 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I25" t="s">
         <v>22</v>
       </c>
       <c r="J25" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K25" t="s">
         <v>24</v>
@@ -2113,13 +2125,13 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" t="s">
         <v>80</v>
       </c>
-      <c r="B26" t="s">
-        <v>81</v>
-      </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D26" t="s">
         <v>21</v>
@@ -2140,7 +2152,7 @@
         <v>22</v>
       </c>
       <c r="J26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K26" t="s">
         <v>24</v>
@@ -2169,13 +2181,13 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" t="s">
         <v>82</v>
       </c>
-      <c r="B27" t="s">
-        <v>83</v>
-      </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D27" t="s">
         <v>21</v>
@@ -2196,7 +2208,7 @@
         <v>22</v>
       </c>
       <c r="J27" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K27" t="s">
         <v>24</v>
@@ -2225,19 +2237,19 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" t="s">
         <v>84</v>
       </c>
-      <c r="B28" t="s">
-        <v>85</v>
-      </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D28" t="s">
         <v>21</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F28" t="s">
         <v>21</v>
@@ -2246,13 +2258,13 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I28" t="s">
         <v>22</v>
       </c>
       <c r="J28" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K28" t="s">
         <v>24</v>
@@ -2281,19 +2293,19 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" t="s">
         <v>86</v>
       </c>
-      <c r="B29" t="s">
-        <v>87</v>
-      </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s">
         <v>21</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F29" t="s">
         <v>21</v>
@@ -2302,13 +2314,13 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I29" t="s">
         <v>22</v>
       </c>
       <c r="J29" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K29" t="s">
         <v>24</v>
@@ -2337,19 +2349,19 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" t="s">
         <v>88</v>
       </c>
-      <c r="B30" t="s">
-        <v>89</v>
-      </c>
       <c r="C30" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
         <v>21</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" t="s">
         <v>21</v>
@@ -2358,13 +2370,13 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I30" t="s">
         <v>22</v>
       </c>
       <c r="J30" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K30" t="s">
         <v>24</v>
@@ -2393,13 +2405,13 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>89</v>
+      </c>
+      <c r="B31" t="s">
         <v>90</v>
       </c>
-      <c r="B31" t="s">
-        <v>91</v>
-      </c>
       <c r="C31" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D31" t="s">
         <v>21</v>
@@ -2420,7 +2432,7 @@
         <v>22</v>
       </c>
       <c r="J31" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K31" t="s">
         <v>24</v>
@@ -2449,13 +2461,13 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" t="s">
         <v>92</v>
       </c>
-      <c r="B32" t="s">
-        <v>93</v>
-      </c>
       <c r="C32" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D32" t="s">
         <v>21</v>
@@ -2476,7 +2488,7 @@
         <v>22</v>
       </c>
       <c r="J32" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K32" t="s">
         <v>24</v>
@@ -2505,19 +2517,19 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" t="s">
         <v>94</v>
       </c>
-      <c r="B33" t="s">
-        <v>95</v>
-      </c>
       <c r="C33" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D33" t="s">
         <v>21</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F33" t="s">
         <v>21</v>
@@ -2526,13 +2538,13 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I33" t="s">
         <v>22</v>
       </c>
       <c r="J33" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K33" t="s">
         <v>24</v>
@@ -2561,19 +2573,19 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" t="s">
         <v>96</v>
       </c>
-      <c r="B34" t="s">
-        <v>97</v>
-      </c>
       <c r="C34" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D34" t="s">
         <v>21</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F34" t="s">
         <v>21</v>
@@ -2582,13 +2594,13 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I34" t="s">
         <v>22</v>
       </c>
       <c r="J34" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K34" t="s">
         <v>24</v>
@@ -2617,19 +2629,19 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" t="s">
         <v>98</v>
       </c>
-      <c r="B35" t="s">
-        <v>99</v>
-      </c>
       <c r="C35" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D35" t="s">
         <v>21</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F35" t="s">
         <v>21</v>
@@ -2638,13 +2650,13 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I35" t="s">
         <v>22</v>
       </c>
       <c r="J35" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K35" t="s">
         <v>24</v>
@@ -2673,19 +2685,19 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" t="s">
         <v>100</v>
       </c>
-      <c r="B36" t="s">
-        <v>101</v>
-      </c>
       <c r="C36" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D36" t="s">
         <v>21</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" t="s">
         <v>21</v>
@@ -2694,13 +2706,13 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36" t="s">
         <v>22</v>
       </c>
       <c r="J36" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K36" t="s">
         <v>24</v>
@@ -2729,19 +2741,19 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" t="s">
         <v>102</v>
       </c>
-      <c r="B37" t="s">
-        <v>103</v>
-      </c>
       <c r="C37" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D37" t="s">
         <v>21</v>
       </c>
       <c r="E37">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F37" t="s">
         <v>21</v>
@@ -2750,13 +2762,13 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="I37" t="s">
         <v>22</v>
       </c>
       <c r="J37" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K37" t="s">
         <v>24</v>
@@ -2785,19 +2797,19 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" t="s">
         <v>104</v>
       </c>
-      <c r="B38" t="s">
-        <v>105</v>
-      </c>
       <c r="C38" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D38" t="s">
         <v>21</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" t="s">
         <v>21</v>
@@ -2806,13 +2818,13 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" t="s">
         <v>22</v>
       </c>
       <c r="J38" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K38" t="s">
         <v>24</v>
@@ -2841,13 +2853,13 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" t="s">
         <v>106</v>
       </c>
-      <c r="B39" t="s">
-        <v>107</v>
-      </c>
       <c r="C39" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D39" t="s">
         <v>21</v>
@@ -2868,7 +2880,7 @@
         <v>22</v>
       </c>
       <c r="J39" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K39" t="s">
         <v>24</v>
@@ -2897,57 +2909,225 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" t="s">
         <v>108</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40">
+        <v>9</v>
+      </c>
+      <c r="F40" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>9</v>
+      </c>
+      <c r="I40" t="s">
+        <v>22</v>
+      </c>
+      <c r="J40" t="s">
+        <v>56</v>
+      </c>
+      <c r="K40" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" t="s">
+        <v>25</v>
+      </c>
+      <c r="M40" t="s">
+        <v>26</v>
+      </c>
+      <c r="N40" t="s">
+        <v>21</v>
+      </c>
+      <c r="O40" t="s">
+        <v>21</v>
+      </c>
+      <c r="P40" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>21</v>
+      </c>
+      <c r="R40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" t="s">
         <v>109</v>
       </c>
-      <c r="C40" t="s">
-        <v>73</v>
-      </c>
-      <c r="D40" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40">
-        <v>1</v>
-      </c>
-      <c r="F40" t="s">
-        <v>21</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>1</v>
-      </c>
-      <c r="I40" t="s">
-        <v>22</v>
-      </c>
-      <c r="J40" t="s">
-        <v>54</v>
-      </c>
-      <c r="K40" t="s">
-        <v>24</v>
-      </c>
-      <c r="L40" t="s">
-        <v>25</v>
-      </c>
-      <c r="M40" t="s">
-        <v>26</v>
-      </c>
-      <c r="N40" t="s">
-        <v>21</v>
-      </c>
-      <c r="O40" t="s">
-        <v>21</v>
-      </c>
-      <c r="P40" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>21</v>
-      </c>
-      <c r="R40" t="s">
+      <c r="D41" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41">
+        <v>40</v>
+      </c>
+      <c r="F41" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>40</v>
+      </c>
+      <c r="I41" t="s">
+        <v>22</v>
+      </c>
+      <c r="J41" t="s">
+        <v>56</v>
+      </c>
+      <c r="K41" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" t="s">
+        <v>25</v>
+      </c>
+      <c r="M41" t="s">
+        <v>26</v>
+      </c>
+      <c r="N41" t="s">
+        <v>21</v>
+      </c>
+      <c r="O41" t="s">
+        <v>21</v>
+      </c>
+      <c r="P41" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>21</v>
+      </c>
+      <c r="R41" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>110</v>
+      </c>
+      <c r="B42" t="s">
+        <v>111</v>
+      </c>
+      <c r="C42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D42" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42">
+        <v>10</v>
+      </c>
+      <c r="F42" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>10</v>
+      </c>
+      <c r="I42" t="s">
+        <v>22</v>
+      </c>
+      <c r="J42" t="s">
+        <v>56</v>
+      </c>
+      <c r="K42" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" t="s">
+        <v>25</v>
+      </c>
+      <c r="M42" t="s">
+        <v>26</v>
+      </c>
+      <c r="N42" t="s">
+        <v>21</v>
+      </c>
+      <c r="O42" t="s">
+        <v>21</v>
+      </c>
+      <c r="P42" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>21</v>
+      </c>
+      <c r="R42" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>112</v>
+      </c>
+      <c r="B43" t="s">
+        <v>113</v>
+      </c>
+      <c r="C43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D43" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43">
+        <v>30</v>
+      </c>
+      <c r="F43" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>30</v>
+      </c>
+      <c r="I43" t="s">
+        <v>22</v>
+      </c>
+      <c r="J43" t="s">
+        <v>56</v>
+      </c>
+      <c r="K43" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" t="s">
+        <v>25</v>
+      </c>
+      <c r="M43" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" t="s">
+        <v>21</v>
+      </c>
+      <c r="O43" t="s">
+        <v>21</v>
+      </c>
+      <c r="P43" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>21</v>
+      </c>
+      <c r="R43" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03D10498-183F-4904-8D70-E439E8E04F48}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{56AD8CAA-47CB-4D02-B5CA-823792B05E6C}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="153">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -134,75 +134,78 @@
     <t>Deposito NQN</t>
   </si>
   <si>
+    <t>391-2882-051</t>
+  </si>
+  <si>
+    <t>CUERDA P30 Y P50</t>
+  </si>
+  <si>
+    <t>SOL - 2384</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>391-2884-021P</t>
+  </si>
+  <si>
+    <t>SELLO GOMA SQUARE GASKET 50-25</t>
+  </si>
+  <si>
     <t>C5OX-24-20F</t>
   </si>
   <si>
     <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
   </si>
   <si>
-    <t>SOL - 2384</t>
-  </si>
-  <si>
-    <t>2026-07</t>
-  </si>
-  <si>
-    <t>391-2882-051</t>
-  </si>
-  <si>
-    <t>CUERDA P30 Y P50</t>
-  </si>
-  <si>
-    <t>391-2884-021P</t>
-  </si>
-  <si>
-    <t>SELLO GOMA SQUARE GASKET 50-25</t>
-  </si>
-  <si>
-    <t>RD200EZ</t>
-  </si>
-  <si>
-    <t>ACOPLE TIPO CAMLOCK 2" EZ CUERPO X HEMBRA AISI 316 DIXON</t>
-  </si>
-  <si>
-    <t>SOL - 2489</t>
+    <t>MA-310</t>
+  </si>
+  <si>
+    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
+  </si>
+  <si>
+    <t>SOL - 2493</t>
   </si>
   <si>
     <t>2026-08</t>
   </si>
   <si>
-    <t>MA-310</t>
-  </si>
-  <si>
-    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
-  </si>
-  <si>
-    <t>SOL - 2493</t>
-  </si>
-  <si>
     <t>FILT-D-AB-2</t>
   </si>
   <si>
     <t>FILTRO AIRE RESP DESECANTE</t>
   </si>
   <si>
+    <t>SA-632-7800A</t>
+  </si>
+  <si>
+    <t>BOMBA PRECARGA SAUER SERIE 90-75 - 14cc</t>
+  </si>
+  <si>
+    <t>SOL - 2537</t>
+  </si>
+  <si>
+    <t>01049</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>Deposito Nqn 2</t>
+  </si>
+  <si>
+    <t>SA-WLA632-3306F</t>
+  </si>
+  <si>
+    <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
+  </si>
+  <si>
     <t>313-1135-194</t>
   </si>
   <si>
     <t>EJE POSTIZO P50 Z14</t>
   </si>
   <si>
-    <t>SOL - 2537</t>
-  </si>
-  <si>
-    <t>01049</t>
-  </si>
-  <si>
-    <t>2026-09</t>
-  </si>
-  <si>
-    <t>Deposito Nqn 2</t>
-  </si>
-  <si>
     <t>313-2825-000</t>
   </si>
   <si>
@@ -221,16 +224,61 @@
     <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
   </si>
   <si>
-    <t>SA-632-7800A</t>
-  </si>
-  <si>
-    <t>BOMBA PRECARGA SAUER SERIE 90-75 - 14cc</t>
-  </si>
-  <si>
-    <t>SA-WLA632-3306F</t>
-  </si>
-  <si>
-    <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
+    <t>SA-634-1100C</t>
+  </si>
+  <si>
+    <t>BLOCK CILINDROS SAUER SERIE 90-130</t>
+  </si>
+  <si>
+    <t>SOL - 2555</t>
+  </si>
+  <si>
+    <t>SA-634-5256</t>
+  </si>
+  <si>
+    <t>CANASTO PORTA RODILLO SAUER 90-130 SET</t>
+  </si>
+  <si>
+    <t>SA-634-5257A</t>
+  </si>
+  <si>
+    <t>CUNA SAUER SERIE 90-130 (UNITARIO) MN - 148.7x29.8x51</t>
+  </si>
+  <si>
+    <t>SA-634-2200</t>
+  </si>
+  <si>
+    <t>PISTON SAUER SERIE 90-130</t>
+  </si>
+  <si>
+    <t>SA-640-5256</t>
+  </si>
+  <si>
+    <t>CANASTO PORTA RODILLO SAUER SERIE 90-100</t>
+  </si>
+  <si>
+    <t>SA-640-5251</t>
+  </si>
+  <si>
+    <t>CUNA SAUER GRUESA SERIE 90-100 MV</t>
+  </si>
+  <si>
+    <t>SA-632-1100C</t>
+  </si>
+  <si>
+    <t>BLOCK CILINDROS SAUER SERIE 90-75</t>
+  </si>
+  <si>
+    <t>SA-639-5256</t>
+  </si>
+  <si>
+    <t>CANASTO PORTA RODILLO SAUER SERIE 90-75</t>
+  </si>
+  <si>
+    <t>SA-632-2100C</t>
+  </si>
+  <si>
+    <t>PISTON SAUER SERIE 90-75</t>
   </si>
   <si>
     <t>SA-631-3306F</t>
@@ -239,9 +287,6 @@
     <t>KIT SELLOS BOMBA SAUER 90-55</t>
   </si>
   <si>
-    <t>SOL - 2555</t>
-  </si>
-  <si>
     <t>SA-638-4701</t>
   </si>
   <si>
@@ -302,60 +347,6 @@
     <t xml:space="preserve">EJE DANFOSS Z=14 MF90-055 12/24 (S1) </t>
   </si>
   <si>
-    <t>SA-634-1100C</t>
-  </si>
-  <si>
-    <t>BLOCK CILINDROS SAUER SERIE 90-130</t>
-  </si>
-  <si>
-    <t>SA-634-5256</t>
-  </si>
-  <si>
-    <t>CANASTO PORTA RODILLO SAUER 90-130 SET</t>
-  </si>
-  <si>
-    <t>SA-634-5257A</t>
-  </si>
-  <si>
-    <t>CUNA SAUER SERIE 90-130 (UNITARIO) MN - 148.7x29.8x51</t>
-  </si>
-  <si>
-    <t>SA-634-2200</t>
-  </si>
-  <si>
-    <t>PISTON SAUER SERIE 90-130</t>
-  </si>
-  <si>
-    <t>SA-640-5256</t>
-  </si>
-  <si>
-    <t>CANASTO PORTA RODILLO SAUER SERIE 90-100</t>
-  </si>
-  <si>
-    <t>SA-640-5251</t>
-  </si>
-  <si>
-    <t>CUNA SAUER GRUESA SERIE 90-100 MV</t>
-  </si>
-  <si>
-    <t>SA-632-1100C</t>
-  </si>
-  <si>
-    <t>BLOCK CILINDROS SAUER SERIE 90-75</t>
-  </si>
-  <si>
-    <t>SA-639-5256</t>
-  </si>
-  <si>
-    <t>CANASTO PORTA RODILLO SAUER SERIE 90-75</t>
-  </si>
-  <si>
-    <t>SA-632-2100C</t>
-  </si>
-  <si>
-    <t>PISTON SAUER SERIE 90-75</t>
-  </si>
-  <si>
     <t>SOL - 2564</t>
   </si>
   <si>
@@ -369,6 +360,132 @@
   </si>
   <si>
     <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 7"</t>
+  </si>
+  <si>
+    <t>FT 221/3-100</t>
+  </si>
+  <si>
+    <t>VALVULA ESFERICA DE 3 VIAS, ALTA PRESION 1"</t>
+  </si>
+  <si>
+    <t>SOL - 2580</t>
+  </si>
+  <si>
+    <t>01076</t>
+  </si>
+  <si>
+    <t>FT 221/3-112</t>
+  </si>
+  <si>
+    <t>VALVULA ESFERICA DE 3 VIAS, ALTA PRESION 1.1/2"</t>
+  </si>
+  <si>
+    <t>FT 221/3-114</t>
+  </si>
+  <si>
+    <t>VALVULA ESFERICA DE 3 VIAS, ALTA PRESION 1.1/4"</t>
+  </si>
+  <si>
+    <t>FT 221/3-12</t>
+  </si>
+  <si>
+    <t>VALVULA ESFERICA DE 3 VIAS, ALTA PRESION 1/2"</t>
+  </si>
+  <si>
+    <t>FT 221/3-34</t>
+  </si>
+  <si>
+    <t>VALVULA ESFERICA DE 3 VIAS. ALTA PRESION 3/4"</t>
+  </si>
+  <si>
+    <t>FT 251/2-100</t>
+  </si>
+  <si>
+    <t>VÁLVULA AGUJA BIDIRECCIONAL ACERO 1" BSP MANOPLA ALUMINIO</t>
+  </si>
+  <si>
+    <t>FT 251/2-12</t>
+  </si>
+  <si>
+    <t>VÁLVULA AGUJA BIDIRECCIONAL ACERO 1/2" BSP MANOPLA ALUMINIO</t>
+  </si>
+  <si>
+    <t>FT 251/2-14</t>
+  </si>
+  <si>
+    <t>VALVULA AGUJA BIDIRECCIONAL ACERO 1/4" BSP MANOPLA ALUMINIO</t>
+  </si>
+  <si>
+    <t>FT 251/2-34</t>
+  </si>
+  <si>
+    <t>VALVULA AGUJA BIDIRECCIONAL ACERO 3/4" BSP MANOPLA ALUMINIO</t>
+  </si>
+  <si>
+    <t>FT 257/5-12</t>
+  </si>
+  <si>
+    <t>VALVULA AGUJA UNIDIRECCIONAL 1/2" 400 BAR</t>
+  </si>
+  <si>
+    <t>FT 257/5-14</t>
+  </si>
+  <si>
+    <t>VALVULA AGUJA UNIDIRECCIONAL 1/4" - 350 BAR 15 LT</t>
+  </si>
+  <si>
+    <t>FT 257/5-38</t>
+  </si>
+  <si>
+    <t>VALVULA AGUJA UNIDIRECCIONAL 3/8" 400 BAR</t>
+  </si>
+  <si>
+    <t>FT 257/6-100</t>
+  </si>
+  <si>
+    <t>VALVULA DE RETENCION EN LINEA RECTA 1" 160LPM - 350 BAR</t>
+  </si>
+  <si>
+    <t>FT 257/6-112</t>
+  </si>
+  <si>
+    <t>VALVULA DE RETENCION EN LINEA RECTA 1.1/2" 302LPM - 350 BAR</t>
+  </si>
+  <si>
+    <t>FT 257/6-114</t>
+  </si>
+  <si>
+    <t>VALVULA DE RETENCION EN LINEA RECTA 1.1/4" 210LPM - 350 BAR</t>
+  </si>
+  <si>
+    <t>FT 257/6-12</t>
+  </si>
+  <si>
+    <t>VALVULA DE RETENCION EN LINEA RECTA 1/2" 70LPM - 500 BAR</t>
+  </si>
+  <si>
+    <t>FT 257/6-14</t>
+  </si>
+  <si>
+    <t>VALVULA DE RETENCION EN LINEA RECTA 1/4" 30LPM - 500 BAR</t>
+  </si>
+  <si>
+    <t>FT 257/6-38</t>
+  </si>
+  <si>
+    <t>VALVULA DE RETENCION EN LINEA RECTA 3/8" 45LPM - 500 BAR</t>
+  </si>
+  <si>
+    <t>SEAL KIT HMA280</t>
+  </si>
+  <si>
+    <t>SEAL KIT MOTOR LINDE HMA280 ALTERNATIVO</t>
+  </si>
+  <si>
+    <t>SOL - 2581</t>
+  </si>
+  <si>
+    <t>01077</t>
   </si>
 </sst>
 </file>
@@ -720,7 +837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R43"/>
+  <dimension ref="A1:R61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -793,7 +910,7 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
@@ -802,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
         <v>22</v>
@@ -849,7 +966,7 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
@@ -858,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
@@ -961,7 +1078,7 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
@@ -970,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I5" t="s">
         <v>22</v>
@@ -1017,7 +1134,7 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
@@ -1026,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I6" t="s">
         <v>22</v>
@@ -1129,7 +1246,7 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -1138,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
@@ -1185,7 +1302,7 @@
         <v>21</v>
       </c>
       <c r="E9">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -1194,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
@@ -1241,7 +1358,7 @@
         <v>21</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -1250,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I10" t="s">
         <v>22</v>
@@ -1297,7 +1414,7 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -1347,13 +1464,13 @@
         <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
         <v>21</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1362,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
@@ -1397,19 +1514,19 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
         <v>50</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>51</v>
       </c>
-      <c r="C13" t="s">
-        <v>49</v>
-      </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="E13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1418,22 +1535,22 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
       </c>
       <c r="J13" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="K13" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L13" t="s">
         <v>25</v>
       </c>
       <c r="M13" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="N13" t="s">
         <v>21</v>
@@ -1453,19 +1570,19 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" t="s">
         <v>52</v>
       </c>
-      <c r="B14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" t="s">
-        <v>55</v>
-      </c>
       <c r="E14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1474,13 +1591,13 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
       </c>
       <c r="J14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K14" t="s">
         <v>33</v>
@@ -1489,7 +1606,7 @@
         <v>25</v>
       </c>
       <c r="M14" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N14" t="s">
         <v>21</v>
@@ -1509,19 +1626,19 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" t="s">
         <v>58</v>
       </c>
-      <c r="B15" t="s">
-        <v>59</v>
-      </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1530,13 +1647,13 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
       </c>
       <c r="J15" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K15" t="s">
         <v>33</v>
@@ -1545,7 +1662,7 @@
         <v>25</v>
       </c>
       <c r="M15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N15" t="s">
         <v>21</v>
@@ -1565,16 +1682,16 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" t="s">
         <v>60</v>
       </c>
-      <c r="B16" t="s">
-        <v>61</v>
-      </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -1592,7 +1709,7 @@
         <v>22</v>
       </c>
       <c r="J16" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K16" t="s">
         <v>33</v>
@@ -1601,7 +1718,7 @@
         <v>25</v>
       </c>
       <c r="M16" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N16" t="s">
         <v>21</v>
@@ -1621,19 +1738,19 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" t="s">
         <v>62</v>
       </c>
-      <c r="B17" t="s">
-        <v>63</v>
-      </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E17">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
         <v>21</v>
@@ -1642,13 +1759,13 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
       </c>
       <c r="J17" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K17" t="s">
         <v>33</v>
@@ -1657,7 +1774,7 @@
         <v>25</v>
       </c>
       <c r="M17" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N17" t="s">
         <v>21</v>
@@ -1677,19 +1794,19 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E18">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="F18" t="s">
         <v>21</v>
@@ -1698,13 +1815,13 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="I18" t="s">
         <v>22</v>
       </c>
       <c r="J18" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K18" t="s">
         <v>33</v>
@@ -1713,7 +1830,7 @@
         <v>25</v>
       </c>
       <c r="M18" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N18" t="s">
         <v>21</v>
@@ -1733,19 +1850,19 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F19" t="s">
         <v>21</v>
@@ -1754,13 +1871,13 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
       </c>
       <c r="J19" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K19" t="s">
         <v>33</v>
@@ -1769,7 +1886,7 @@
         <v>25</v>
       </c>
       <c r="M19" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N19" t="s">
         <v>21</v>
@@ -1789,19 +1906,19 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" t="s">
         <v>66</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="C20" t="s">
-        <v>54</v>
-      </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -1810,22 +1927,22 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
       </c>
       <c r="J20" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K20" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L20" t="s">
         <v>25</v>
       </c>
       <c r="M20" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="N20" t="s">
         <v>21</v>
@@ -1851,13 +1968,13 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
         <v>21</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" t="s">
         <v>21</v>
@@ -1866,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
       </c>
       <c r="J21" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K21" t="s">
         <v>24</v>
@@ -1901,19 +2018,19 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" t="s">
         <v>71</v>
       </c>
-      <c r="B22" t="s">
-        <v>72</v>
-      </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
         <v>21</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" t="s">
         <v>21</v>
@@ -1922,13 +2039,13 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22" t="s">
         <v>22</v>
       </c>
       <c r="J22" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K22" t="s">
         <v>24</v>
@@ -1957,19 +2074,19 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" t="s">
         <v>73</v>
       </c>
-      <c r="B23" t="s">
-        <v>74</v>
-      </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
         <v>21</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
         <v>21</v>
@@ -1978,13 +2095,13 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I23" t="s">
         <v>22</v>
       </c>
       <c r="J23" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K23" t="s">
         <v>24</v>
@@ -2013,13 +2130,13 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" t="s">
         <v>75</v>
       </c>
-      <c r="B24" t="s">
-        <v>76</v>
-      </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
         <v>21</v>
@@ -2040,7 +2157,7 @@
         <v>22</v>
       </c>
       <c r="J24" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K24" t="s">
         <v>24</v>
@@ -2069,19 +2186,19 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" t="s">
         <v>77</v>
       </c>
-      <c r="B25" t="s">
-        <v>78</v>
-      </c>
       <c r="C25" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
         <v>21</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="s">
         <v>21</v>
@@ -2090,13 +2207,13 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" t="s">
         <v>22</v>
       </c>
       <c r="J25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K25" t="s">
         <v>24</v>
@@ -2125,19 +2242,19 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s">
         <v>79</v>
       </c>
-      <c r="B26" t="s">
-        <v>80</v>
-      </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
         <v>21</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" t="s">
         <v>21</v>
@@ -2146,13 +2263,13 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" t="s">
         <v>22</v>
       </c>
       <c r="J26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K26" t="s">
         <v>24</v>
@@ -2181,19 +2298,19 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" t="s">
         <v>81</v>
       </c>
-      <c r="B27" t="s">
-        <v>82</v>
-      </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
         <v>21</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" t="s">
         <v>21</v>
@@ -2202,13 +2319,13 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27" t="s">
         <v>22</v>
       </c>
       <c r="J27" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K27" t="s">
         <v>24</v>
@@ -2237,19 +2354,19 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" t="s">
         <v>83</v>
       </c>
-      <c r="B28" t="s">
-        <v>84</v>
-      </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
         <v>21</v>
       </c>
       <c r="E28">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
         <v>21</v>
@@ -2258,13 +2375,13 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I28" t="s">
         <v>22</v>
       </c>
       <c r="J28" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K28" t="s">
         <v>24</v>
@@ -2293,13 +2410,13 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s">
         <v>85</v>
       </c>
-      <c r="B29" t="s">
-        <v>86</v>
-      </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
         <v>21</v>
@@ -2320,7 +2437,7 @@
         <v>22</v>
       </c>
       <c r="J29" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K29" t="s">
         <v>24</v>
@@ -2349,19 +2466,19 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" t="s">
         <v>87</v>
       </c>
-      <c r="B30" t="s">
-        <v>88</v>
-      </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D30" t="s">
         <v>21</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30" t="s">
         <v>21</v>
@@ -2370,13 +2487,13 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I30" t="s">
         <v>22</v>
       </c>
       <c r="J30" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K30" t="s">
         <v>24</v>
@@ -2405,13 +2522,13 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" t="s">
         <v>89</v>
       </c>
-      <c r="B31" t="s">
-        <v>90</v>
-      </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D31" t="s">
         <v>21</v>
@@ -2432,7 +2549,7 @@
         <v>22</v>
       </c>
       <c r="J31" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K31" t="s">
         <v>24</v>
@@ -2461,13 +2578,13 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" t="s">
         <v>91</v>
       </c>
-      <c r="B32" t="s">
-        <v>92</v>
-      </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s">
         <v>21</v>
@@ -2488,7 +2605,7 @@
         <v>22</v>
       </c>
       <c r="J32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K32" t="s">
         <v>24</v>
@@ -2517,19 +2634,19 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" t="s">
         <v>93</v>
       </c>
-      <c r="B33" t="s">
-        <v>94</v>
-      </c>
       <c r="C33" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D33" t="s">
         <v>21</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33" t="s">
         <v>21</v>
@@ -2538,13 +2655,13 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I33" t="s">
         <v>22</v>
       </c>
       <c r="J33" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K33" t="s">
         <v>24</v>
@@ -2573,19 +2690,19 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" t="s">
         <v>95</v>
       </c>
-      <c r="B34" t="s">
-        <v>96</v>
-      </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D34" t="s">
         <v>21</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" t="s">
         <v>21</v>
@@ -2594,13 +2711,13 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I34" t="s">
         <v>22</v>
       </c>
       <c r="J34" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K34" t="s">
         <v>24</v>
@@ -2629,19 +2746,19 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" t="s">
         <v>97</v>
       </c>
-      <c r="B35" t="s">
-        <v>98</v>
-      </c>
       <c r="C35" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D35" t="s">
         <v>21</v>
       </c>
       <c r="E35">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F35" t="s">
         <v>21</v>
@@ -2650,13 +2767,13 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I35" t="s">
         <v>22</v>
       </c>
       <c r="J35" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K35" t="s">
         <v>24</v>
@@ -2685,19 +2802,19 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" t="s">
         <v>99</v>
       </c>
-      <c r="B36" t="s">
-        <v>100</v>
-      </c>
       <c r="C36" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D36" t="s">
         <v>21</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F36" t="s">
         <v>21</v>
@@ -2706,13 +2823,13 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I36" t="s">
         <v>22</v>
       </c>
       <c r="J36" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K36" t="s">
         <v>24</v>
@@ -2741,19 +2858,19 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" t="s">
         <v>101</v>
       </c>
-      <c r="B37" t="s">
-        <v>102</v>
-      </c>
       <c r="C37" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D37" t="s">
         <v>21</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" t="s">
         <v>21</v>
@@ -2762,13 +2879,13 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" t="s">
         <v>22</v>
       </c>
       <c r="J37" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K37" t="s">
         <v>24</v>
@@ -2797,19 +2914,19 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" t="s">
         <v>103</v>
       </c>
-      <c r="B38" t="s">
-        <v>104</v>
-      </c>
       <c r="C38" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D38" t="s">
         <v>21</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" t="s">
         <v>21</v>
@@ -2818,13 +2935,13 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I38" t="s">
         <v>22</v>
       </c>
       <c r="J38" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K38" t="s">
         <v>24</v>
@@ -2853,19 +2970,19 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>104</v>
+      </c>
+      <c r="B39" t="s">
         <v>105</v>
       </c>
-      <c r="B39" t="s">
-        <v>106</v>
-      </c>
       <c r="C39" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D39" t="s">
         <v>21</v>
       </c>
       <c r="E39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F39" t="s">
         <v>21</v>
@@ -2874,13 +2991,13 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I39" t="s">
         <v>22</v>
       </c>
       <c r="J39" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K39" t="s">
         <v>24</v>
@@ -2909,19 +3026,19 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="C40" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="D40" t="s">
         <v>21</v>
       </c>
       <c r="E40">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F40" t="s">
         <v>21</v>
@@ -2930,13 +3047,13 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="I40" t="s">
         <v>22</v>
       </c>
       <c r="J40" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K40" t="s">
         <v>24</v>
@@ -2965,19 +3082,19 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="C41" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D41" t="s">
         <v>21</v>
       </c>
       <c r="E41">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F41" t="s">
         <v>21</v>
@@ -2986,13 +3103,13 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I41" t="s">
         <v>22</v>
       </c>
       <c r="J41" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K41" t="s">
         <v>24</v>
@@ -3021,19 +3138,19 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" t="s">
         <v>110</v>
       </c>
-      <c r="B42" t="s">
-        <v>111</v>
-      </c>
       <c r="C42" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D42" t="s">
         <v>21</v>
       </c>
       <c r="E42">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F42" t="s">
         <v>21</v>
@@ -3042,13 +3159,13 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I42" t="s">
         <v>22</v>
       </c>
       <c r="J42" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K42" t="s">
         <v>24</v>
@@ -3077,19 +3194,19 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" t="s">
         <v>112</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>113</v>
       </c>
-      <c r="C43" t="s">
-        <v>109</v>
-      </c>
       <c r="D43" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="E43">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F43" t="s">
         <v>21</v>
@@ -3098,22 +3215,22 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="I43" t="s">
         <v>22</v>
       </c>
       <c r="J43" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K43" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L43" t="s">
         <v>25</v>
       </c>
       <c r="M43" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="N43" t="s">
         <v>21</v>
@@ -3128,6 +3245,1014 @@
         <v>21</v>
       </c>
       <c r="R43" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" t="s">
+        <v>116</v>
+      </c>
+      <c r="C44" t="s">
+        <v>113</v>
+      </c>
+      <c r="D44" t="s">
+        <v>114</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44" t="s">
+        <v>22</v>
+      </c>
+      <c r="J44" t="s">
+        <v>53</v>
+      </c>
+      <c r="K44" t="s">
+        <v>33</v>
+      </c>
+      <c r="L44" t="s">
+        <v>25</v>
+      </c>
+      <c r="M44" t="s">
+        <v>34</v>
+      </c>
+      <c r="N44" t="s">
+        <v>21</v>
+      </c>
+      <c r="O44" t="s">
+        <v>21</v>
+      </c>
+      <c r="P44" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>21</v>
+      </c>
+      <c r="R44" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>117</v>
+      </c>
+      <c r="B45" t="s">
+        <v>118</v>
+      </c>
+      <c r="C45" t="s">
+        <v>113</v>
+      </c>
+      <c r="D45" t="s">
+        <v>114</v>
+      </c>
+      <c r="E45">
+        <v>2</v>
+      </c>
+      <c r="F45" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>2</v>
+      </c>
+      <c r="I45" t="s">
+        <v>22</v>
+      </c>
+      <c r="J45" t="s">
+        <v>53</v>
+      </c>
+      <c r="K45" t="s">
+        <v>33</v>
+      </c>
+      <c r="L45" t="s">
+        <v>25</v>
+      </c>
+      <c r="M45" t="s">
+        <v>34</v>
+      </c>
+      <c r="N45" t="s">
+        <v>21</v>
+      </c>
+      <c r="O45" t="s">
+        <v>21</v>
+      </c>
+      <c r="P45" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>21</v>
+      </c>
+      <c r="R45" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>119</v>
+      </c>
+      <c r="B46" t="s">
+        <v>120</v>
+      </c>
+      <c r="C46" t="s">
+        <v>113</v>
+      </c>
+      <c r="D46" t="s">
+        <v>114</v>
+      </c>
+      <c r="E46">
+        <v>4</v>
+      </c>
+      <c r="F46" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>4</v>
+      </c>
+      <c r="I46" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" t="s">
+        <v>53</v>
+      </c>
+      <c r="K46" t="s">
+        <v>33</v>
+      </c>
+      <c r="L46" t="s">
+        <v>25</v>
+      </c>
+      <c r="M46" t="s">
+        <v>34</v>
+      </c>
+      <c r="N46" t="s">
+        <v>21</v>
+      </c>
+      <c r="O46" t="s">
+        <v>21</v>
+      </c>
+      <c r="P46" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>21</v>
+      </c>
+      <c r="R46" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>121</v>
+      </c>
+      <c r="B47" t="s">
+        <v>122</v>
+      </c>
+      <c r="C47" t="s">
+        <v>113</v>
+      </c>
+      <c r="D47" t="s">
+        <v>114</v>
+      </c>
+      <c r="E47">
+        <v>3</v>
+      </c>
+      <c r="F47" t="s">
+        <v>21</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>3</v>
+      </c>
+      <c r="I47" t="s">
+        <v>22</v>
+      </c>
+      <c r="J47" t="s">
+        <v>53</v>
+      </c>
+      <c r="K47" t="s">
+        <v>33</v>
+      </c>
+      <c r="L47" t="s">
+        <v>25</v>
+      </c>
+      <c r="M47" t="s">
+        <v>34</v>
+      </c>
+      <c r="N47" t="s">
+        <v>21</v>
+      </c>
+      <c r="O47" t="s">
+        <v>21</v>
+      </c>
+      <c r="P47" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>21</v>
+      </c>
+      <c r="R47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>123</v>
+      </c>
+      <c r="B48" t="s">
+        <v>124</v>
+      </c>
+      <c r="C48" t="s">
+        <v>113</v>
+      </c>
+      <c r="D48" t="s">
+        <v>114</v>
+      </c>
+      <c r="E48">
+        <v>4</v>
+      </c>
+      <c r="F48" t="s">
+        <v>21</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>4</v>
+      </c>
+      <c r="I48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J48" t="s">
+        <v>53</v>
+      </c>
+      <c r="K48" t="s">
+        <v>33</v>
+      </c>
+      <c r="L48" t="s">
+        <v>25</v>
+      </c>
+      <c r="M48" t="s">
+        <v>34</v>
+      </c>
+      <c r="N48" t="s">
+        <v>21</v>
+      </c>
+      <c r="O48" t="s">
+        <v>21</v>
+      </c>
+      <c r="P48" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>21</v>
+      </c>
+      <c r="R48" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>125</v>
+      </c>
+      <c r="B49" t="s">
+        <v>126</v>
+      </c>
+      <c r="C49" t="s">
+        <v>113</v>
+      </c>
+      <c r="D49" t="s">
+        <v>114</v>
+      </c>
+      <c r="E49">
+        <v>6</v>
+      </c>
+      <c r="F49" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>6</v>
+      </c>
+      <c r="I49" t="s">
+        <v>22</v>
+      </c>
+      <c r="J49" t="s">
+        <v>53</v>
+      </c>
+      <c r="K49" t="s">
+        <v>33</v>
+      </c>
+      <c r="L49" t="s">
+        <v>25</v>
+      </c>
+      <c r="M49" t="s">
+        <v>34</v>
+      </c>
+      <c r="N49" t="s">
+        <v>21</v>
+      </c>
+      <c r="O49" t="s">
+        <v>21</v>
+      </c>
+      <c r="P49" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>21</v>
+      </c>
+      <c r="R49" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" t="s">
+        <v>128</v>
+      </c>
+      <c r="C50" t="s">
+        <v>113</v>
+      </c>
+      <c r="D50" t="s">
+        <v>114</v>
+      </c>
+      <c r="E50">
+        <v>2</v>
+      </c>
+      <c r="F50" t="s">
+        <v>21</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>2</v>
+      </c>
+      <c r="I50" t="s">
+        <v>22</v>
+      </c>
+      <c r="J50" t="s">
+        <v>53</v>
+      </c>
+      <c r="K50" t="s">
+        <v>33</v>
+      </c>
+      <c r="L50" t="s">
+        <v>25</v>
+      </c>
+      <c r="M50" t="s">
+        <v>34</v>
+      </c>
+      <c r="N50" t="s">
+        <v>21</v>
+      </c>
+      <c r="O50" t="s">
+        <v>21</v>
+      </c>
+      <c r="P50" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>21</v>
+      </c>
+      <c r="R50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>129</v>
+      </c>
+      <c r="B51" t="s">
+        <v>130</v>
+      </c>
+      <c r="C51" t="s">
+        <v>113</v>
+      </c>
+      <c r="D51" t="s">
+        <v>114</v>
+      </c>
+      <c r="E51">
+        <v>4</v>
+      </c>
+      <c r="F51" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>4</v>
+      </c>
+      <c r="I51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J51" t="s">
+        <v>53</v>
+      </c>
+      <c r="K51" t="s">
+        <v>33</v>
+      </c>
+      <c r="L51" t="s">
+        <v>25</v>
+      </c>
+      <c r="M51" t="s">
+        <v>34</v>
+      </c>
+      <c r="N51" t="s">
+        <v>21</v>
+      </c>
+      <c r="O51" t="s">
+        <v>21</v>
+      </c>
+      <c r="P51" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>21</v>
+      </c>
+      <c r="R51" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>131</v>
+      </c>
+      <c r="B52" t="s">
+        <v>132</v>
+      </c>
+      <c r="C52" t="s">
+        <v>113</v>
+      </c>
+      <c r="D52" t="s">
+        <v>114</v>
+      </c>
+      <c r="E52">
+        <v>3</v>
+      </c>
+      <c r="F52" t="s">
+        <v>21</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>3</v>
+      </c>
+      <c r="I52" t="s">
+        <v>22</v>
+      </c>
+      <c r="J52" t="s">
+        <v>53</v>
+      </c>
+      <c r="K52" t="s">
+        <v>33</v>
+      </c>
+      <c r="L52" t="s">
+        <v>25</v>
+      </c>
+      <c r="M52" t="s">
+        <v>34</v>
+      </c>
+      <c r="N52" t="s">
+        <v>21</v>
+      </c>
+      <c r="O52" t="s">
+        <v>21</v>
+      </c>
+      <c r="P52" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>21</v>
+      </c>
+      <c r="R52" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>133</v>
+      </c>
+      <c r="B53" t="s">
+        <v>134</v>
+      </c>
+      <c r="C53" t="s">
+        <v>113</v>
+      </c>
+      <c r="D53" t="s">
+        <v>114</v>
+      </c>
+      <c r="E53">
+        <v>4</v>
+      </c>
+      <c r="F53" t="s">
+        <v>21</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>4</v>
+      </c>
+      <c r="I53" t="s">
+        <v>22</v>
+      </c>
+      <c r="J53" t="s">
+        <v>53</v>
+      </c>
+      <c r="K53" t="s">
+        <v>33</v>
+      </c>
+      <c r="L53" t="s">
+        <v>25</v>
+      </c>
+      <c r="M53" t="s">
+        <v>34</v>
+      </c>
+      <c r="N53" t="s">
+        <v>21</v>
+      </c>
+      <c r="O53" t="s">
+        <v>21</v>
+      </c>
+      <c r="P53" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>21</v>
+      </c>
+      <c r="R53" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>135</v>
+      </c>
+      <c r="B54" t="s">
+        <v>136</v>
+      </c>
+      <c r="C54" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" t="s">
+        <v>114</v>
+      </c>
+      <c r="E54">
+        <v>2</v>
+      </c>
+      <c r="F54" t="s">
+        <v>21</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>2</v>
+      </c>
+      <c r="I54" t="s">
+        <v>22</v>
+      </c>
+      <c r="J54" t="s">
+        <v>53</v>
+      </c>
+      <c r="K54" t="s">
+        <v>33</v>
+      </c>
+      <c r="L54" t="s">
+        <v>25</v>
+      </c>
+      <c r="M54" t="s">
+        <v>34</v>
+      </c>
+      <c r="N54" t="s">
+        <v>21</v>
+      </c>
+      <c r="O54" t="s">
+        <v>21</v>
+      </c>
+      <c r="P54" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>21</v>
+      </c>
+      <c r="R54" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>137</v>
+      </c>
+      <c r="B55" t="s">
+        <v>138</v>
+      </c>
+      <c r="C55" t="s">
+        <v>113</v>
+      </c>
+      <c r="D55" t="s">
+        <v>114</v>
+      </c>
+      <c r="E55">
+        <v>4</v>
+      </c>
+      <c r="F55" t="s">
+        <v>21</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>4</v>
+      </c>
+      <c r="I55" t="s">
+        <v>22</v>
+      </c>
+      <c r="J55" t="s">
+        <v>53</v>
+      </c>
+      <c r="K55" t="s">
+        <v>33</v>
+      </c>
+      <c r="L55" t="s">
+        <v>25</v>
+      </c>
+      <c r="M55" t="s">
+        <v>34</v>
+      </c>
+      <c r="N55" t="s">
+        <v>21</v>
+      </c>
+      <c r="O55" t="s">
+        <v>21</v>
+      </c>
+      <c r="P55" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>21</v>
+      </c>
+      <c r="R55" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>139</v>
+      </c>
+      <c r="B56" t="s">
+        <v>140</v>
+      </c>
+      <c r="C56" t="s">
+        <v>113</v>
+      </c>
+      <c r="D56" t="s">
+        <v>114</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="F56" t="s">
+        <v>21</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>1</v>
+      </c>
+      <c r="I56" t="s">
+        <v>22</v>
+      </c>
+      <c r="J56" t="s">
+        <v>53</v>
+      </c>
+      <c r="K56" t="s">
+        <v>33</v>
+      </c>
+      <c r="L56" t="s">
+        <v>25</v>
+      </c>
+      <c r="M56" t="s">
+        <v>34</v>
+      </c>
+      <c r="N56" t="s">
+        <v>21</v>
+      </c>
+      <c r="O56" t="s">
+        <v>21</v>
+      </c>
+      <c r="P56" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>21</v>
+      </c>
+      <c r="R56" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>141</v>
+      </c>
+      <c r="B57" t="s">
+        <v>142</v>
+      </c>
+      <c r="C57" t="s">
+        <v>113</v>
+      </c>
+      <c r="D57" t="s">
+        <v>114</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="F57" t="s">
+        <v>21</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57" t="s">
+        <v>22</v>
+      </c>
+      <c r="J57" t="s">
+        <v>53</v>
+      </c>
+      <c r="K57" t="s">
+        <v>33</v>
+      </c>
+      <c r="L57" t="s">
+        <v>25</v>
+      </c>
+      <c r="M57" t="s">
+        <v>34</v>
+      </c>
+      <c r="N57" t="s">
+        <v>21</v>
+      </c>
+      <c r="O57" t="s">
+        <v>21</v>
+      </c>
+      <c r="P57" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>21</v>
+      </c>
+      <c r="R57" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>143</v>
+      </c>
+      <c r="B58" t="s">
+        <v>144</v>
+      </c>
+      <c r="C58" t="s">
+        <v>113</v>
+      </c>
+      <c r="D58" t="s">
+        <v>114</v>
+      </c>
+      <c r="E58">
+        <v>10</v>
+      </c>
+      <c r="F58" t="s">
+        <v>21</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>10</v>
+      </c>
+      <c r="I58" t="s">
+        <v>22</v>
+      </c>
+      <c r="J58" t="s">
+        <v>53</v>
+      </c>
+      <c r="K58" t="s">
+        <v>33</v>
+      </c>
+      <c r="L58" t="s">
+        <v>25</v>
+      </c>
+      <c r="M58" t="s">
+        <v>34</v>
+      </c>
+      <c r="N58" t="s">
+        <v>21</v>
+      </c>
+      <c r="O58" t="s">
+        <v>21</v>
+      </c>
+      <c r="P58" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>21</v>
+      </c>
+      <c r="R58" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>145</v>
+      </c>
+      <c r="B59" t="s">
+        <v>146</v>
+      </c>
+      <c r="C59" t="s">
+        <v>113</v>
+      </c>
+      <c r="D59" t="s">
+        <v>114</v>
+      </c>
+      <c r="E59">
+        <v>15</v>
+      </c>
+      <c r="F59" t="s">
+        <v>21</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>15</v>
+      </c>
+      <c r="I59" t="s">
+        <v>22</v>
+      </c>
+      <c r="J59" t="s">
+        <v>53</v>
+      </c>
+      <c r="K59" t="s">
+        <v>33</v>
+      </c>
+      <c r="L59" t="s">
+        <v>25</v>
+      </c>
+      <c r="M59" t="s">
+        <v>34</v>
+      </c>
+      <c r="N59" t="s">
+        <v>21</v>
+      </c>
+      <c r="O59" t="s">
+        <v>21</v>
+      </c>
+      <c r="P59" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>21</v>
+      </c>
+      <c r="R59" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>147</v>
+      </c>
+      <c r="B60" t="s">
+        <v>148</v>
+      </c>
+      <c r="C60" t="s">
+        <v>113</v>
+      </c>
+      <c r="D60" t="s">
+        <v>114</v>
+      </c>
+      <c r="E60">
+        <v>15</v>
+      </c>
+      <c r="F60" t="s">
+        <v>21</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>15</v>
+      </c>
+      <c r="I60" t="s">
+        <v>22</v>
+      </c>
+      <c r="J60" t="s">
+        <v>53</v>
+      </c>
+      <c r="K60" t="s">
+        <v>33</v>
+      </c>
+      <c r="L60" t="s">
+        <v>25</v>
+      </c>
+      <c r="M60" t="s">
+        <v>34</v>
+      </c>
+      <c r="N60" t="s">
+        <v>21</v>
+      </c>
+      <c r="O60" t="s">
+        <v>21</v>
+      </c>
+      <c r="P60" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>21</v>
+      </c>
+      <c r="R60" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>149</v>
+      </c>
+      <c r="B61" t="s">
+        <v>150</v>
+      </c>
+      <c r="C61" t="s">
+        <v>151</v>
+      </c>
+      <c r="D61" t="s">
+        <v>152</v>
+      </c>
+      <c r="E61">
+        <v>5</v>
+      </c>
+      <c r="F61" t="s">
+        <v>21</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>5</v>
+      </c>
+      <c r="I61" t="s">
+        <v>22</v>
+      </c>
+      <c r="J61" t="s">
+        <v>53</v>
+      </c>
+      <c r="K61" t="s">
+        <v>33</v>
+      </c>
+      <c r="L61" t="s">
+        <v>25</v>
+      </c>
+      <c r="M61" t="s">
+        <v>34</v>
+      </c>
+      <c r="N61" t="s">
+        <v>21</v>
+      </c>
+      <c r="O61" t="s">
+        <v>21</v>
+      </c>
+      <c r="P61" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>21</v>
+      </c>
+      <c r="R61" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56AD8CAA-47CB-4D02-B5CA-823792B05E6C}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FB38E5A-BC47-4B72-A614-3FC9854EDA70}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="107">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -134,30 +134,30 @@
     <t>Deposito NQN</t>
   </si>
   <si>
+    <t>C5OX-24-20F</t>
+  </si>
+  <si>
+    <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
+  </si>
+  <si>
+    <t>SOL - 2384</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
     <t>391-2882-051</t>
   </si>
   <si>
     <t>CUERDA P30 Y P50</t>
   </si>
   <si>
-    <t>SOL - 2384</t>
-  </si>
-  <si>
-    <t>2026-07</t>
-  </si>
-  <si>
     <t>391-2884-021P</t>
   </si>
   <si>
     <t>SELLO GOMA SQUARE GASKET 50-25</t>
   </si>
   <si>
-    <t>C5OX-24-20F</t>
-  </si>
-  <si>
-    <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
-  </si>
-  <si>
     <t>MA-310</t>
   </si>
   <si>
@@ -176,52 +176,109 @@
     <t>FILTRO AIRE RESP DESECANTE</t>
   </si>
   <si>
+    <t>313-1135-194</t>
+  </si>
+  <si>
+    <t>EJE POSTIZO P50 Z14</t>
+  </si>
+  <si>
+    <t>SOL - 2537</t>
+  </si>
+  <si>
+    <t>01049</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>Deposito Nqn 2</t>
+  </si>
+  <si>
+    <t>313-2825-000</t>
+  </si>
+  <si>
+    <t>ENGRANAJE P50 DE 2 1/2"</t>
+  </si>
+  <si>
+    <t>313-5037-202</t>
+  </si>
+  <si>
+    <t>TROMPA P50 DE 5" X 4</t>
+  </si>
+  <si>
+    <t>313-8225-100</t>
+  </si>
+  <si>
+    <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
+  </si>
+  <si>
     <t>SA-632-7800A</t>
   </si>
   <si>
     <t>BOMBA PRECARGA SAUER SERIE 90-75 - 14cc</t>
   </si>
   <si>
-    <t>SOL - 2537</t>
-  </si>
-  <si>
-    <t>01049</t>
-  </si>
-  <si>
-    <t>2026-09</t>
-  </si>
-  <si>
-    <t>Deposito Nqn 2</t>
-  </si>
-  <si>
     <t>SA-WLA632-3306F</t>
   </si>
   <si>
     <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
   </si>
   <si>
-    <t>313-1135-194</t>
-  </si>
-  <si>
-    <t>EJE POSTIZO P50 Z14</t>
-  </si>
-  <si>
-    <t>313-2825-000</t>
-  </si>
-  <si>
-    <t>ENGRANAJE P50 DE 2 1/2"</t>
-  </si>
-  <si>
-    <t>313-5037-202</t>
-  </si>
-  <si>
-    <t>TROMPA P50 DE 5" X 4</t>
-  </si>
-  <si>
-    <t>313-8225-100</t>
-  </si>
-  <si>
-    <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
+    <t>SA-631-3306F</t>
+  </si>
+  <si>
+    <t>KIT SELLOS BOMBA SAUER 90-55</t>
+  </si>
+  <si>
+    <t>SOL - 2555</t>
+  </si>
+  <si>
+    <t>SA-638-4701</t>
+  </si>
+  <si>
+    <t>PLACA FRICCION SAUER 90-55</t>
+  </si>
+  <si>
+    <t>SA-638-3306F</t>
+  </si>
+  <si>
+    <t>KIT SELLOS MOTOR SAUER 90-55</t>
+  </si>
+  <si>
+    <t>SA-638-5256</t>
+  </si>
+  <si>
+    <t>CANASTO PORTA RODILLO SAUER 90-55</t>
+  </si>
+  <si>
+    <t>SA-631-4301</t>
+  </si>
+  <si>
+    <t>PLACA VALV. MOTOR SAUER SERIE 90-55</t>
+  </si>
+  <si>
+    <t>SA-631-4501</t>
+  </si>
+  <si>
+    <t>PLACA VALV. LH/RH SAUER SERIE 90-55</t>
+  </si>
+  <si>
+    <t>SA-631-1100C</t>
+  </si>
+  <si>
+    <t>BLOCK CILINDROS SAUER SERIE 90-55 - 8510363</t>
+  </si>
+  <si>
+    <t>SA-631-2100C</t>
+  </si>
+  <si>
+    <t>PISTON SAUER SERIE 90-55</t>
+  </si>
+  <si>
+    <t>SA-634-5221</t>
+  </si>
+  <si>
+    <t>BASCULANTE SAUER SERIE 90-130 BOMBA - VERSION VIEJA</t>
   </si>
   <si>
     <t>SA-634-1100C</t>
@@ -230,9 +287,6 @@
     <t>BLOCK CILINDROS SAUER SERIE 90-130</t>
   </si>
   <si>
-    <t>SOL - 2555</t>
-  </si>
-  <si>
     <t>SA-634-5256</t>
   </si>
   <si>
@@ -281,72 +335,6 @@
     <t>PISTON SAUER SERIE 90-75</t>
   </si>
   <si>
-    <t>SA-631-3306F</t>
-  </si>
-  <si>
-    <t>KIT SELLOS BOMBA SAUER 90-55</t>
-  </si>
-  <si>
-    <t>SA-638-4701</t>
-  </si>
-  <si>
-    <t>PLACA FRICCION SAUER 90-55</t>
-  </si>
-  <si>
-    <t>SA-638-3306F</t>
-  </si>
-  <si>
-    <t>KIT SELLOS MOTOR SAUER 90-55</t>
-  </si>
-  <si>
-    <t>SA-638-5256</t>
-  </si>
-  <si>
-    <t>CANASTO PORTA RODILLO SAUER 90-55</t>
-  </si>
-  <si>
-    <t>SA-631-4301</t>
-  </si>
-  <si>
-    <t>PLACA VALV. MOTOR SAUER SERIE 90-55</t>
-  </si>
-  <si>
-    <t>SA-631-4501</t>
-  </si>
-  <si>
-    <t>PLACA VALV. LH/RH SAUER SERIE 90-55</t>
-  </si>
-  <si>
-    <t>SA-631-1100C</t>
-  </si>
-  <si>
-    <t>BLOCK CILINDROS SAUER SERIE 90-55 - 8510363</t>
-  </si>
-  <si>
-    <t>SA-631-2100C</t>
-  </si>
-  <si>
-    <t>PISTON SAUER SERIE 90-55</t>
-  </si>
-  <si>
-    <t>SA-634-5221</t>
-  </si>
-  <si>
-    <t>BASCULANTE SAUER SERIE 90-130 BOMBA - VERSION VIEJA</t>
-  </si>
-  <si>
-    <t>SA-505410</t>
-  </si>
-  <si>
-    <t>BOMBA DE CARGA DANFOSS 90 PV250 65 CC/REV</t>
-  </si>
-  <si>
-    <t>SA-11012275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EJE DANFOSS Z=14 MF90-055 12/24 (S1) </t>
-  </si>
-  <si>
     <t>SOL - 2564</t>
   </si>
   <si>
@@ -360,132 +348,6 @@
   </si>
   <si>
     <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 7"</t>
-  </si>
-  <si>
-    <t>FT 221/3-100</t>
-  </si>
-  <si>
-    <t>VALVULA ESFERICA DE 3 VIAS, ALTA PRESION 1"</t>
-  </si>
-  <si>
-    <t>SOL - 2580</t>
-  </si>
-  <si>
-    <t>01076</t>
-  </si>
-  <si>
-    <t>FT 221/3-112</t>
-  </si>
-  <si>
-    <t>VALVULA ESFERICA DE 3 VIAS, ALTA PRESION 1.1/2"</t>
-  </si>
-  <si>
-    <t>FT 221/3-114</t>
-  </si>
-  <si>
-    <t>VALVULA ESFERICA DE 3 VIAS, ALTA PRESION 1.1/4"</t>
-  </si>
-  <si>
-    <t>FT 221/3-12</t>
-  </si>
-  <si>
-    <t>VALVULA ESFERICA DE 3 VIAS, ALTA PRESION 1/2"</t>
-  </si>
-  <si>
-    <t>FT 221/3-34</t>
-  </si>
-  <si>
-    <t>VALVULA ESFERICA DE 3 VIAS. ALTA PRESION 3/4"</t>
-  </si>
-  <si>
-    <t>FT 251/2-100</t>
-  </si>
-  <si>
-    <t>VÁLVULA AGUJA BIDIRECCIONAL ACERO 1" BSP MANOPLA ALUMINIO</t>
-  </si>
-  <si>
-    <t>FT 251/2-12</t>
-  </si>
-  <si>
-    <t>VÁLVULA AGUJA BIDIRECCIONAL ACERO 1/2" BSP MANOPLA ALUMINIO</t>
-  </si>
-  <si>
-    <t>FT 251/2-14</t>
-  </si>
-  <si>
-    <t>VALVULA AGUJA BIDIRECCIONAL ACERO 1/4" BSP MANOPLA ALUMINIO</t>
-  </si>
-  <si>
-    <t>FT 251/2-34</t>
-  </si>
-  <si>
-    <t>VALVULA AGUJA BIDIRECCIONAL ACERO 3/4" BSP MANOPLA ALUMINIO</t>
-  </si>
-  <si>
-    <t>FT 257/5-12</t>
-  </si>
-  <si>
-    <t>VALVULA AGUJA UNIDIRECCIONAL 1/2" 400 BAR</t>
-  </si>
-  <si>
-    <t>FT 257/5-14</t>
-  </si>
-  <si>
-    <t>VALVULA AGUJA UNIDIRECCIONAL 1/4" - 350 BAR 15 LT</t>
-  </si>
-  <si>
-    <t>FT 257/5-38</t>
-  </si>
-  <si>
-    <t>VALVULA AGUJA UNIDIRECCIONAL 3/8" 400 BAR</t>
-  </si>
-  <si>
-    <t>FT 257/6-100</t>
-  </si>
-  <si>
-    <t>VALVULA DE RETENCION EN LINEA RECTA 1" 160LPM - 350 BAR</t>
-  </si>
-  <si>
-    <t>FT 257/6-112</t>
-  </si>
-  <si>
-    <t>VALVULA DE RETENCION EN LINEA RECTA 1.1/2" 302LPM - 350 BAR</t>
-  </si>
-  <si>
-    <t>FT 257/6-114</t>
-  </si>
-  <si>
-    <t>VALVULA DE RETENCION EN LINEA RECTA 1.1/4" 210LPM - 350 BAR</t>
-  </si>
-  <si>
-    <t>FT 257/6-12</t>
-  </si>
-  <si>
-    <t>VALVULA DE RETENCION EN LINEA RECTA 1/2" 70LPM - 500 BAR</t>
-  </si>
-  <si>
-    <t>FT 257/6-14</t>
-  </si>
-  <si>
-    <t>VALVULA DE RETENCION EN LINEA RECTA 1/4" 30LPM - 500 BAR</t>
-  </si>
-  <si>
-    <t>FT 257/6-38</t>
-  </si>
-  <si>
-    <t>VALVULA DE RETENCION EN LINEA RECTA 3/8" 45LPM - 500 BAR</t>
-  </si>
-  <si>
-    <t>SEAL KIT HMA280</t>
-  </si>
-  <si>
-    <t>SEAL KIT MOTOR LINDE HMA280 ALTERNATIVO</t>
-  </si>
-  <si>
-    <t>SOL - 2581</t>
-  </si>
-  <si>
-    <t>01077</t>
   </si>
 </sst>
 </file>
@@ -837,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R61"/>
+  <dimension ref="A1:R40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -910,7 +772,7 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
@@ -919,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I2" t="s">
         <v>22</v>
@@ -966,7 +828,7 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
@@ -975,7 +837,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
@@ -1078,7 +940,7 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
@@ -1087,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
         <v>22</v>
@@ -1134,7 +996,7 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
@@ -1143,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
         <v>22</v>
@@ -1246,7 +1108,7 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -1255,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
@@ -1302,7 +1164,7 @@
         <v>21</v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -1311,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
@@ -1358,7 +1220,7 @@
         <v>21</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -1367,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="I10" t="s">
         <v>22</v>
@@ -1526,7 +1388,7 @@
         <v>52</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1535,7 +1397,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
@@ -1582,7 +1444,7 @@
         <v>52</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1591,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
@@ -1638,7 +1500,7 @@
         <v>52</v>
       </c>
       <c r="E15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1647,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
@@ -1694,7 +1556,7 @@
         <v>52</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
@@ -1703,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
@@ -1738,10 +1600,10 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
         <v>51</v>
@@ -1750,7 +1612,7 @@
         <v>52</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="F17" t="s">
         <v>21</v>
@@ -1759,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
@@ -1794,10 +1656,10 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
         <v>51</v>
@@ -1806,7 +1668,7 @@
         <v>52</v>
       </c>
       <c r="E18">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
         <v>21</v>
@@ -1815,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I18" t="s">
         <v>22</v>
@@ -1850,10 +1712,10 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s">
         <v>51</v>
@@ -1862,7 +1724,7 @@
         <v>52</v>
       </c>
       <c r="E19">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="F19" t="s">
         <v>21</v>
@@ -1871,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
@@ -1974,7 +1836,7 @@
         <v>21</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" t="s">
         <v>21</v>
@@ -1983,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
@@ -2030,7 +1892,7 @@
         <v>21</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" t="s">
         <v>21</v>
@@ -2039,7 +1901,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22" t="s">
         <v>22</v>
@@ -2086,7 +1948,7 @@
         <v>21</v>
       </c>
       <c r="E23">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F23" t="s">
         <v>21</v>
@@ -2095,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I23" t="s">
         <v>22</v>
@@ -2198,7 +2060,7 @@
         <v>21</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" t="s">
         <v>21</v>
@@ -2207,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" t="s">
         <v>22</v>
@@ -2310,7 +2172,7 @@
         <v>21</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F27" t="s">
         <v>21</v>
@@ -2319,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I27" t="s">
         <v>22</v>
@@ -2366,7 +2228,7 @@
         <v>21</v>
       </c>
       <c r="E28">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F28" t="s">
         <v>21</v>
@@ -2375,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I28" t="s">
         <v>22</v>
@@ -2478,7 +2340,7 @@
         <v>21</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" t="s">
         <v>21</v>
@@ -2487,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I30" t="s">
         <v>22</v>
@@ -2534,7 +2396,7 @@
         <v>21</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31" t="s">
         <v>21</v>
@@ -2543,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31" t="s">
         <v>22</v>
@@ -2590,7 +2452,7 @@
         <v>21</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F32" t="s">
         <v>21</v>
@@ -2599,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I32" t="s">
         <v>22</v>
@@ -2702,7 +2564,7 @@
         <v>21</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="s">
         <v>21</v>
@@ -2711,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" t="s">
         <v>22</v>
@@ -2814,7 +2676,7 @@
         <v>21</v>
       </c>
       <c r="E36">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F36" t="s">
         <v>21</v>
@@ -2823,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I36" t="s">
         <v>22</v>
@@ -2870,7 +2732,7 @@
         <v>21</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F37" t="s">
         <v>21</v>
@@ -2879,7 +2741,7 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I37" t="s">
         <v>22</v>
@@ -2914,19 +2776,19 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" t="s">
         <v>102</v>
       </c>
-      <c r="B38" t="s">
-        <v>103</v>
-      </c>
-      <c r="C38" t="s">
-        <v>67</v>
-      </c>
       <c r="D38" t="s">
         <v>21</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="F38" t="s">
         <v>21</v>
@@ -2935,7 +2797,7 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="I38" t="s">
         <v>22</v>
@@ -2970,19 +2832,19 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" t="s">
         <v>104</v>
       </c>
-      <c r="B39" t="s">
-        <v>105</v>
-      </c>
       <c r="C39" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="D39" t="s">
         <v>21</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F39" t="s">
         <v>21</v>
@@ -2991,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I39" t="s">
         <v>22</v>
@@ -3026,19 +2888,19 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="C40" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D40" t="s">
         <v>21</v>
       </c>
       <c r="E40">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F40" t="s">
         <v>21</v>
@@ -3047,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I40" t="s">
         <v>22</v>
@@ -3077,1182 +2939,6 @@
         <v>21</v>
       </c>
       <c r="R40" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>107</v>
-      </c>
-      <c r="B41" t="s">
-        <v>108</v>
-      </c>
-      <c r="C41" t="s">
-        <v>106</v>
-      </c>
-      <c r="D41" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>21</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>10</v>
-      </c>
-      <c r="I41" t="s">
-        <v>22</v>
-      </c>
-      <c r="J41" t="s">
-        <v>53</v>
-      </c>
-      <c r="K41" t="s">
-        <v>24</v>
-      </c>
-      <c r="L41" t="s">
-        <v>25</v>
-      </c>
-      <c r="M41" t="s">
-        <v>26</v>
-      </c>
-      <c r="N41" t="s">
-        <v>21</v>
-      </c>
-      <c r="O41" t="s">
-        <v>21</v>
-      </c>
-      <c r="P41" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>21</v>
-      </c>
-      <c r="R41" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>109</v>
-      </c>
-      <c r="B42" t="s">
-        <v>110</v>
-      </c>
-      <c r="C42" t="s">
-        <v>106</v>
-      </c>
-      <c r="D42" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42">
-        <v>30</v>
-      </c>
-      <c r="F42" t="s">
-        <v>21</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>30</v>
-      </c>
-      <c r="I42" t="s">
-        <v>22</v>
-      </c>
-      <c r="J42" t="s">
-        <v>53</v>
-      </c>
-      <c r="K42" t="s">
-        <v>24</v>
-      </c>
-      <c r="L42" t="s">
-        <v>25</v>
-      </c>
-      <c r="M42" t="s">
-        <v>26</v>
-      </c>
-      <c r="N42" t="s">
-        <v>21</v>
-      </c>
-      <c r="O42" t="s">
-        <v>21</v>
-      </c>
-      <c r="P42" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>21</v>
-      </c>
-      <c r="R42" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>111</v>
-      </c>
-      <c r="B43" t="s">
-        <v>112</v>
-      </c>
-      <c r="C43" t="s">
-        <v>113</v>
-      </c>
-      <c r="D43" t="s">
-        <v>114</v>
-      </c>
-      <c r="E43">
-        <v>4</v>
-      </c>
-      <c r="F43" t="s">
-        <v>21</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>4</v>
-      </c>
-      <c r="I43" t="s">
-        <v>22</v>
-      </c>
-      <c r="J43" t="s">
-        <v>53</v>
-      </c>
-      <c r="K43" t="s">
-        <v>33</v>
-      </c>
-      <c r="L43" t="s">
-        <v>25</v>
-      </c>
-      <c r="M43" t="s">
-        <v>34</v>
-      </c>
-      <c r="N43" t="s">
-        <v>21</v>
-      </c>
-      <c r="O43" t="s">
-        <v>21</v>
-      </c>
-      <c r="P43" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>21</v>
-      </c>
-      <c r="R43" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>115</v>
-      </c>
-      <c r="B44" t="s">
-        <v>116</v>
-      </c>
-      <c r="C44" t="s">
-        <v>113</v>
-      </c>
-      <c r="D44" t="s">
-        <v>114</v>
-      </c>
-      <c r="E44">
-        <v>1</v>
-      </c>
-      <c r="F44" t="s">
-        <v>21</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>1</v>
-      </c>
-      <c r="I44" t="s">
-        <v>22</v>
-      </c>
-      <c r="J44" t="s">
-        <v>53</v>
-      </c>
-      <c r="K44" t="s">
-        <v>33</v>
-      </c>
-      <c r="L44" t="s">
-        <v>25</v>
-      </c>
-      <c r="M44" t="s">
-        <v>34</v>
-      </c>
-      <c r="N44" t="s">
-        <v>21</v>
-      </c>
-      <c r="O44" t="s">
-        <v>21</v>
-      </c>
-      <c r="P44" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>21</v>
-      </c>
-      <c r="R44" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>117</v>
-      </c>
-      <c r="B45" t="s">
-        <v>118</v>
-      </c>
-      <c r="C45" t="s">
-        <v>113</v>
-      </c>
-      <c r="D45" t="s">
-        <v>114</v>
-      </c>
-      <c r="E45">
-        <v>2</v>
-      </c>
-      <c r="F45" t="s">
-        <v>21</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>2</v>
-      </c>
-      <c r="I45" t="s">
-        <v>22</v>
-      </c>
-      <c r="J45" t="s">
-        <v>53</v>
-      </c>
-      <c r="K45" t="s">
-        <v>33</v>
-      </c>
-      <c r="L45" t="s">
-        <v>25</v>
-      </c>
-      <c r="M45" t="s">
-        <v>34</v>
-      </c>
-      <c r="N45" t="s">
-        <v>21</v>
-      </c>
-      <c r="O45" t="s">
-        <v>21</v>
-      </c>
-      <c r="P45" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>21</v>
-      </c>
-      <c r="R45" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>119</v>
-      </c>
-      <c r="B46" t="s">
-        <v>120</v>
-      </c>
-      <c r="C46" t="s">
-        <v>113</v>
-      </c>
-      <c r="D46" t="s">
-        <v>114</v>
-      </c>
-      <c r="E46">
-        <v>4</v>
-      </c>
-      <c r="F46" t="s">
-        <v>21</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>4</v>
-      </c>
-      <c r="I46" t="s">
-        <v>22</v>
-      </c>
-      <c r="J46" t="s">
-        <v>53</v>
-      </c>
-      <c r="K46" t="s">
-        <v>33</v>
-      </c>
-      <c r="L46" t="s">
-        <v>25</v>
-      </c>
-      <c r="M46" t="s">
-        <v>34</v>
-      </c>
-      <c r="N46" t="s">
-        <v>21</v>
-      </c>
-      <c r="O46" t="s">
-        <v>21</v>
-      </c>
-      <c r="P46" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>21</v>
-      </c>
-      <c r="R46" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>121</v>
-      </c>
-      <c r="B47" t="s">
-        <v>122</v>
-      </c>
-      <c r="C47" t="s">
-        <v>113</v>
-      </c>
-      <c r="D47" t="s">
-        <v>114</v>
-      </c>
-      <c r="E47">
-        <v>3</v>
-      </c>
-      <c r="F47" t="s">
-        <v>21</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>3</v>
-      </c>
-      <c r="I47" t="s">
-        <v>22</v>
-      </c>
-      <c r="J47" t="s">
-        <v>53</v>
-      </c>
-      <c r="K47" t="s">
-        <v>33</v>
-      </c>
-      <c r="L47" t="s">
-        <v>25</v>
-      </c>
-      <c r="M47" t="s">
-        <v>34</v>
-      </c>
-      <c r="N47" t="s">
-        <v>21</v>
-      </c>
-      <c r="O47" t="s">
-        <v>21</v>
-      </c>
-      <c r="P47" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>21</v>
-      </c>
-      <c r="R47" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>123</v>
-      </c>
-      <c r="B48" t="s">
-        <v>124</v>
-      </c>
-      <c r="C48" t="s">
-        <v>113</v>
-      </c>
-      <c r="D48" t="s">
-        <v>114</v>
-      </c>
-      <c r="E48">
-        <v>4</v>
-      </c>
-      <c r="F48" t="s">
-        <v>21</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>4</v>
-      </c>
-      <c r="I48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J48" t="s">
-        <v>53</v>
-      </c>
-      <c r="K48" t="s">
-        <v>33</v>
-      </c>
-      <c r="L48" t="s">
-        <v>25</v>
-      </c>
-      <c r="M48" t="s">
-        <v>34</v>
-      </c>
-      <c r="N48" t="s">
-        <v>21</v>
-      </c>
-      <c r="O48" t="s">
-        <v>21</v>
-      </c>
-      <c r="P48" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>21</v>
-      </c>
-      <c r="R48" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>125</v>
-      </c>
-      <c r="B49" t="s">
-        <v>126</v>
-      </c>
-      <c r="C49" t="s">
-        <v>113</v>
-      </c>
-      <c r="D49" t="s">
-        <v>114</v>
-      </c>
-      <c r="E49">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>21</v>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>6</v>
-      </c>
-      <c r="I49" t="s">
-        <v>22</v>
-      </c>
-      <c r="J49" t="s">
-        <v>53</v>
-      </c>
-      <c r="K49" t="s">
-        <v>33</v>
-      </c>
-      <c r="L49" t="s">
-        <v>25</v>
-      </c>
-      <c r="M49" t="s">
-        <v>34</v>
-      </c>
-      <c r="N49" t="s">
-        <v>21</v>
-      </c>
-      <c r="O49" t="s">
-        <v>21</v>
-      </c>
-      <c r="P49" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>21</v>
-      </c>
-      <c r="R49" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>127</v>
-      </c>
-      <c r="B50" t="s">
-        <v>128</v>
-      </c>
-      <c r="C50" t="s">
-        <v>113</v>
-      </c>
-      <c r="D50" t="s">
-        <v>114</v>
-      </c>
-      <c r="E50">
-        <v>2</v>
-      </c>
-      <c r="F50" t="s">
-        <v>21</v>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>2</v>
-      </c>
-      <c r="I50" t="s">
-        <v>22</v>
-      </c>
-      <c r="J50" t="s">
-        <v>53</v>
-      </c>
-      <c r="K50" t="s">
-        <v>33</v>
-      </c>
-      <c r="L50" t="s">
-        <v>25</v>
-      </c>
-      <c r="M50" t="s">
-        <v>34</v>
-      </c>
-      <c r="N50" t="s">
-        <v>21</v>
-      </c>
-      <c r="O50" t="s">
-        <v>21</v>
-      </c>
-      <c r="P50" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>21</v>
-      </c>
-      <c r="R50" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>129</v>
-      </c>
-      <c r="B51" t="s">
-        <v>130</v>
-      </c>
-      <c r="C51" t="s">
-        <v>113</v>
-      </c>
-      <c r="D51" t="s">
-        <v>114</v>
-      </c>
-      <c r="E51">
-        <v>4</v>
-      </c>
-      <c r="F51" t="s">
-        <v>21</v>
-      </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51">
-        <v>4</v>
-      </c>
-      <c r="I51" t="s">
-        <v>22</v>
-      </c>
-      <c r="J51" t="s">
-        <v>53</v>
-      </c>
-      <c r="K51" t="s">
-        <v>33</v>
-      </c>
-      <c r="L51" t="s">
-        <v>25</v>
-      </c>
-      <c r="M51" t="s">
-        <v>34</v>
-      </c>
-      <c r="N51" t="s">
-        <v>21</v>
-      </c>
-      <c r="O51" t="s">
-        <v>21</v>
-      </c>
-      <c r="P51" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>21</v>
-      </c>
-      <c r="R51" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>131</v>
-      </c>
-      <c r="B52" t="s">
-        <v>132</v>
-      </c>
-      <c r="C52" t="s">
-        <v>113</v>
-      </c>
-      <c r="D52" t="s">
-        <v>114</v>
-      </c>
-      <c r="E52">
-        <v>3</v>
-      </c>
-      <c r="F52" t="s">
-        <v>21</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52">
-        <v>3</v>
-      </c>
-      <c r="I52" t="s">
-        <v>22</v>
-      </c>
-      <c r="J52" t="s">
-        <v>53</v>
-      </c>
-      <c r="K52" t="s">
-        <v>33</v>
-      </c>
-      <c r="L52" t="s">
-        <v>25</v>
-      </c>
-      <c r="M52" t="s">
-        <v>34</v>
-      </c>
-      <c r="N52" t="s">
-        <v>21</v>
-      </c>
-      <c r="O52" t="s">
-        <v>21</v>
-      </c>
-      <c r="P52" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>21</v>
-      </c>
-      <c r="R52" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>133</v>
-      </c>
-      <c r="B53" t="s">
-        <v>134</v>
-      </c>
-      <c r="C53" t="s">
-        <v>113</v>
-      </c>
-      <c r="D53" t="s">
-        <v>114</v>
-      </c>
-      <c r="E53">
-        <v>4</v>
-      </c>
-      <c r="F53" t="s">
-        <v>21</v>
-      </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-      <c r="H53">
-        <v>4</v>
-      </c>
-      <c r="I53" t="s">
-        <v>22</v>
-      </c>
-      <c r="J53" t="s">
-        <v>53</v>
-      </c>
-      <c r="K53" t="s">
-        <v>33</v>
-      </c>
-      <c r="L53" t="s">
-        <v>25</v>
-      </c>
-      <c r="M53" t="s">
-        <v>34</v>
-      </c>
-      <c r="N53" t="s">
-        <v>21</v>
-      </c>
-      <c r="O53" t="s">
-        <v>21</v>
-      </c>
-      <c r="P53" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>21</v>
-      </c>
-      <c r="R53" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>135</v>
-      </c>
-      <c r="B54" t="s">
-        <v>136</v>
-      </c>
-      <c r="C54" t="s">
-        <v>113</v>
-      </c>
-      <c r="D54" t="s">
-        <v>114</v>
-      </c>
-      <c r="E54">
-        <v>2</v>
-      </c>
-      <c r="F54" t="s">
-        <v>21</v>
-      </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
-      <c r="H54">
-        <v>2</v>
-      </c>
-      <c r="I54" t="s">
-        <v>22</v>
-      </c>
-      <c r="J54" t="s">
-        <v>53</v>
-      </c>
-      <c r="K54" t="s">
-        <v>33</v>
-      </c>
-      <c r="L54" t="s">
-        <v>25</v>
-      </c>
-      <c r="M54" t="s">
-        <v>34</v>
-      </c>
-      <c r="N54" t="s">
-        <v>21</v>
-      </c>
-      <c r="O54" t="s">
-        <v>21</v>
-      </c>
-      <c r="P54" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>21</v>
-      </c>
-      <c r="R54" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>137</v>
-      </c>
-      <c r="B55" t="s">
-        <v>138</v>
-      </c>
-      <c r="C55" t="s">
-        <v>113</v>
-      </c>
-      <c r="D55" t="s">
-        <v>114</v>
-      </c>
-      <c r="E55">
-        <v>4</v>
-      </c>
-      <c r="F55" t="s">
-        <v>21</v>
-      </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
-      <c r="H55">
-        <v>4</v>
-      </c>
-      <c r="I55" t="s">
-        <v>22</v>
-      </c>
-      <c r="J55" t="s">
-        <v>53</v>
-      </c>
-      <c r="K55" t="s">
-        <v>33</v>
-      </c>
-      <c r="L55" t="s">
-        <v>25</v>
-      </c>
-      <c r="M55" t="s">
-        <v>34</v>
-      </c>
-      <c r="N55" t="s">
-        <v>21</v>
-      </c>
-      <c r="O55" t="s">
-        <v>21</v>
-      </c>
-      <c r="P55" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>21</v>
-      </c>
-      <c r="R55" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>139</v>
-      </c>
-      <c r="B56" t="s">
-        <v>140</v>
-      </c>
-      <c r="C56" t="s">
-        <v>113</v>
-      </c>
-      <c r="D56" t="s">
-        <v>114</v>
-      </c>
-      <c r="E56">
-        <v>1</v>
-      </c>
-      <c r="F56" t="s">
-        <v>21</v>
-      </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
-      <c r="H56">
-        <v>1</v>
-      </c>
-      <c r="I56" t="s">
-        <v>22</v>
-      </c>
-      <c r="J56" t="s">
-        <v>53</v>
-      </c>
-      <c r="K56" t="s">
-        <v>33</v>
-      </c>
-      <c r="L56" t="s">
-        <v>25</v>
-      </c>
-      <c r="M56" t="s">
-        <v>34</v>
-      </c>
-      <c r="N56" t="s">
-        <v>21</v>
-      </c>
-      <c r="O56" t="s">
-        <v>21</v>
-      </c>
-      <c r="P56" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>21</v>
-      </c>
-      <c r="R56" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>141</v>
-      </c>
-      <c r="B57" t="s">
-        <v>142</v>
-      </c>
-      <c r="C57" t="s">
-        <v>113</v>
-      </c>
-      <c r="D57" t="s">
-        <v>114</v>
-      </c>
-      <c r="E57">
-        <v>1</v>
-      </c>
-      <c r="F57" t="s">
-        <v>21</v>
-      </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
-      <c r="H57">
-        <v>1</v>
-      </c>
-      <c r="I57" t="s">
-        <v>22</v>
-      </c>
-      <c r="J57" t="s">
-        <v>53</v>
-      </c>
-      <c r="K57" t="s">
-        <v>33</v>
-      </c>
-      <c r="L57" t="s">
-        <v>25</v>
-      </c>
-      <c r="M57" t="s">
-        <v>34</v>
-      </c>
-      <c r="N57" t="s">
-        <v>21</v>
-      </c>
-      <c r="O57" t="s">
-        <v>21</v>
-      </c>
-      <c r="P57" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>21</v>
-      </c>
-      <c r="R57" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>143</v>
-      </c>
-      <c r="B58" t="s">
-        <v>144</v>
-      </c>
-      <c r="C58" t="s">
-        <v>113</v>
-      </c>
-      <c r="D58" t="s">
-        <v>114</v>
-      </c>
-      <c r="E58">
-        <v>10</v>
-      </c>
-      <c r="F58" t="s">
-        <v>21</v>
-      </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
-      <c r="H58">
-        <v>10</v>
-      </c>
-      <c r="I58" t="s">
-        <v>22</v>
-      </c>
-      <c r="J58" t="s">
-        <v>53</v>
-      </c>
-      <c r="K58" t="s">
-        <v>33</v>
-      </c>
-      <c r="L58" t="s">
-        <v>25</v>
-      </c>
-      <c r="M58" t="s">
-        <v>34</v>
-      </c>
-      <c r="N58" t="s">
-        <v>21</v>
-      </c>
-      <c r="O58" t="s">
-        <v>21</v>
-      </c>
-      <c r="P58" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>21</v>
-      </c>
-      <c r="R58" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>145</v>
-      </c>
-      <c r="B59" t="s">
-        <v>146</v>
-      </c>
-      <c r="C59" t="s">
-        <v>113</v>
-      </c>
-      <c r="D59" t="s">
-        <v>114</v>
-      </c>
-      <c r="E59">
-        <v>15</v>
-      </c>
-      <c r="F59" t="s">
-        <v>21</v>
-      </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
-      <c r="H59">
-        <v>15</v>
-      </c>
-      <c r="I59" t="s">
-        <v>22</v>
-      </c>
-      <c r="J59" t="s">
-        <v>53</v>
-      </c>
-      <c r="K59" t="s">
-        <v>33</v>
-      </c>
-      <c r="L59" t="s">
-        <v>25</v>
-      </c>
-      <c r="M59" t="s">
-        <v>34</v>
-      </c>
-      <c r="N59" t="s">
-        <v>21</v>
-      </c>
-      <c r="O59" t="s">
-        <v>21</v>
-      </c>
-      <c r="P59" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>21</v>
-      </c>
-      <c r="R59" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>147</v>
-      </c>
-      <c r="B60" t="s">
-        <v>148</v>
-      </c>
-      <c r="C60" t="s">
-        <v>113</v>
-      </c>
-      <c r="D60" t="s">
-        <v>114</v>
-      </c>
-      <c r="E60">
-        <v>15</v>
-      </c>
-      <c r="F60" t="s">
-        <v>21</v>
-      </c>
-      <c r="G60">
-        <v>0</v>
-      </c>
-      <c r="H60">
-        <v>15</v>
-      </c>
-      <c r="I60" t="s">
-        <v>22</v>
-      </c>
-      <c r="J60" t="s">
-        <v>53</v>
-      </c>
-      <c r="K60" t="s">
-        <v>33</v>
-      </c>
-      <c r="L60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M60" t="s">
-        <v>34</v>
-      </c>
-      <c r="N60" t="s">
-        <v>21</v>
-      </c>
-      <c r="O60" t="s">
-        <v>21</v>
-      </c>
-      <c r="P60" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>21</v>
-      </c>
-      <c r="R60" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>149</v>
-      </c>
-      <c r="B61" t="s">
-        <v>150</v>
-      </c>
-      <c r="C61" t="s">
-        <v>151</v>
-      </c>
-      <c r="D61" t="s">
-        <v>152</v>
-      </c>
-      <c r="E61">
-        <v>5</v>
-      </c>
-      <c r="F61" t="s">
-        <v>21</v>
-      </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
-      <c r="H61">
-        <v>5</v>
-      </c>
-      <c r="I61" t="s">
-        <v>22</v>
-      </c>
-      <c r="J61" t="s">
-        <v>53</v>
-      </c>
-      <c r="K61" t="s">
-        <v>33</v>
-      </c>
-      <c r="L61" t="s">
-        <v>25</v>
-      </c>
-      <c r="M61" t="s">
-        <v>34</v>
-      </c>
-      <c r="N61" t="s">
-        <v>21</v>
-      </c>
-      <c r="O61" t="s">
-        <v>21</v>
-      </c>
-      <c r="P61" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>21</v>
-      </c>
-      <c r="R61" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FB38E5A-BC47-4B72-A614-3FC9854EDA70}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{360A652F-DEB9-4C1C-92C3-AA2523DB2A61}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="98">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -158,22 +158,46 @@
     <t>SELLO GOMA SQUARE GASKET 50-25</t>
   </si>
   <si>
+    <t>FILT-D-AB-2</t>
+  </si>
+  <si>
+    <t>FILTRO AIRE RESP DESECANTE</t>
+  </si>
+  <si>
+    <t>SOL - 2493</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
     <t>MA-310</t>
   </si>
   <si>
     <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
   </si>
   <si>
-    <t>SOL - 2493</t>
-  </si>
-  <si>
-    <t>2026-08</t>
-  </si>
-  <si>
-    <t>FILT-D-AB-2</t>
-  </si>
-  <si>
-    <t>FILTRO AIRE RESP DESECANTE</t>
+    <t>SA-WLA632-3306F</t>
+  </si>
+  <si>
+    <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
+  </si>
+  <si>
+    <t>SOL - 2537</t>
+  </si>
+  <si>
+    <t>01049</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>Deposito Nqn 2</t>
+  </si>
+  <si>
+    <t>SA-632-7800A</t>
+  </si>
+  <si>
+    <t>BOMBA PRECARGA SAUER SERIE 90-75 - 14cc</t>
   </si>
   <si>
     <t>313-1135-194</t>
@@ -182,18 +206,6 @@
     <t>EJE POSTIZO P50 Z14</t>
   </si>
   <si>
-    <t>SOL - 2537</t>
-  </si>
-  <si>
-    <t>01049</t>
-  </si>
-  <si>
-    <t>2026-09</t>
-  </si>
-  <si>
-    <t>Deposito Nqn 2</t>
-  </si>
-  <si>
     <t>313-2825-000</t>
   </si>
   <si>
@@ -212,129 +224,6 @@
     <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
   </si>
   <si>
-    <t>SA-632-7800A</t>
-  </si>
-  <si>
-    <t>BOMBA PRECARGA SAUER SERIE 90-75 - 14cc</t>
-  </si>
-  <si>
-    <t>SA-WLA632-3306F</t>
-  </si>
-  <si>
-    <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
-  </si>
-  <si>
-    <t>SA-631-3306F</t>
-  </si>
-  <si>
-    <t>KIT SELLOS BOMBA SAUER 90-55</t>
-  </si>
-  <si>
-    <t>SOL - 2555</t>
-  </si>
-  <si>
-    <t>SA-638-4701</t>
-  </si>
-  <si>
-    <t>PLACA FRICCION SAUER 90-55</t>
-  </si>
-  <si>
-    <t>SA-638-3306F</t>
-  </si>
-  <si>
-    <t>KIT SELLOS MOTOR SAUER 90-55</t>
-  </si>
-  <si>
-    <t>SA-638-5256</t>
-  </si>
-  <si>
-    <t>CANASTO PORTA RODILLO SAUER 90-55</t>
-  </si>
-  <si>
-    <t>SA-631-4301</t>
-  </si>
-  <si>
-    <t>PLACA VALV. MOTOR SAUER SERIE 90-55</t>
-  </si>
-  <si>
-    <t>SA-631-4501</t>
-  </si>
-  <si>
-    <t>PLACA VALV. LH/RH SAUER SERIE 90-55</t>
-  </si>
-  <si>
-    <t>SA-631-1100C</t>
-  </si>
-  <si>
-    <t>BLOCK CILINDROS SAUER SERIE 90-55 - 8510363</t>
-  </si>
-  <si>
-    <t>SA-631-2100C</t>
-  </si>
-  <si>
-    <t>PISTON SAUER SERIE 90-55</t>
-  </si>
-  <si>
-    <t>SA-634-5221</t>
-  </si>
-  <si>
-    <t>BASCULANTE SAUER SERIE 90-130 BOMBA - VERSION VIEJA</t>
-  </si>
-  <si>
-    <t>SA-634-1100C</t>
-  </si>
-  <si>
-    <t>BLOCK CILINDROS SAUER SERIE 90-130</t>
-  </si>
-  <si>
-    <t>SA-634-5256</t>
-  </si>
-  <si>
-    <t>CANASTO PORTA RODILLO SAUER 90-130 SET</t>
-  </si>
-  <si>
-    <t>SA-634-5257A</t>
-  </si>
-  <si>
-    <t>CUNA SAUER SERIE 90-130 (UNITARIO) MN - 148.7x29.8x51</t>
-  </si>
-  <si>
-    <t>SA-634-2200</t>
-  </si>
-  <si>
-    <t>PISTON SAUER SERIE 90-130</t>
-  </si>
-  <si>
-    <t>SA-640-5256</t>
-  </si>
-  <si>
-    <t>CANASTO PORTA RODILLO SAUER SERIE 90-100</t>
-  </si>
-  <si>
-    <t>SA-640-5251</t>
-  </si>
-  <si>
-    <t>CUNA SAUER GRUESA SERIE 90-100 MV</t>
-  </si>
-  <si>
-    <t>SA-632-1100C</t>
-  </si>
-  <si>
-    <t>BLOCK CILINDROS SAUER SERIE 90-75</t>
-  </si>
-  <si>
-    <t>SA-639-5256</t>
-  </si>
-  <si>
-    <t>CANASTO PORTA RODILLO SAUER SERIE 90-75</t>
-  </si>
-  <si>
-    <t>SA-632-2100C</t>
-  </si>
-  <si>
-    <t>PISTON SAUER SERIE 90-75</t>
-  </si>
-  <si>
     <t>SOL - 2564</t>
   </si>
   <si>
@@ -348,6 +237,90 @@
   </si>
   <si>
     <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 7"</t>
+  </si>
+  <si>
+    <t>VRP-L-1 1/4-C</t>
+  </si>
+  <si>
+    <t>VALVULA  REGULADORA DE PRESION MONTAJE LINEA DE 1 1/4" 190LPM-105-210KG/CM2</t>
+  </si>
+  <si>
+    <t>SOL - 2587</t>
+  </si>
+  <si>
+    <t>01026</t>
+  </si>
+  <si>
+    <t>HIDROIL SRL</t>
+  </si>
+  <si>
+    <t>Deposito</t>
+  </si>
+  <si>
+    <t>SOL - 2594</t>
+  </si>
+  <si>
+    <t>01029</t>
+  </si>
+  <si>
+    <t>FNTX-16P</t>
+  </si>
+  <si>
+    <t>TAPON HEMBRA JIC 37° ROSCA  1.5/16" UNF</t>
+  </si>
+  <si>
+    <t>SOL - 2595</t>
+  </si>
+  <si>
+    <t>934332T</t>
+  </si>
+  <si>
+    <t>FILTRO TRICEPTOR SILICA GEL 10"</t>
+  </si>
+  <si>
+    <t>HTX-06P</t>
+  </si>
+  <si>
+    <t>ADAP RECTO DOBLE MF JIC 9/16" UNF</t>
+  </si>
+  <si>
+    <t>MOTORES HCOS Y TOMAS</t>
+  </si>
+  <si>
+    <t>MOTORES HIDRÁULICOS Y TOMAS DE FUERZA - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2604</t>
+  </si>
+  <si>
+    <t>01088</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+  <si>
+    <t>FTX-06-08P</t>
+  </si>
+  <si>
+    <t>ADAP RECTO 9/16 UNF JIC X 1/2 NPT</t>
+  </si>
+  <si>
+    <t>SOL - 2619</t>
+  </si>
+  <si>
+    <t>01103</t>
+  </si>
+  <si>
+    <t>FTX-06P</t>
+  </si>
+  <si>
+    <t>ADAP RECTO 9/16 UNF JIC X 1/4 NPT</t>
+  </si>
+  <si>
+    <t>FTX-08-04P</t>
+  </si>
+  <si>
+    <t>ADAP RECTO 3/4 UNF JIC X 1/4 NPT</t>
   </si>
 </sst>
 </file>
@@ -699,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R40"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1276,7 +1249,7 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -1285,7 +1258,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I11" t="s">
         <v>22</v>
@@ -1332,7 +1305,7 @@
         <v>21</v>
       </c>
       <c r="E12">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1341,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
@@ -1388,7 +1361,7 @@
         <v>52</v>
       </c>
       <c r="E13">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1397,7 +1370,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
@@ -1444,7 +1417,7 @@
         <v>52</v>
       </c>
       <c r="E14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1453,7 +1426,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
@@ -1488,10 +1461,10 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
         <v>51</v>
@@ -1500,7 +1473,7 @@
         <v>52</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1509,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
@@ -1544,10 +1517,10 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
         <v>51</v>
@@ -1556,7 +1529,7 @@
         <v>52</v>
       </c>
       <c r="E16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
@@ -1565,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
@@ -1600,10 +1573,10 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
         <v>51</v>
@@ -1612,7 +1585,7 @@
         <v>52</v>
       </c>
       <c r="E17">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
         <v>21</v>
@@ -1621,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
@@ -1668,7 +1641,7 @@
         <v>52</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
         <v>21</v>
@@ -1677,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I18" t="s">
         <v>22</v>
@@ -1724,7 +1697,7 @@
         <v>52</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F19" t="s">
         <v>21</v>
@@ -1733,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
@@ -1768,19 +1741,19 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" t="s">
         <v>65</v>
       </c>
-      <c r="B20" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" t="s">
-        <v>67</v>
-      </c>
       <c r="D20" t="s">
         <v>21</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -1789,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
@@ -1824,19 +1797,19 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D21" t="s">
         <v>21</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
         <v>21</v>
@@ -1845,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
@@ -1880,19 +1853,19 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
         <v>21</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F22" t="s">
         <v>21</v>
@@ -1901,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I22" t="s">
         <v>22</v>
@@ -1936,19 +1909,19 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" t="s">
         <v>72</v>
       </c>
-      <c r="B23" t="s">
+      <c r="D23" t="s">
         <v>73</v>
       </c>
-      <c r="C23" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" t="s">
-        <v>21</v>
-      </c>
       <c r="E23">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s">
         <v>21</v>
@@ -1957,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I23" t="s">
         <v>22</v>
@@ -1966,13 +1939,13 @@
         <v>53</v>
       </c>
       <c r="K23" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L23" t="s">
         <v>25</v>
       </c>
       <c r="M23" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="N23" t="s">
         <v>21</v>
@@ -1992,19 +1965,19 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
         <v>21</v>
@@ -2013,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
@@ -2022,13 +1995,13 @@
         <v>53</v>
       </c>
       <c r="K24" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L24" t="s">
         <v>25</v>
       </c>
       <c r="M24" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="N24" t="s">
         <v>21</v>
@@ -2048,19 +2021,19 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
         <v>21</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="F25" t="s">
         <v>21</v>
@@ -2069,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="I25" t="s">
         <v>22</v>
@@ -2104,19 +2077,19 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D26" t="s">
         <v>21</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F26" t="s">
         <v>21</v>
@@ -2125,7 +2098,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I26" t="s">
         <v>22</v>
@@ -2160,19 +2133,19 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" t="s">
         <v>80</v>
       </c>
-      <c r="B27" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" t="s">
-        <v>67</v>
-      </c>
       <c r="D27" t="s">
         <v>21</v>
       </c>
       <c r="E27">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F27" t="s">
         <v>21</v>
@@ -2181,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="I27" t="s">
         <v>22</v>
@@ -2216,16 +2189,16 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -2243,16 +2216,16 @@
         <v>22</v>
       </c>
       <c r="J28" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L28" t="s">
         <v>25</v>
       </c>
       <c r="M28" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="N28" t="s">
         <v>21</v>
@@ -2272,19 +2245,19 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F29" t="s">
         <v>21</v>
@@ -2293,22 +2266,22 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="I29" t="s">
         <v>22</v>
       </c>
       <c r="J29" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L29" t="s">
         <v>25</v>
       </c>
       <c r="M29" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="N29" t="s">
         <v>21</v>
@@ -2328,19 +2301,19 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="D30" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="F30" t="s">
         <v>21</v>
@@ -2349,22 +2322,22 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="I30" t="s">
         <v>22</v>
       </c>
       <c r="J30" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L30" t="s">
         <v>25</v>
       </c>
       <c r="M30" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="N30" t="s">
         <v>21</v>
@@ -2384,43 +2357,43 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B31" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" t="s">
+        <v>93</v>
+      </c>
+      <c r="E31">
+        <v>50</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>50</v>
+      </c>
+      <c r="I31" t="s">
+        <v>22</v>
+      </c>
+      <c r="J31" t="s">
         <v>89</v>
       </c>
-      <c r="C31" t="s">
-        <v>67</v>
-      </c>
-      <c r="D31" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31">
-        <v>3</v>
-      </c>
-      <c r="F31" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>3</v>
-      </c>
-      <c r="I31" t="s">
-        <v>22</v>
-      </c>
-      <c r="J31" t="s">
-        <v>53</v>
-      </c>
       <c r="K31" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L31" t="s">
         <v>25</v>
       </c>
       <c r="M31" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="N31" t="s">
         <v>21</v>
@@ -2435,510 +2408,6 @@
         <v>21</v>
       </c>
       <c r="R31" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>90</v>
-      </c>
-      <c r="B32" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>9</v>
-      </c>
-      <c r="I32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" t="s">
-        <v>53</v>
-      </c>
-      <c r="K32" t="s">
-        <v>24</v>
-      </c>
-      <c r="L32" t="s">
-        <v>25</v>
-      </c>
-      <c r="M32" t="s">
-        <v>26</v>
-      </c>
-      <c r="N32" t="s">
-        <v>21</v>
-      </c>
-      <c r="O32" t="s">
-        <v>21</v>
-      </c>
-      <c r="P32" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>21</v>
-      </c>
-      <c r="R32" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>92</v>
-      </c>
-      <c r="B33" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" t="s">
-        <v>67</v>
-      </c>
-      <c r="D33" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33">
-        <v>1</v>
-      </c>
-      <c r="F33" t="s">
-        <v>21</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>1</v>
-      </c>
-      <c r="I33" t="s">
-        <v>22</v>
-      </c>
-      <c r="J33" t="s">
-        <v>53</v>
-      </c>
-      <c r="K33" t="s">
-        <v>24</v>
-      </c>
-      <c r="L33" t="s">
-        <v>25</v>
-      </c>
-      <c r="M33" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" t="s">
-        <v>21</v>
-      </c>
-      <c r="O33" t="s">
-        <v>21</v>
-      </c>
-      <c r="P33" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>21</v>
-      </c>
-      <c r="R33" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>94</v>
-      </c>
-      <c r="B34" t="s">
-        <v>95</v>
-      </c>
-      <c r="C34" t="s">
-        <v>67</v>
-      </c>
-      <c r="D34" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34">
-        <v>2</v>
-      </c>
-      <c r="F34" t="s">
-        <v>21</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>2</v>
-      </c>
-      <c r="I34" t="s">
-        <v>22</v>
-      </c>
-      <c r="J34" t="s">
-        <v>53</v>
-      </c>
-      <c r="K34" t="s">
-        <v>24</v>
-      </c>
-      <c r="L34" t="s">
-        <v>25</v>
-      </c>
-      <c r="M34" t="s">
-        <v>26</v>
-      </c>
-      <c r="N34" t="s">
-        <v>21</v>
-      </c>
-      <c r="O34" t="s">
-        <v>21</v>
-      </c>
-      <c r="P34" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>21</v>
-      </c>
-      <c r="R34" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>96</v>
-      </c>
-      <c r="B35" t="s">
-        <v>97</v>
-      </c>
-      <c r="C35" t="s">
-        <v>67</v>
-      </c>
-      <c r="D35" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35">
-        <v>2</v>
-      </c>
-      <c r="F35" t="s">
-        <v>21</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>2</v>
-      </c>
-      <c r="I35" t="s">
-        <v>22</v>
-      </c>
-      <c r="J35" t="s">
-        <v>53</v>
-      </c>
-      <c r="K35" t="s">
-        <v>24</v>
-      </c>
-      <c r="L35" t="s">
-        <v>25</v>
-      </c>
-      <c r="M35" t="s">
-        <v>26</v>
-      </c>
-      <c r="N35" t="s">
-        <v>21</v>
-      </c>
-      <c r="O35" t="s">
-        <v>21</v>
-      </c>
-      <c r="P35" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>21</v>
-      </c>
-      <c r="R35" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>98</v>
-      </c>
-      <c r="B36" t="s">
-        <v>99</v>
-      </c>
-      <c r="C36" t="s">
-        <v>67</v>
-      </c>
-      <c r="D36" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36">
-        <v>3</v>
-      </c>
-      <c r="F36" t="s">
-        <v>21</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>3</v>
-      </c>
-      <c r="I36" t="s">
-        <v>22</v>
-      </c>
-      <c r="J36" t="s">
-        <v>53</v>
-      </c>
-      <c r="K36" t="s">
-        <v>24</v>
-      </c>
-      <c r="L36" t="s">
-        <v>25</v>
-      </c>
-      <c r="M36" t="s">
-        <v>26</v>
-      </c>
-      <c r="N36" t="s">
-        <v>21</v>
-      </c>
-      <c r="O36" t="s">
-        <v>21</v>
-      </c>
-      <c r="P36" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>21</v>
-      </c>
-      <c r="R36" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>100</v>
-      </c>
-      <c r="B37" t="s">
-        <v>101</v>
-      </c>
-      <c r="C37" t="s">
-        <v>67</v>
-      </c>
-      <c r="D37" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>21</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>9</v>
-      </c>
-      <c r="I37" t="s">
-        <v>22</v>
-      </c>
-      <c r="J37" t="s">
-        <v>53</v>
-      </c>
-      <c r="K37" t="s">
-        <v>24</v>
-      </c>
-      <c r="L37" t="s">
-        <v>25</v>
-      </c>
-      <c r="M37" t="s">
-        <v>26</v>
-      </c>
-      <c r="N37" t="s">
-        <v>21</v>
-      </c>
-      <c r="O37" t="s">
-        <v>21</v>
-      </c>
-      <c r="P37" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>21</v>
-      </c>
-      <c r="R37" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
-      </c>
-      <c r="C38" t="s">
-        <v>102</v>
-      </c>
-      <c r="D38" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38">
-        <v>40</v>
-      </c>
-      <c r="F38" t="s">
-        <v>21</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <v>40</v>
-      </c>
-      <c r="I38" t="s">
-        <v>22</v>
-      </c>
-      <c r="J38" t="s">
-        <v>53</v>
-      </c>
-      <c r="K38" t="s">
-        <v>24</v>
-      </c>
-      <c r="L38" t="s">
-        <v>25</v>
-      </c>
-      <c r="M38" t="s">
-        <v>26</v>
-      </c>
-      <c r="N38" t="s">
-        <v>21</v>
-      </c>
-      <c r="O38" t="s">
-        <v>21</v>
-      </c>
-      <c r="P38" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>21</v>
-      </c>
-      <c r="R38" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>103</v>
-      </c>
-      <c r="B39" t="s">
-        <v>104</v>
-      </c>
-      <c r="C39" t="s">
-        <v>102</v>
-      </c>
-      <c r="D39" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>21</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>10</v>
-      </c>
-      <c r="I39" t="s">
-        <v>22</v>
-      </c>
-      <c r="J39" t="s">
-        <v>53</v>
-      </c>
-      <c r="K39" t="s">
-        <v>24</v>
-      </c>
-      <c r="L39" t="s">
-        <v>25</v>
-      </c>
-      <c r="M39" t="s">
-        <v>26</v>
-      </c>
-      <c r="N39" t="s">
-        <v>21</v>
-      </c>
-      <c r="O39" t="s">
-        <v>21</v>
-      </c>
-      <c r="P39" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>21</v>
-      </c>
-      <c r="R39" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>105</v>
-      </c>
-      <c r="B40" t="s">
-        <v>106</v>
-      </c>
-      <c r="C40" t="s">
-        <v>102</v>
-      </c>
-      <c r="D40" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40">
-        <v>30</v>
-      </c>
-      <c r="F40" t="s">
-        <v>21</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>30</v>
-      </c>
-      <c r="I40" t="s">
-        <v>22</v>
-      </c>
-      <c r="J40" t="s">
-        <v>53</v>
-      </c>
-      <c r="K40" t="s">
-        <v>24</v>
-      </c>
-      <c r="L40" t="s">
-        <v>25</v>
-      </c>
-      <c r="M40" t="s">
-        <v>26</v>
-      </c>
-      <c r="N40" t="s">
-        <v>21</v>
-      </c>
-      <c r="O40" t="s">
-        <v>21</v>
-      </c>
-      <c r="P40" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>21</v>
-      </c>
-      <c r="R40" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,26 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{360A652F-DEB9-4C1C-92C3-AA2523DB2A61}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E1979E1-FF6F-430F-838E-A902727FBB6E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="96">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -158,22 +151,106 @@
     <t>SELLO GOMA SQUARE GASKET 50-25</t>
   </si>
   <si>
+    <t>MA-310</t>
+  </si>
+  <si>
+    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
+  </si>
+  <si>
+    <t>SOL - 2493</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
     <t>FILT-D-AB-2</t>
   </si>
   <si>
     <t>FILTRO AIRE RESP DESECANTE</t>
   </si>
   <si>
-    <t>SOL - 2493</t>
-  </si>
-  <si>
-    <t>2026-08</t>
-  </si>
-  <si>
-    <t>MA-310</t>
-  </si>
-  <si>
-    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
+    <t>CV HERRAMIENTAS</t>
+  </si>
+  <si>
+    <t>Herramientas</t>
+  </si>
+  <si>
+    <t>SOL - 2621</t>
+  </si>
+  <si>
+    <t>01033</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>HIDROIL SRL</t>
+  </si>
+  <si>
+    <t>Servicio Comodoro R.</t>
+  </si>
+  <si>
+    <t>SOL - 2622</t>
+  </si>
+  <si>
+    <t>01034</t>
+  </si>
+  <si>
+    <t>SOL - 2623</t>
+  </si>
+  <si>
+    <t>01035</t>
+  </si>
+  <si>
+    <t>SOL - 2624</t>
+  </si>
+  <si>
+    <t>01036</t>
+  </si>
+  <si>
+    <t>SOL - 2625</t>
+  </si>
+  <si>
+    <t>01037</t>
+  </si>
+  <si>
+    <t>SOL - 2626</t>
+  </si>
+  <si>
+    <t>01038</t>
+  </si>
+  <si>
+    <t>313-1135-194</t>
+  </si>
+  <si>
+    <t>EJE POSTIZO P50 Z14</t>
+  </si>
+  <si>
+    <t>SOL - 2537</t>
+  </si>
+  <si>
+    <t>01049</t>
+  </si>
+  <si>
+    <t>Deposito Nqn 2</t>
+  </si>
+  <si>
+    <t>313-2825-000</t>
+  </si>
+  <si>
+    <t>ENGRANAJE P50 DE 2 1/2"</t>
+  </si>
+  <si>
+    <t>313-5037-202</t>
+  </si>
+  <si>
+    <t>TROMPA P50 DE 5" X 4</t>
+  </si>
+  <si>
+    <t>313-8225-100</t>
+  </si>
+  <si>
+    <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
   </si>
   <si>
     <t>SA-WLA632-3306F</t>
@@ -182,48 +259,12 @@
     <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
   </si>
   <si>
-    <t>SOL - 2537</t>
-  </si>
-  <si>
-    <t>01049</t>
-  </si>
-  <si>
-    <t>2026-09</t>
-  </si>
-  <si>
-    <t>Deposito Nqn 2</t>
-  </si>
-  <si>
     <t>SA-632-7800A</t>
   </si>
   <si>
     <t>BOMBA PRECARGA SAUER SERIE 90-75 - 14cc</t>
   </si>
   <si>
-    <t>313-1135-194</t>
-  </si>
-  <si>
-    <t>EJE POSTIZO P50 Z14</t>
-  </si>
-  <si>
-    <t>313-2825-000</t>
-  </si>
-  <si>
-    <t>ENGRANAJE P50 DE 2 1/2"</t>
-  </si>
-  <si>
-    <t>313-5037-202</t>
-  </si>
-  <si>
-    <t>TROMPA P50 DE 5" X 4</t>
-  </si>
-  <si>
-    <t>313-8225-100</t>
-  </si>
-  <si>
-    <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
-  </si>
-  <si>
     <t>SOL - 2564</t>
   </si>
   <si>
@@ -239,88 +280,34 @@
     <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 7"</t>
   </si>
   <si>
-    <t>VRP-L-1 1/4-C</t>
-  </si>
-  <si>
-    <t>VALVULA  REGULADORA DE PRESION MONTAJE LINEA DE 1 1/4" 190LPM-105-210KG/CM2</t>
-  </si>
-  <si>
-    <t>SOL - 2587</t>
-  </si>
-  <si>
-    <t>01026</t>
-  </si>
-  <si>
-    <t>HIDROIL SRL</t>
-  </si>
-  <si>
-    <t>Deposito</t>
-  </si>
-  <si>
-    <t>SOL - 2594</t>
-  </si>
-  <si>
-    <t>01029</t>
-  </si>
-  <si>
-    <t>FNTX-16P</t>
-  </si>
-  <si>
-    <t>TAPON HEMBRA JIC 37° ROSCA  1.5/16" UNF</t>
+    <t>934332T</t>
+  </si>
+  <si>
+    <t>FILTRO TRICEPTOR SILICA GEL 10"</t>
   </si>
   <si>
     <t>SOL - 2595</t>
   </si>
   <si>
-    <t>934332T</t>
-  </si>
-  <si>
-    <t>FILTRO TRICEPTOR SILICA GEL 10"</t>
-  </si>
-  <si>
-    <t>HTX-06P</t>
-  </si>
-  <si>
-    <t>ADAP RECTO DOBLE MF JIC 9/16" UNF</t>
-  </si>
-  <si>
-    <t>MOTORES HCOS Y TOMAS</t>
-  </si>
-  <si>
-    <t>MOTORES HIDRÁULICOS Y TOMAS DE FUERZA - GENERICO</t>
-  </si>
-  <si>
-    <t>SOL - 2604</t>
-  </si>
-  <si>
-    <t>01088</t>
+    <t>INSUMOS DEPOSITO</t>
+  </si>
+  <si>
+    <t>INSUMOS PARA DEPOSITO - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2620</t>
+  </si>
+  <si>
+    <t>01104</t>
   </si>
   <si>
     <t>2026-10</t>
   </si>
   <si>
-    <t>FTX-06-08P</t>
-  </si>
-  <si>
-    <t>ADAP RECTO 9/16 UNF JIC X 1/2 NPT</t>
-  </si>
-  <si>
-    <t>SOL - 2619</t>
-  </si>
-  <si>
-    <t>01103</t>
-  </si>
-  <si>
-    <t>FTX-06P</t>
-  </si>
-  <si>
-    <t>ADAP RECTO 9/16 UNF JIC X 1/4 NPT</t>
-  </si>
-  <si>
-    <t>FTX-08-04P</t>
-  </si>
-  <si>
-    <t>ADAP RECTO 3/4 UNF JIC X 1/4 NPT</t>
+    <t>INSUMOS VARIOS 10.5%</t>
+  </si>
+  <si>
+    <t>INSUMOS VARIOS 10.5% - GENERICO</t>
   </si>
 </sst>
 </file>
@@ -1249,7 +1236,7 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -1258,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I11" t="s">
         <v>22</v>
@@ -1305,7 +1292,7 @@
         <v>21</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1314,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
@@ -1361,7 +1348,7 @@
         <v>52</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1370,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
@@ -1379,13 +1366,13 @@
         <v>53</v>
       </c>
       <c r="K13" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="L13" t="s">
         <v>25</v>
       </c>
       <c r="M13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N13" t="s">
         <v>21</v>
@@ -1405,19 +1392,19 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s">
         <v>56</v>
       </c>
-      <c r="C14" t="s">
-        <v>51</v>
-      </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1426,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
@@ -1435,13 +1422,13 @@
         <v>53</v>
       </c>
       <c r="K14" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="L14" t="s">
         <v>25</v>
       </c>
       <c r="M14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N14" t="s">
         <v>21</v>
@@ -1461,19 +1448,19 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E15">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1482,7 +1469,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
@@ -1491,13 +1478,13 @@
         <v>53</v>
       </c>
       <c r="K15" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="L15" t="s">
         <v>25</v>
       </c>
       <c r="M15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N15" t="s">
         <v>21</v>
@@ -1517,19 +1504,19 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
@@ -1538,7 +1525,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
@@ -1547,13 +1534,13 @@
         <v>53</v>
       </c>
       <c r="K16" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="L16" t="s">
         <v>25</v>
       </c>
       <c r="M16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N16" t="s">
         <v>21</v>
@@ -1573,19 +1560,19 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F17" t="s">
         <v>21</v>
@@ -1594,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
@@ -1603,13 +1590,13 @@
         <v>53</v>
       </c>
       <c r="K17" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="L17" t="s">
         <v>25</v>
       </c>
       <c r="M17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N17" t="s">
         <v>21</v>
@@ -1629,19 +1616,19 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E18">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F18" t="s">
         <v>21</v>
@@ -1650,7 +1637,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I18" t="s">
         <v>22</v>
@@ -1659,13 +1646,13 @@
         <v>53</v>
       </c>
       <c r="K18" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="L18" t="s">
         <v>25</v>
       </c>
       <c r="M18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N18" t="s">
         <v>21</v>
@@ -1685,19 +1672,19 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B19" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="E19">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
         <v>21</v>
@@ -1706,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
@@ -1721,7 +1708,7 @@
         <v>25</v>
       </c>
       <c r="M19" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="N19" t="s">
         <v>21</v>
@@ -1741,19 +1728,19 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="E20">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -1762,7 +1749,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
@@ -1771,13 +1758,13 @@
         <v>53</v>
       </c>
       <c r="K20" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L20" t="s">
         <v>25</v>
       </c>
       <c r="M20" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="N20" t="s">
         <v>21</v>
@@ -1797,19 +1784,19 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
         <v>21</v>
@@ -1818,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
@@ -1827,13 +1814,13 @@
         <v>53</v>
       </c>
       <c r="K21" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L21" t="s">
         <v>25</v>
       </c>
       <c r="M21" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="N21" t="s">
         <v>21</v>
@@ -1853,19 +1840,19 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
         <v>68</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D22" t="s">
         <v>69</v>
       </c>
-      <c r="C22" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" t="s">
-        <v>21</v>
-      </c>
       <c r="E22">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F22" t="s">
         <v>21</v>
@@ -1874,7 +1861,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I22" t="s">
         <v>22</v>
@@ -1883,13 +1870,13 @@
         <v>53</v>
       </c>
       <c r="K22" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L22" t="s">
         <v>25</v>
       </c>
       <c r="M22" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="N22" t="s">
         <v>21</v>
@@ -1909,19 +1896,19 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="F23" t="s">
         <v>21</v>
@@ -1930,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="I23" t="s">
         <v>22</v>
@@ -1939,13 +1926,13 @@
         <v>53</v>
       </c>
       <c r="K23" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="L23" t="s">
         <v>25</v>
       </c>
       <c r="M23" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="N23" t="s">
         <v>21</v>
@@ -1965,19 +1952,19 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E24">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F24" t="s">
         <v>21</v>
@@ -1986,7 +1973,7 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
@@ -1995,13 +1982,13 @@
         <v>53</v>
       </c>
       <c r="K24" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="L24" t="s">
         <v>25</v>
       </c>
       <c r="M24" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="N24" t="s">
         <v>21</v>
@@ -2021,19 +2008,19 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D25" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="E25">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="F25" t="s">
         <v>21</v>
@@ -2042,7 +2029,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="I25" t="s">
         <v>22</v>
@@ -2051,13 +2038,13 @@
         <v>53</v>
       </c>
       <c r="K25" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L25" t="s">
         <v>25</v>
       </c>
       <c r="M25" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="N25" t="s">
         <v>21</v>
@@ -2077,19 +2064,19 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" t="s">
         <v>81</v>
       </c>
-      <c r="B26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" t="s">
-        <v>80</v>
-      </c>
       <c r="D26" t="s">
         <v>21</v>
       </c>
       <c r="E26">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F26" t="s">
         <v>21</v>
@@ -2098,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="I26" t="s">
         <v>22</v>
@@ -2133,19 +2120,19 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" t="s">
         <v>83</v>
       </c>
-      <c r="B27" t="s">
-        <v>84</v>
-      </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s">
         <v>21</v>
       </c>
       <c r="E27">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
         <v>21</v>
@@ -2154,7 +2141,7 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I27" t="s">
         <v>22</v>
@@ -2189,19 +2176,19 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" t="s">
         <v>85</v>
       </c>
-      <c r="B28" t="s">
-        <v>86</v>
-      </c>
       <c r="C28" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D28" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F28" t="s">
         <v>21</v>
@@ -2210,22 +2197,22 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I28" t="s">
         <v>22</v>
       </c>
       <c r="J28" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="K28" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L28" t="s">
         <v>25</v>
       </c>
       <c r="M28" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N28" t="s">
         <v>21</v>
@@ -2245,19 +2232,19 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="E29">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="F29" t="s">
         <v>21</v>
@@ -2266,22 +2253,22 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="I29" t="s">
         <v>22</v>
       </c>
       <c r="J29" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="K29" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L29" t="s">
         <v>25</v>
       </c>
       <c r="M29" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N29" t="s">
         <v>21</v>
@@ -2301,34 +2288,34 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" t="s">
         <v>92</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30">
+        <v>96</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>96</v>
+      </c>
+      <c r="I30" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" t="s">
         <v>93</v>
-      </c>
-      <c r="E30">
-        <v>150</v>
-      </c>
-      <c r="F30" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>150</v>
-      </c>
-      <c r="I30" t="s">
-        <v>22</v>
-      </c>
-      <c r="J30" t="s">
-        <v>89</v>
       </c>
       <c r="K30" t="s">
         <v>33</v>
@@ -2337,7 +2324,7 @@
         <v>25</v>
       </c>
       <c r="M30" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N30" t="s">
         <v>21</v>
@@ -2357,34 +2344,34 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31" t="s">
         <v>92</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31">
+        <v>24</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>24</v>
+      </c>
+      <c r="I31" t="s">
+        <v>22</v>
+      </c>
+      <c r="J31" t="s">
         <v>93</v>
-      </c>
-      <c r="E31">
-        <v>50</v>
-      </c>
-      <c r="F31" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>50</v>
-      </c>
-      <c r="I31" t="s">
-        <v>22</v>
-      </c>
-      <c r="J31" t="s">
-        <v>89</v>
       </c>
       <c r="K31" t="s">
         <v>33</v>
@@ -2393,7 +2380,7 @@
         <v>25</v>
       </c>
       <c r="M31" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N31" t="s">
         <v>21</v>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E1979E1-FF6F-430F-838E-A902727FBB6E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA0FAB0C-2E72-4042-BE8D-EEF0C780E51E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="90">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -127,28 +127,40 @@
     <t>Deposito NQN</t>
   </si>
   <si>
+    <t>391-2882-051</t>
+  </si>
+  <si>
+    <t>CUERDA P30 Y P50</t>
+  </si>
+  <si>
+    <t>SOL - 2384</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>391-2884-021P</t>
+  </si>
+  <si>
+    <t>SELLO GOMA SQUARE GASKET 50-25</t>
+  </si>
+  <si>
     <t>C5OX-24-20F</t>
   </si>
   <si>
     <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
   </si>
   <si>
-    <t>SOL - 2384</t>
-  </si>
-  <si>
-    <t>2026-07</t>
-  </si>
-  <si>
-    <t>391-2882-051</t>
-  </si>
-  <si>
-    <t>CUERDA P30 Y P50</t>
-  </si>
-  <si>
-    <t>391-2884-021P</t>
-  </si>
-  <si>
-    <t>SELLO GOMA SQUARE GASKET 50-25</t>
+    <t>FILT-D-AB-2</t>
+  </si>
+  <si>
+    <t>FILTRO AIRE RESP DESECANTE</t>
+  </si>
+  <si>
+    <t>SOL - 2493</t>
+  </si>
+  <si>
+    <t>2026-08</t>
   </si>
   <si>
     <t>MA-310</t>
@@ -157,157 +169,127 @@
     <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
   </si>
   <si>
-    <t>SOL - 2493</t>
-  </si>
-  <si>
-    <t>2026-08</t>
-  </si>
-  <si>
-    <t>FILT-D-AB-2</t>
-  </si>
-  <si>
-    <t>FILTRO AIRE RESP DESECANTE</t>
-  </si>
-  <si>
-    <t>CV HERRAMIENTAS</t>
-  </si>
-  <si>
-    <t>Herramientas</t>
-  </si>
-  <si>
-    <t>SOL - 2621</t>
-  </si>
-  <si>
-    <t>01033</t>
+    <t>SA-WLA632-3306F</t>
+  </si>
+  <si>
+    <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
+  </si>
+  <si>
+    <t>SOL - 2537</t>
+  </si>
+  <si>
+    <t>01049</t>
   </si>
   <si>
     <t>2026-09</t>
   </si>
   <si>
+    <t>Deposito Nqn 2</t>
+  </si>
+  <si>
+    <t>313-1135-194</t>
+  </si>
+  <si>
+    <t>EJE POSTIZO P50 Z14</t>
+  </si>
+  <si>
+    <t>313-2825-000</t>
+  </si>
+  <si>
+    <t>ENGRANAJE P50 DE 2 1/2"</t>
+  </si>
+  <si>
+    <t>313-5037-202</t>
+  </si>
+  <si>
+    <t>TROMPA P50 DE 5" X 4</t>
+  </si>
+  <si>
+    <t>313-8225-100</t>
+  </si>
+  <si>
+    <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
+  </si>
+  <si>
+    <t>SOL - 2564</t>
+  </si>
+  <si>
+    <t>FILT-10MZ10</t>
+  </si>
+  <si>
+    <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 10"</t>
+  </si>
+  <si>
+    <t>FILT-MZ10</t>
+  </si>
+  <si>
+    <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 7"</t>
+  </si>
+  <si>
+    <t>934332T</t>
+  </si>
+  <si>
+    <t>FILTRO TRICEPTOR SILICA GEL 10"</t>
+  </si>
+  <si>
+    <t>SOL - 2595</t>
+  </si>
+  <si>
+    <t>INSUMOS DEPOSITO</t>
+  </si>
+  <si>
+    <t>INSUMOS PARA DEPOSITO - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2620</t>
+  </si>
+  <si>
+    <t>01104</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+  <si>
+    <t>INSUMOS VARIOS 10.5%</t>
+  </si>
+  <si>
+    <t>INSUMOS VARIOS 10.5% - GENERICO</t>
+  </si>
+  <si>
+    <t>2-230-N70</t>
+  </si>
+  <si>
+    <t>ORING 2-230 D70 DI 63.09 X DE 70.15 ESP 3.53</t>
+  </si>
+  <si>
+    <t>SOL - 2629</t>
+  </si>
+  <si>
+    <t>01039</t>
+  </si>
+  <si>
     <t>HIDROIL SRL</t>
   </si>
   <si>
-    <t>Servicio Comodoro R.</t>
-  </si>
-  <si>
-    <t>SOL - 2622</t>
-  </si>
-  <si>
-    <t>01034</t>
-  </si>
-  <si>
-    <t>SOL - 2623</t>
-  </si>
-  <si>
-    <t>01035</t>
-  </si>
-  <si>
-    <t>SOL - 2624</t>
-  </si>
-  <si>
-    <t>01036</t>
-  </si>
-  <si>
-    <t>SOL - 2625</t>
-  </si>
-  <si>
-    <t>01037</t>
-  </si>
-  <si>
-    <t>SOL - 2626</t>
-  </si>
-  <si>
-    <t>01038</t>
-  </si>
-  <si>
-    <t>313-1135-194</t>
-  </si>
-  <si>
-    <t>EJE POSTIZO P50 Z14</t>
-  </si>
-  <si>
-    <t>SOL - 2537</t>
-  </si>
-  <si>
-    <t>01049</t>
-  </si>
-  <si>
-    <t>Deposito Nqn 2</t>
-  </si>
-  <si>
-    <t>313-2825-000</t>
-  </si>
-  <si>
-    <t>ENGRANAJE P50 DE 2 1/2"</t>
-  </si>
-  <si>
-    <t>313-5037-202</t>
-  </si>
-  <si>
-    <t>TROMPA P50 DE 5" X 4</t>
-  </si>
-  <si>
-    <t>313-8225-100</t>
-  </si>
-  <si>
-    <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
-  </si>
-  <si>
-    <t>SA-WLA632-3306F</t>
-  </si>
-  <si>
-    <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
-  </si>
-  <si>
-    <t>SA-632-7800A</t>
-  </si>
-  <si>
-    <t>BOMBA PRECARGA SAUER SERIE 90-75 - 14cc</t>
-  </si>
-  <si>
-    <t>SOL - 2564</t>
-  </si>
-  <si>
-    <t>FILT-10MZ10</t>
-  </si>
-  <si>
-    <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 10"</t>
-  </si>
-  <si>
-    <t>FILT-MZ10</t>
-  </si>
-  <si>
-    <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 7"</t>
-  </si>
-  <si>
-    <t>934332T</t>
-  </si>
-  <si>
-    <t>FILTRO TRICEPTOR SILICA GEL 10"</t>
-  </si>
-  <si>
-    <t>SOL - 2595</t>
-  </si>
-  <si>
-    <t>INSUMOS DEPOSITO</t>
-  </si>
-  <si>
-    <t>INSUMOS PARA DEPOSITO - GENERICO</t>
-  </si>
-  <si>
-    <t>SOL - 2620</t>
-  </si>
-  <si>
-    <t>01104</t>
-  </si>
-  <si>
-    <t>2026-10</t>
-  </si>
-  <si>
-    <t>INSUMOS VARIOS 10.5%</t>
-  </si>
-  <si>
-    <t>INSUMOS VARIOS 10.5% - GENERICO</t>
+    <t>Recepcion deposito</t>
+  </si>
+  <si>
+    <t>2-231-N70</t>
+  </si>
+  <si>
+    <t>ORING 2-231 D70 DI 66.27 X DE 73.33 ESP 3.53</t>
+  </si>
+  <si>
+    <t>2-332-N70</t>
+  </si>
+  <si>
+    <t>ORING 2-332 D70 DI 59.69 X DE 70.35 ESP 5.33</t>
+  </si>
+  <si>
+    <t>2-339-N70</t>
+  </si>
+  <si>
+    <t>ORING 2-339 D70 DI 81.92 X DE 92.58 ESP 5.33</t>
   </si>
 </sst>
 </file>
@@ -659,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1068,7 +1050,7 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -1077,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
@@ -1124,7 +1106,7 @@
         <v>21</v>
       </c>
       <c r="E9">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -1133,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
@@ -1180,7 +1162,7 @@
         <v>21</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -1189,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I10" t="s">
         <v>22</v>
@@ -1236,7 +1218,7 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -1245,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I11" t="s">
         <v>22</v>
@@ -1292,7 +1274,7 @@
         <v>21</v>
       </c>
       <c r="E12">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1301,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
@@ -1348,7 +1330,7 @@
         <v>52</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1357,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
@@ -1366,13 +1348,13 @@
         <v>53</v>
       </c>
       <c r="K13" t="s">
+        <v>33</v>
+      </c>
+      <c r="L13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" t="s">
         <v>54</v>
-      </c>
-      <c r="L13" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13" t="s">
-        <v>55</v>
       </c>
       <c r="N13" t="s">
         <v>21</v>
@@ -1392,19 +1374,19 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1413,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
@@ -1422,13 +1404,13 @@
         <v>53</v>
       </c>
       <c r="K14" t="s">
+        <v>33</v>
+      </c>
+      <c r="L14" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" t="s">
         <v>54</v>
-      </c>
-      <c r="L14" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" t="s">
-        <v>55</v>
       </c>
       <c r="N14" t="s">
         <v>21</v>
@@ -1448,19 +1430,19 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1469,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
@@ -1478,13 +1460,13 @@
         <v>53</v>
       </c>
       <c r="K15" t="s">
+        <v>33</v>
+      </c>
+      <c r="L15" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" t="s">
         <v>54</v>
-      </c>
-      <c r="L15" t="s">
-        <v>25</v>
-      </c>
-      <c r="M15" t="s">
-        <v>55</v>
       </c>
       <c r="N15" t="s">
         <v>21</v>
@@ -1504,19 +1486,19 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
@@ -1525,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
@@ -1534,13 +1516,13 @@
         <v>53</v>
       </c>
       <c r="K16" t="s">
+        <v>33</v>
+      </c>
+      <c r="L16" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" t="s">
         <v>54</v>
-      </c>
-      <c r="L16" t="s">
-        <v>25</v>
-      </c>
-      <c r="M16" t="s">
-        <v>55</v>
       </c>
       <c r="N16" t="s">
         <v>21</v>
@@ -1560,19 +1542,19 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F17" t="s">
         <v>21</v>
@@ -1581,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
@@ -1590,13 +1572,13 @@
         <v>53</v>
       </c>
       <c r="K17" t="s">
+        <v>33</v>
+      </c>
+      <c r="L17" t="s">
+        <v>25</v>
+      </c>
+      <c r="M17" t="s">
         <v>54</v>
-      </c>
-      <c r="L17" t="s">
-        <v>25</v>
-      </c>
-      <c r="M17" t="s">
-        <v>55</v>
       </c>
       <c r="N17" t="s">
         <v>21</v>
@@ -1616,19 +1598,19 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="F18" t="s">
         <v>21</v>
@@ -1637,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="I18" t="s">
         <v>22</v>
@@ -1646,13 +1628,13 @@
         <v>53</v>
       </c>
       <c r="K18" t="s">
+        <v>33</v>
+      </c>
+      <c r="L18" t="s">
+        <v>25</v>
+      </c>
+      <c r="M18" t="s">
         <v>54</v>
-      </c>
-      <c r="L18" t="s">
-        <v>25</v>
-      </c>
-      <c r="M18" t="s">
-        <v>55</v>
       </c>
       <c r="N18" t="s">
         <v>21</v>
@@ -1672,19 +1654,19 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="E19">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F19" t="s">
         <v>21</v>
@@ -1693,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
@@ -1702,13 +1684,13 @@
         <v>53</v>
       </c>
       <c r="K19" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L19" t="s">
         <v>25</v>
       </c>
       <c r="M19" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="N19" t="s">
         <v>21</v>
@@ -1728,19 +1710,19 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="E20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -1749,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
@@ -1758,13 +1740,13 @@
         <v>53</v>
       </c>
       <c r="K20" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L20" t="s">
         <v>25</v>
       </c>
       <c r="M20" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="N20" t="s">
         <v>21</v>
@@ -1784,19 +1766,19 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="E21">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F21" t="s">
         <v>21</v>
@@ -1805,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
@@ -1814,13 +1796,13 @@
         <v>53</v>
       </c>
       <c r="K21" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L21" t="s">
         <v>25</v>
       </c>
       <c r="M21" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="N21" t="s">
         <v>21</v>
@@ -1840,16 +1822,16 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="E22">
         <v>12</v>
@@ -1870,13 +1852,13 @@
         <v>53</v>
       </c>
       <c r="K22" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L22" t="s">
         <v>25</v>
       </c>
       <c r="M22" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="N22" t="s">
         <v>21</v>
@@ -1896,19 +1878,19 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E23">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F23" t="s">
         <v>21</v>
@@ -1917,13 +1899,13 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I23" t="s">
         <v>22</v>
       </c>
       <c r="J23" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="K23" t="s">
         <v>33</v>
@@ -1932,7 +1914,7 @@
         <v>25</v>
       </c>
       <c r="M23" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="N23" t="s">
         <v>21</v>
@@ -1952,19 +1934,19 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
         <v>77</v>
       </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
       <c r="C24" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="F24" t="s">
         <v>21</v>
@@ -1973,13 +1955,13 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
       </c>
       <c r="J24" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="K24" t="s">
         <v>33</v>
@@ -1988,7 +1970,7 @@
         <v>25</v>
       </c>
       <c r="M24" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="N24" t="s">
         <v>21</v>
@@ -2008,19 +1990,19 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" t="s">
         <v>79</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>80</v>
       </c>
-      <c r="C25" t="s">
-        <v>68</v>
-      </c>
       <c r="D25" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>250</v>
       </c>
       <c r="F25" t="s">
         <v>21</v>
@@ -2029,22 +2011,22 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>5</v>
+        <v>250</v>
       </c>
       <c r="I25" t="s">
         <v>22</v>
       </c>
       <c r="J25" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="K25" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="L25" t="s">
         <v>25</v>
       </c>
       <c r="M25" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="N25" t="s">
         <v>21</v>
@@ -2064,19 +2046,19 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" t="s">
         <v>81</v>
       </c>
-      <c r="D26" t="s">
-        <v>21</v>
-      </c>
       <c r="E26">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="F26" t="s">
         <v>21</v>
@@ -2085,22 +2067,22 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="I26" t="s">
         <v>22</v>
       </c>
       <c r="J26" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="K26" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="L26" t="s">
         <v>25</v>
       </c>
       <c r="M26" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="N26" t="s">
         <v>21</v>
@@ -2120,43 +2102,43 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27">
+        <v>500</v>
+      </c>
+      <c r="F27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>500</v>
+      </c>
+      <c r="I27" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" t="s">
+        <v>75</v>
+      </c>
+      <c r="K27" t="s">
         <v>82</v>
       </c>
-      <c r="B27" t="s">
+      <c r="L27" t="s">
+        <v>25</v>
+      </c>
+      <c r="M27" t="s">
         <v>83</v>
-      </c>
-      <c r="C27" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>10</v>
-      </c>
-      <c r="I27" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" t="s">
-        <v>53</v>
-      </c>
-      <c r="K27" t="s">
-        <v>24</v>
-      </c>
-      <c r="L27" t="s">
-        <v>25</v>
-      </c>
-      <c r="M27" t="s">
-        <v>26</v>
       </c>
       <c r="N27" t="s">
         <v>21</v>
@@ -2176,19 +2158,19 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" t="s">
         <v>81</v>
       </c>
-      <c r="D28" t="s">
-        <v>21</v>
-      </c>
       <c r="E28">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="F28" t="s">
         <v>21</v>
@@ -2197,22 +2179,22 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I28" t="s">
         <v>22</v>
       </c>
       <c r="J28" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="K28" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="L28" t="s">
         <v>25</v>
       </c>
       <c r="M28" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="N28" t="s">
         <v>21</v>
@@ -2227,174 +2209,6 @@
         <v>21</v>
       </c>
       <c r="R28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>86</v>
-      </c>
-      <c r="B29" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29">
-        <v>12</v>
-      </c>
-      <c r="F29" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>12</v>
-      </c>
-      <c r="I29" t="s">
-        <v>22</v>
-      </c>
-      <c r="J29" t="s">
-        <v>53</v>
-      </c>
-      <c r="K29" t="s">
-        <v>24</v>
-      </c>
-      <c r="L29" t="s">
-        <v>25</v>
-      </c>
-      <c r="M29" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" t="s">
-        <v>21</v>
-      </c>
-      <c r="O29" t="s">
-        <v>21</v>
-      </c>
-      <c r="P29" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>21</v>
-      </c>
-      <c r="R29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>89</v>
-      </c>
-      <c r="B30" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" t="s">
-        <v>91</v>
-      </c>
-      <c r="D30" t="s">
-        <v>92</v>
-      </c>
-      <c r="E30">
-        <v>96</v>
-      </c>
-      <c r="F30" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>96</v>
-      </c>
-      <c r="I30" t="s">
-        <v>22</v>
-      </c>
-      <c r="J30" t="s">
-        <v>93</v>
-      </c>
-      <c r="K30" t="s">
-        <v>33</v>
-      </c>
-      <c r="L30" t="s">
-        <v>25</v>
-      </c>
-      <c r="M30" t="s">
-        <v>26</v>
-      </c>
-      <c r="N30" t="s">
-        <v>21</v>
-      </c>
-      <c r="O30" t="s">
-        <v>21</v>
-      </c>
-      <c r="P30" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>21</v>
-      </c>
-      <c r="R30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>94</v>
-      </c>
-      <c r="B31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" t="s">
-        <v>91</v>
-      </c>
-      <c r="D31" t="s">
-        <v>92</v>
-      </c>
-      <c r="E31">
-        <v>24</v>
-      </c>
-      <c r="F31" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>24</v>
-      </c>
-      <c r="I31" t="s">
-        <v>22</v>
-      </c>
-      <c r="J31" t="s">
-        <v>93</v>
-      </c>
-      <c r="K31" t="s">
-        <v>33</v>
-      </c>
-      <c r="L31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M31" t="s">
-        <v>26</v>
-      </c>
-      <c r="N31" t="s">
-        <v>21</v>
-      </c>
-      <c r="O31" t="s">
-        <v>21</v>
-      </c>
-      <c r="P31" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>21</v>
-      </c>
-      <c r="R31" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA0FAB0C-2E72-4042-BE8D-EEF0C780E51E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C7764F5-C4E4-422D-BC5B-9E73934B1428}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="99">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -127,30 +127,30 @@
     <t>Deposito NQN</t>
   </si>
   <si>
+    <t>C5OX-24-20F</t>
+  </si>
+  <si>
+    <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
+  </si>
+  <si>
+    <t>SOL - 2384</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
     <t>391-2882-051</t>
   </si>
   <si>
     <t>CUERDA P30 Y P50</t>
   </si>
   <si>
-    <t>SOL - 2384</t>
-  </si>
-  <si>
-    <t>2026-07</t>
-  </si>
-  <si>
     <t>391-2884-021P</t>
   </si>
   <si>
     <t>SELLO GOMA SQUARE GASKET 50-25</t>
   </si>
   <si>
-    <t>C5OX-24-20F</t>
-  </si>
-  <si>
-    <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
-  </si>
-  <si>
     <t>FILT-D-AB-2</t>
   </si>
   <si>
@@ -256,40 +256,67 @@
     <t>INSUMOS VARIOS 10.5% - GENERICO</t>
   </si>
   <si>
-    <t>2-230-N70</t>
-  </si>
-  <si>
-    <t>ORING 2-230 D70 DI 63.09 X DE 70.15 ESP 3.53</t>
-  </si>
-  <si>
-    <t>SOL - 2629</t>
-  </si>
-  <si>
-    <t>01039</t>
-  </si>
-  <si>
-    <t>HIDROIL SRL</t>
-  </si>
-  <si>
-    <t>Recepcion deposito</t>
-  </si>
-  <si>
-    <t>2-231-N70</t>
-  </si>
-  <si>
-    <t>ORING 2-231 D70 DI 66.27 X DE 73.33 ESP 3.53</t>
-  </si>
-  <si>
-    <t>2-332-N70</t>
-  </si>
-  <si>
-    <t>ORING 2-332 D70 DI 59.69 X DE 70.35 ESP 5.33</t>
-  </si>
-  <si>
-    <t>2-339-N70</t>
-  </si>
-  <si>
-    <t>ORING 2-339 D70 DI 81.92 X DE 92.58 ESP 5.33</t>
+    <t>BOMBA HCA A ENGRANAJES</t>
+  </si>
+  <si>
+    <t>BOMBA HIDRAULICA A ENGRANAJES - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2632</t>
+  </si>
+  <si>
+    <t>01107</t>
+  </si>
+  <si>
+    <t>PFQ909R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-60 BAR C/GLICERINA</t>
+  </si>
+  <si>
+    <t>SOL - 2634</t>
+  </si>
+  <si>
+    <t>PFQ912R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-300 BAR C/GLICERINA</t>
+  </si>
+  <si>
+    <t>2-012-N70</t>
+  </si>
+  <si>
+    <t>ORING 2-012 D70 DI 9.25 X DE 12.81 ESP 1.78</t>
+  </si>
+  <si>
+    <t>2-015-N70</t>
+  </si>
+  <si>
+    <t>ORING 2-015 D70 DI 14.00 X DE 17.56 ESP 1.78</t>
+  </si>
+  <si>
+    <t>2-018-N70</t>
+  </si>
+  <si>
+    <t>ORING 2-018 D70 DI 18.77 X DE 22.33 ESP 1.78</t>
+  </si>
+  <si>
+    <t>2-219-N70</t>
+  </si>
+  <si>
+    <t>ORING 2-219 D70 DI 32.92 X DE 39.98 ESP 3.53</t>
+  </si>
+  <si>
+    <t>2-224-N70</t>
+  </si>
+  <si>
+    <t>ORING 2-224 D70 DI 44.04 X DE 51.10 ESP 3.53</t>
+  </si>
+  <si>
+    <t>2-240-N90</t>
+  </si>
+  <si>
+    <t>ORING 2-240 D90 DI 94.84 X DE 101.90 ESP 3.53</t>
   </si>
 </sst>
 </file>
@@ -641,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1050,7 +1077,7 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -1059,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
@@ -1106,7 +1133,7 @@
         <v>21</v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -1115,7 +1142,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
@@ -1162,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -1171,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="I10" t="s">
         <v>22</v>
@@ -1598,10 +1625,10 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
         <v>51</v>
@@ -2002,7 +2029,7 @@
         <v>81</v>
       </c>
       <c r="E25">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="F25" t="s">
         <v>21</v>
@@ -2011,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="I25" t="s">
         <v>22</v>
@@ -2020,13 +2047,13 @@
         <v>75</v>
       </c>
       <c r="K25" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="L25" t="s">
         <v>25</v>
       </c>
       <c r="M25" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="N25" t="s">
         <v>21</v>
@@ -2046,19 +2073,19 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" t="s">
         <v>84</v>
       </c>
-      <c r="B26" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" t="s">
-        <v>80</v>
-      </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="E26">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
         <v>21</v>
@@ -2067,7 +2094,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="I26" t="s">
         <v>22</v>
@@ -2076,13 +2103,13 @@
         <v>75</v>
       </c>
       <c r="K26" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="L26" t="s">
         <v>25</v>
       </c>
       <c r="M26" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="N26" t="s">
         <v>21</v>
@@ -2102,19 +2129,19 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" t="s">
         <v>86</v>
       </c>
-      <c r="B27" t="s">
-        <v>87</v>
-      </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="E27">
-        <v>500</v>
+        <v>5</v>
       </c>
       <c r="F27" t="s">
         <v>21</v>
@@ -2123,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>500</v>
+        <v>5</v>
       </c>
       <c r="I27" t="s">
         <v>22</v>
@@ -2132,13 +2159,13 @@
         <v>75</v>
       </c>
       <c r="K27" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="L27" t="s">
         <v>25</v>
       </c>
       <c r="M27" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="N27" t="s">
         <v>21</v>
@@ -2158,19 +2185,19 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" t="s">
         <v>88</v>
       </c>
-      <c r="B28" t="s">
-        <v>89</v>
-      </c>
       <c r="C28" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="E28">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F28" t="s">
         <v>21</v>
@@ -2179,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I28" t="s">
         <v>22</v>
@@ -2188,13 +2215,13 @@
         <v>75</v>
       </c>
       <c r="K28" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="L28" t="s">
         <v>25</v>
       </c>
       <c r="M28" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="N28" t="s">
         <v>21</v>
@@ -2209,6 +2236,286 @@
         <v>21</v>
       </c>
       <c r="R28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29">
+        <v>100</v>
+      </c>
+      <c r="F29" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>100</v>
+      </c>
+      <c r="I29" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" t="s">
+        <v>75</v>
+      </c>
+      <c r="K29" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" t="s">
+        <v>25</v>
+      </c>
+      <c r="M29" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" t="s">
+        <v>21</v>
+      </c>
+      <c r="O29" t="s">
+        <v>21</v>
+      </c>
+      <c r="P29" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>21</v>
+      </c>
+      <c r="R29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30">
+        <v>100</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>100</v>
+      </c>
+      <c r="I30" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" t="s">
+        <v>75</v>
+      </c>
+      <c r="K30" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" t="s">
+        <v>25</v>
+      </c>
+      <c r="M30" t="s">
+        <v>26</v>
+      </c>
+      <c r="N30" t="s">
+        <v>21</v>
+      </c>
+      <c r="O30" t="s">
+        <v>21</v>
+      </c>
+      <c r="P30" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>21</v>
+      </c>
+      <c r="R30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31">
+        <v>100</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>100</v>
+      </c>
+      <c r="I31" t="s">
+        <v>22</v>
+      </c>
+      <c r="J31" t="s">
+        <v>75</v>
+      </c>
+      <c r="K31" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" t="s">
+        <v>25</v>
+      </c>
+      <c r="M31" t="s">
+        <v>26</v>
+      </c>
+      <c r="N31" t="s">
+        <v>21</v>
+      </c>
+      <c r="O31" t="s">
+        <v>21</v>
+      </c>
+      <c r="P31" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>21</v>
+      </c>
+      <c r="R31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32">
+        <v>100</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>100</v>
+      </c>
+      <c r="I32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" t="s">
+        <v>75</v>
+      </c>
+      <c r="K32" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" t="s">
+        <v>25</v>
+      </c>
+      <c r="M32" t="s">
+        <v>26</v>
+      </c>
+      <c r="N32" t="s">
+        <v>21</v>
+      </c>
+      <c r="O32" t="s">
+        <v>21</v>
+      </c>
+      <c r="P32" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>21</v>
+      </c>
+      <c r="R32" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" t="s">
+        <v>84</v>
+      </c>
+      <c r="D33" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33">
+        <v>700</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>700</v>
+      </c>
+      <c r="I33" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" t="s">
+        <v>75</v>
+      </c>
+      <c r="K33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" t="s">
+        <v>25</v>
+      </c>
+      <c r="M33" t="s">
+        <v>26</v>
+      </c>
+      <c r="N33" t="s">
+        <v>21</v>
+      </c>
+      <c r="O33" t="s">
+        <v>21</v>
+      </c>
+      <c r="P33" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>21</v>
+      </c>
+      <c r="R33" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,19 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C7764F5-C4E4-422D-BC5B-9E73934B1428}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FABD283-1C30-40D0-BADA-78EED9B8C43E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="69">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -127,22 +134,58 @@
     <t>Deposito NQN</t>
   </si>
   <si>
-    <t>C5OX-24-20F</t>
-  </si>
-  <si>
-    <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
-  </si>
-  <si>
-    <t>SOL - 2384</t>
-  </si>
-  <si>
-    <t>2026-07</t>
-  </si>
-  <si>
-    <t>391-2882-051</t>
-  </si>
-  <si>
-    <t>CUERDA P30 Y P50</t>
+    <t>MA-310</t>
+  </si>
+  <si>
+    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
+  </si>
+  <si>
+    <t>SOL - 2493</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>FILT-D-AB-2</t>
+  </si>
+  <si>
+    <t>FILTRO AIRE RESP DESECANTE</t>
+  </si>
+  <si>
+    <t>313-1135-194</t>
+  </si>
+  <si>
+    <t>EJE POSTIZO P50 Z14</t>
+  </si>
+  <si>
+    <t>SOL - 2537</t>
+  </si>
+  <si>
+    <t>01049</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>Deposito Nqn 2</t>
+  </si>
+  <si>
+    <t>313-2825-000</t>
+  </si>
+  <si>
+    <t>ENGRANAJE P50 DE 2 1/2"</t>
+  </si>
+  <si>
+    <t>313-5037-202</t>
+  </si>
+  <si>
+    <t>TROMPA P50 DE 5" X 4</t>
+  </si>
+  <si>
+    <t>313-8225-100</t>
+  </si>
+  <si>
+    <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
   </si>
   <si>
     <t>391-2884-021P</t>
@@ -151,66 +194,12 @@
     <t>SELLO GOMA SQUARE GASKET 50-25</t>
   </si>
   <si>
-    <t>FILT-D-AB-2</t>
-  </si>
-  <si>
-    <t>FILTRO AIRE RESP DESECANTE</t>
-  </si>
-  <si>
-    <t>SOL - 2493</t>
-  </si>
-  <si>
-    <t>2026-08</t>
-  </si>
-  <si>
-    <t>MA-310</t>
-  </si>
-  <si>
-    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
-  </si>
-  <si>
     <t>SA-WLA632-3306F</t>
   </si>
   <si>
     <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
   </si>
   <si>
-    <t>SOL - 2537</t>
-  </si>
-  <si>
-    <t>01049</t>
-  </si>
-  <si>
-    <t>2026-09</t>
-  </si>
-  <si>
-    <t>Deposito Nqn 2</t>
-  </si>
-  <si>
-    <t>313-1135-194</t>
-  </si>
-  <si>
-    <t>EJE POSTIZO P50 Z14</t>
-  </si>
-  <si>
-    <t>313-2825-000</t>
-  </si>
-  <si>
-    <t>ENGRANAJE P50 DE 2 1/2"</t>
-  </si>
-  <si>
-    <t>313-5037-202</t>
-  </si>
-  <si>
-    <t>TROMPA P50 DE 5" X 4</t>
-  </si>
-  <si>
-    <t>313-8225-100</t>
-  </si>
-  <si>
-    <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
-  </si>
-  <si>
     <t>SOL - 2564</t>
   </si>
   <si>
@@ -226,15 +215,6 @@
     <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 7"</t>
   </si>
   <si>
-    <t>934332T</t>
-  </si>
-  <si>
-    <t>FILTRO TRICEPTOR SILICA GEL 10"</t>
-  </si>
-  <si>
-    <t>SOL - 2595</t>
-  </si>
-  <si>
     <t>INSUMOS DEPOSITO</t>
   </si>
   <si>
@@ -254,69 +234,6 @@
   </si>
   <si>
     <t>INSUMOS VARIOS 10.5% - GENERICO</t>
-  </si>
-  <si>
-    <t>BOMBA HCA A ENGRANAJES</t>
-  </si>
-  <si>
-    <t>BOMBA HIDRAULICA A ENGRANAJES - GENERICO</t>
-  </si>
-  <si>
-    <t>SOL - 2632</t>
-  </si>
-  <si>
-    <t>01107</t>
-  </si>
-  <si>
-    <t>PFQ909R3R1</t>
-  </si>
-  <si>
-    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-60 BAR C/GLICERINA</t>
-  </si>
-  <si>
-    <t>SOL - 2634</t>
-  </si>
-  <si>
-    <t>PFQ912R3R1</t>
-  </si>
-  <si>
-    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-300 BAR C/GLICERINA</t>
-  </si>
-  <si>
-    <t>2-012-N70</t>
-  </si>
-  <si>
-    <t>ORING 2-012 D70 DI 9.25 X DE 12.81 ESP 1.78</t>
-  </si>
-  <si>
-    <t>2-015-N70</t>
-  </si>
-  <si>
-    <t>ORING 2-015 D70 DI 14.00 X DE 17.56 ESP 1.78</t>
-  </si>
-  <si>
-    <t>2-018-N70</t>
-  </si>
-  <si>
-    <t>ORING 2-018 D70 DI 18.77 X DE 22.33 ESP 1.78</t>
-  </si>
-  <si>
-    <t>2-219-N70</t>
-  </si>
-  <si>
-    <t>ORING 2-219 D70 DI 32.92 X DE 39.98 ESP 3.53</t>
-  </si>
-  <si>
-    <t>2-224-N70</t>
-  </si>
-  <si>
-    <t>ORING 2-224 D70 DI 44.04 X DE 51.10 ESP 3.53</t>
-  </si>
-  <si>
-    <t>2-240-N90</t>
-  </si>
-  <si>
-    <t>ORING 2-240 D90 DI 94.84 X DE 101.90 ESP 3.53</t>
   </si>
 </sst>
 </file>
@@ -668,7 +585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1077,7 +994,7 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -1133,7 +1050,7 @@
         <v>21</v>
       </c>
       <c r="E9">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -1142,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
@@ -1183,13 +1100,13 @@
         <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -1198,22 +1115,22 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I10" t="s">
         <v>22</v>
       </c>
       <c r="J10" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="K10" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L10" t="s">
         <v>25</v>
       </c>
       <c r="M10" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="N10" t="s">
         <v>21</v>
@@ -1233,16 +1150,16 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
         <v>43</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
         <v>44</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" t="s">
-        <v>21</v>
       </c>
       <c r="E11">
         <v>6</v>
@@ -1260,16 +1177,16 @@
         <v>22</v>
       </c>
       <c r="J11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" t="s">
         <v>46</v>
-      </c>
-      <c r="K11" t="s">
-        <v>24</v>
-      </c>
-      <c r="L11" t="s">
-        <v>25</v>
-      </c>
-      <c r="M11" t="s">
-        <v>26</v>
       </c>
       <c r="N11" t="s">
         <v>21</v>
@@ -1289,43 +1206,43 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>6</v>
+      </c>
+      <c r="I12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" t="s">
         <v>45</v>
       </c>
-      <c r="D12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12">
-        <v>20</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>10</v>
-      </c>
-      <c r="I12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
+        <v>33</v>
+      </c>
+      <c r="L12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" t="s">
         <v>46</v>
-      </c>
-      <c r="K12" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" t="s">
-        <v>26</v>
       </c>
       <c r="N12" t="s">
         <v>21</v>
@@ -1345,19 +1262,19 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1366,13 +1283,13 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
       </c>
       <c r="J13" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="K13" t="s">
         <v>33</v>
@@ -1381,7 +1298,7 @@
         <v>25</v>
       </c>
       <c r="M13" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="N13" t="s">
         <v>21</v>
@@ -1401,19 +1318,19 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1422,13 +1339,13 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
       </c>
       <c r="J14" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="K14" t="s">
         <v>33</v>
@@ -1437,7 +1354,7 @@
         <v>25</v>
       </c>
       <c r="M14" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="N14" t="s">
         <v>21</v>
@@ -1457,19 +1374,19 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1478,13 +1395,13 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
       </c>
       <c r="J15" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="K15" t="s">
         <v>33</v>
@@ -1493,7 +1410,7 @@
         <v>25</v>
       </c>
       <c r="M15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="N15" t="s">
         <v>21</v>
@@ -1513,19 +1430,19 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
@@ -1534,22 +1451,22 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
       </c>
       <c r="J16" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="K16" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L16" t="s">
         <v>25</v>
       </c>
       <c r="M16" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N16" t="s">
         <v>21</v>
@@ -1569,19 +1486,19 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="E17">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
         <v>21</v>
@@ -1590,22 +1507,22 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
       </c>
       <c r="J17" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="K17" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L17" t="s">
         <v>25</v>
       </c>
       <c r="M17" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N17" t="s">
         <v>21</v>
@@ -1625,19 +1542,19 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="E18">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F18" t="s">
         <v>21</v>
@@ -1646,22 +1563,22 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="I18" t="s">
         <v>22</v>
       </c>
       <c r="J18" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="K18" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L18" t="s">
         <v>25</v>
       </c>
       <c r="M18" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N18" t="s">
         <v>21</v>
@@ -1681,19 +1598,19 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="E19">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="F19" t="s">
         <v>21</v>
@@ -1702,16 +1619,16 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
       </c>
       <c r="J19" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="K19" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L19" t="s">
         <v>25</v>
@@ -1737,19 +1654,19 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" t="s">
         <v>64</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" t="s">
         <v>65</v>
       </c>
-      <c r="C20" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" t="s">
-        <v>21</v>
-      </c>
       <c r="E20">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -1758,16 +1675,16 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
       </c>
       <c r="J20" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="K20" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L20" t="s">
         <v>25</v>
@@ -1788,734 +1705,6 @@
         <v>21</v>
       </c>
       <c r="R20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>66</v>
-      </c>
-      <c r="B21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21">
-        <v>30</v>
-      </c>
-      <c r="F21" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>30</v>
-      </c>
-      <c r="I21" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" t="s">
-        <v>53</v>
-      </c>
-      <c r="K21" t="s">
-        <v>24</v>
-      </c>
-      <c r="L21" t="s">
-        <v>25</v>
-      </c>
-      <c r="M21" t="s">
-        <v>26</v>
-      </c>
-      <c r="N21" t="s">
-        <v>21</v>
-      </c>
-      <c r="O21" t="s">
-        <v>21</v>
-      </c>
-      <c r="P21" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>21</v>
-      </c>
-      <c r="R21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22">
-        <v>12</v>
-      </c>
-      <c r="F22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>12</v>
-      </c>
-      <c r="I22" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" t="s">
-        <v>53</v>
-      </c>
-      <c r="K22" t="s">
-        <v>24</v>
-      </c>
-      <c r="L22" t="s">
-        <v>25</v>
-      </c>
-      <c r="M22" t="s">
-        <v>26</v>
-      </c>
-      <c r="N22" t="s">
-        <v>21</v>
-      </c>
-      <c r="O22" t="s">
-        <v>21</v>
-      </c>
-      <c r="P22" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>21</v>
-      </c>
-      <c r="R22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>71</v>
-      </c>
-      <c r="B23" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" t="s">
-        <v>74</v>
-      </c>
-      <c r="E23">
-        <v>96</v>
-      </c>
-      <c r="F23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>96</v>
-      </c>
-      <c r="I23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J23" t="s">
-        <v>75</v>
-      </c>
-      <c r="K23" t="s">
-        <v>33</v>
-      </c>
-      <c r="L23" t="s">
-        <v>25</v>
-      </c>
-      <c r="M23" t="s">
-        <v>26</v>
-      </c>
-      <c r="N23" t="s">
-        <v>21</v>
-      </c>
-      <c r="O23" t="s">
-        <v>21</v>
-      </c>
-      <c r="P23" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>21</v>
-      </c>
-      <c r="R23" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>76</v>
-      </c>
-      <c r="B24" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24">
-        <v>24</v>
-      </c>
-      <c r="F24" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>24</v>
-      </c>
-      <c r="I24" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" t="s">
-        <v>75</v>
-      </c>
-      <c r="K24" t="s">
-        <v>33</v>
-      </c>
-      <c r="L24" t="s">
-        <v>25</v>
-      </c>
-      <c r="M24" t="s">
-        <v>26</v>
-      </c>
-      <c r="N24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O24" t="s">
-        <v>21</v>
-      </c>
-      <c r="P24" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>21</v>
-      </c>
-      <c r="R24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>78</v>
-      </c>
-      <c r="B25" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="I25" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" t="s">
-        <v>75</v>
-      </c>
-      <c r="K25" t="s">
-        <v>33</v>
-      </c>
-      <c r="L25" t="s">
-        <v>25</v>
-      </c>
-      <c r="M25" t="s">
-        <v>34</v>
-      </c>
-      <c r="N25" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" t="s">
-        <v>21</v>
-      </c>
-      <c r="P25" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>21</v>
-      </c>
-      <c r="R25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>82</v>
-      </c>
-      <c r="B26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>10</v>
-      </c>
-      <c r="I26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" t="s">
-        <v>75</v>
-      </c>
-      <c r="K26" t="s">
-        <v>24</v>
-      </c>
-      <c r="L26" t="s">
-        <v>25</v>
-      </c>
-      <c r="M26" t="s">
-        <v>26</v>
-      </c>
-      <c r="N26" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" t="s">
-        <v>21</v>
-      </c>
-      <c r="P26" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>21</v>
-      </c>
-      <c r="R26" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>85</v>
-      </c>
-      <c r="B27" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D27" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>5</v>
-      </c>
-      <c r="I27" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" t="s">
-        <v>75</v>
-      </c>
-      <c r="K27" t="s">
-        <v>24</v>
-      </c>
-      <c r="L27" t="s">
-        <v>25</v>
-      </c>
-      <c r="M27" t="s">
-        <v>26</v>
-      </c>
-      <c r="N27" t="s">
-        <v>21</v>
-      </c>
-      <c r="O27" t="s">
-        <v>21</v>
-      </c>
-      <c r="P27" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>21</v>
-      </c>
-      <c r="R27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>87</v>
-      </c>
-      <c r="B28" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" t="s">
-        <v>84</v>
-      </c>
-      <c r="D28" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28">
-        <v>100</v>
-      </c>
-      <c r="F28" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>100</v>
-      </c>
-      <c r="I28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J28" t="s">
-        <v>75</v>
-      </c>
-      <c r="K28" t="s">
-        <v>24</v>
-      </c>
-      <c r="L28" t="s">
-        <v>25</v>
-      </c>
-      <c r="M28" t="s">
-        <v>26</v>
-      </c>
-      <c r="N28" t="s">
-        <v>21</v>
-      </c>
-      <c r="O28" t="s">
-        <v>21</v>
-      </c>
-      <c r="P28" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>21</v>
-      </c>
-      <c r="R28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>89</v>
-      </c>
-      <c r="B29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" t="s">
-        <v>84</v>
-      </c>
-      <c r="D29" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29">
-        <v>100</v>
-      </c>
-      <c r="F29" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>100</v>
-      </c>
-      <c r="I29" t="s">
-        <v>22</v>
-      </c>
-      <c r="J29" t="s">
-        <v>75</v>
-      </c>
-      <c r="K29" t="s">
-        <v>24</v>
-      </c>
-      <c r="L29" t="s">
-        <v>25</v>
-      </c>
-      <c r="M29" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" t="s">
-        <v>21</v>
-      </c>
-      <c r="O29" t="s">
-        <v>21</v>
-      </c>
-      <c r="P29" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>21</v>
-      </c>
-      <c r="R29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>91</v>
-      </c>
-      <c r="B30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30">
-        <v>100</v>
-      </c>
-      <c r="F30" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>100</v>
-      </c>
-      <c r="I30" t="s">
-        <v>22</v>
-      </c>
-      <c r="J30" t="s">
-        <v>75</v>
-      </c>
-      <c r="K30" t="s">
-        <v>24</v>
-      </c>
-      <c r="L30" t="s">
-        <v>25</v>
-      </c>
-      <c r="M30" t="s">
-        <v>26</v>
-      </c>
-      <c r="N30" t="s">
-        <v>21</v>
-      </c>
-      <c r="O30" t="s">
-        <v>21</v>
-      </c>
-      <c r="P30" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>21</v>
-      </c>
-      <c r="R30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>93</v>
-      </c>
-      <c r="B31" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31">
-        <v>100</v>
-      </c>
-      <c r="F31" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>100</v>
-      </c>
-      <c r="I31" t="s">
-        <v>22</v>
-      </c>
-      <c r="J31" t="s">
-        <v>75</v>
-      </c>
-      <c r="K31" t="s">
-        <v>24</v>
-      </c>
-      <c r="L31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M31" t="s">
-        <v>26</v>
-      </c>
-      <c r="N31" t="s">
-        <v>21</v>
-      </c>
-      <c r="O31" t="s">
-        <v>21</v>
-      </c>
-      <c r="P31" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>21</v>
-      </c>
-      <c r="R31" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>95</v>
-      </c>
-      <c r="B32" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" t="s">
-        <v>84</v>
-      </c>
-      <c r="D32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32">
-        <v>100</v>
-      </c>
-      <c r="F32" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>100</v>
-      </c>
-      <c r="I32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" t="s">
-        <v>75</v>
-      </c>
-      <c r="K32" t="s">
-        <v>24</v>
-      </c>
-      <c r="L32" t="s">
-        <v>25</v>
-      </c>
-      <c r="M32" t="s">
-        <v>26</v>
-      </c>
-      <c r="N32" t="s">
-        <v>21</v>
-      </c>
-      <c r="O32" t="s">
-        <v>21</v>
-      </c>
-      <c r="P32" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>21</v>
-      </c>
-      <c r="R32" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>97</v>
-      </c>
-      <c r="B33" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" t="s">
-        <v>84</v>
-      </c>
-      <c r="D33" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33">
-        <v>700</v>
-      </c>
-      <c r="F33" t="s">
-        <v>21</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>700</v>
-      </c>
-      <c r="I33" t="s">
-        <v>22</v>
-      </c>
-      <c r="J33" t="s">
-        <v>75</v>
-      </c>
-      <c r="K33" t="s">
-        <v>24</v>
-      </c>
-      <c r="L33" t="s">
-        <v>25</v>
-      </c>
-      <c r="M33" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" t="s">
-        <v>21</v>
-      </c>
-      <c r="O33" t="s">
-        <v>21</v>
-      </c>
-      <c r="P33" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>21</v>
-      </c>
-      <c r="R33" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FABD283-1C30-40D0-BADA-78EED9B8C43E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0927E906-1184-49E9-9107-5B25F138BA55}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="62">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -152,54 +152,54 @@
     <t>FILTRO AIRE RESP DESECANTE</t>
   </si>
   <si>
+    <t>313-5037-202</t>
+  </si>
+  <si>
+    <t>TROMPA P50 DE 5" X 4</t>
+  </si>
+  <si>
+    <t>SOL - 2537</t>
+  </si>
+  <si>
+    <t>01049</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>Deposito Nqn 2</t>
+  </si>
+  <si>
+    <t>313-8225-100</t>
+  </si>
+  <si>
+    <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
+  </si>
+  <si>
+    <t>391-2884-021P</t>
+  </si>
+  <si>
+    <t>SELLO GOMA SQUARE GASKET 50-25</t>
+  </si>
+  <si>
+    <t>SA-WLA632-3306F</t>
+  </si>
+  <si>
+    <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
+  </si>
+  <si>
+    <t>313-2825-000</t>
+  </si>
+  <si>
+    <t>ENGRANAJE P50 DE 2 1/2"</t>
+  </si>
+  <si>
     <t>313-1135-194</t>
   </si>
   <si>
     <t>EJE POSTIZO P50 Z14</t>
   </si>
   <si>
-    <t>SOL - 2537</t>
-  </si>
-  <si>
-    <t>01049</t>
-  </si>
-  <si>
-    <t>2026-09</t>
-  </si>
-  <si>
-    <t>Deposito Nqn 2</t>
-  </si>
-  <si>
-    <t>313-2825-000</t>
-  </si>
-  <si>
-    <t>ENGRANAJE P50 DE 2 1/2"</t>
-  </si>
-  <si>
-    <t>313-5037-202</t>
-  </si>
-  <si>
-    <t>TROMPA P50 DE 5" X 4</t>
-  </si>
-  <si>
-    <t>313-8225-100</t>
-  </si>
-  <si>
-    <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
-  </si>
-  <si>
-    <t>391-2884-021P</t>
-  </si>
-  <si>
-    <t>SELLO GOMA SQUARE GASKET 50-25</t>
-  </si>
-  <si>
-    <t>SA-WLA632-3306F</t>
-  </si>
-  <si>
-    <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
-  </si>
-  <si>
     <t>SOL - 2564</t>
   </si>
   <si>
@@ -213,27 +213,6 @@
   </si>
   <si>
     <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 7"</t>
-  </si>
-  <si>
-    <t>INSUMOS DEPOSITO</t>
-  </si>
-  <si>
-    <t>INSUMOS PARA DEPOSITO - GENERICO</t>
-  </si>
-  <si>
-    <t>SOL - 2620</t>
-  </si>
-  <si>
-    <t>01104</t>
-  </si>
-  <si>
-    <t>2026-10</t>
-  </si>
-  <si>
-    <t>INSUMOS VARIOS 10.5%</t>
-  </si>
-  <si>
-    <t>INSUMOS VARIOS 10.5% - GENERICO</t>
   </si>
 </sst>
 </file>
@@ -585,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -714,7 +693,7 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
@@ -723,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
@@ -882,7 +861,7 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
@@ -891,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I6" t="s">
         <v>22</v>
@@ -1106,7 +1085,7 @@
         <v>44</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -1115,7 +1094,7 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I10" t="s">
         <v>22</v>
@@ -1162,7 +1141,7 @@
         <v>44</v>
       </c>
       <c r="E11">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -1171,7 +1150,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I11" t="s">
         <v>22</v>
@@ -1218,7 +1197,7 @@
         <v>44</v>
       </c>
       <c r="E12">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1227,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
@@ -1274,7 +1253,7 @@
         <v>44</v>
       </c>
       <c r="E13">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1283,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
@@ -1330,7 +1309,7 @@
         <v>44</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1339,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
@@ -1386,7 +1365,7 @@
         <v>44</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1395,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
@@ -1593,118 +1572,6 @@
         <v>21</v>
       </c>
       <c r="R18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" t="s">
-        <v>65</v>
-      </c>
-      <c r="E19">
-        <v>96</v>
-      </c>
-      <c r="F19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>96</v>
-      </c>
-      <c r="I19" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" t="s">
-        <v>66</v>
-      </c>
-      <c r="K19" t="s">
-        <v>33</v>
-      </c>
-      <c r="L19" t="s">
-        <v>25</v>
-      </c>
-      <c r="M19" t="s">
-        <v>26</v>
-      </c>
-      <c r="N19" t="s">
-        <v>21</v>
-      </c>
-      <c r="O19" t="s">
-        <v>21</v>
-      </c>
-      <c r="P19" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>21</v>
-      </c>
-      <c r="R19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20">
-        <v>24</v>
-      </c>
-      <c r="F20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>24</v>
-      </c>
-      <c r="I20" t="s">
-        <v>22</v>
-      </c>
-      <c r="J20" t="s">
-        <v>66</v>
-      </c>
-      <c r="K20" t="s">
-        <v>33</v>
-      </c>
-      <c r="L20" t="s">
-        <v>25</v>
-      </c>
-      <c r="M20" t="s">
-        <v>26</v>
-      </c>
-      <c r="N20" t="s">
-        <v>21</v>
-      </c>
-      <c r="O20" t="s">
-        <v>21</v>
-      </c>
-      <c r="P20" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>21</v>
-      </c>
-      <c r="R20" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0927E906-1184-49E9-9107-5B25F138BA55}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{430E501A-83F0-4EE9-82F7-4E3BE36CAA1E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="87">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -152,24 +152,36 @@
     <t>FILTRO AIRE RESP DESECANTE</t>
   </si>
   <si>
+    <t>313-1135-194</t>
+  </si>
+  <si>
+    <t>EJE POSTIZO P50 Z14</t>
+  </si>
+  <si>
+    <t>SOL - 2537</t>
+  </si>
+  <si>
+    <t>01049</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>Deposito Nqn 2</t>
+  </si>
+  <si>
+    <t>313-2825-000</t>
+  </si>
+  <si>
+    <t>ENGRANAJE P50 DE 2 1/2"</t>
+  </si>
+  <si>
     <t>313-5037-202</t>
   </si>
   <si>
     <t>TROMPA P50 DE 5" X 4</t>
   </si>
   <si>
-    <t>SOL - 2537</t>
-  </si>
-  <si>
-    <t>01049</t>
-  </si>
-  <si>
-    <t>2026-09</t>
-  </si>
-  <si>
-    <t>Deposito Nqn 2</t>
-  </si>
-  <si>
     <t>313-8225-100</t>
   </si>
   <si>
@@ -188,31 +200,94 @@
     <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
   </si>
   <si>
-    <t>313-2825-000</t>
-  </si>
-  <si>
-    <t>ENGRANAJE P50 DE 2 1/2"</t>
-  </si>
-  <si>
-    <t>313-1135-194</t>
-  </si>
-  <si>
-    <t>EJE POSTIZO P50 Z14</t>
+    <t>FILT-10MZ10</t>
+  </si>
+  <si>
+    <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 10"</t>
   </si>
   <si>
     <t>SOL - 2564</t>
   </si>
   <si>
-    <t>FILT-10MZ10</t>
-  </si>
-  <si>
-    <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 10"</t>
-  </si>
-  <si>
     <t>FILT-MZ10</t>
   </si>
   <si>
     <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 7"</t>
+  </si>
+  <si>
+    <t>FILT-MZ3</t>
+  </si>
+  <si>
+    <t>ELEMENTO FILTRO HIDRAULICO 3MIC SPIN-ON LARGO 7"</t>
+  </si>
+  <si>
+    <t>2-212-N90</t>
+  </si>
+  <si>
+    <t>ORING 2-212 D90 DI 21.82 X DE 28.88 ESP 3.53</t>
+  </si>
+  <si>
+    <t>SOL - 2659</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+  <si>
+    <t>HIDROIL SRL</t>
+  </si>
+  <si>
+    <t>Deposito</t>
+  </si>
+  <si>
+    <t>HTX-06P</t>
+  </si>
+  <si>
+    <t>ADAP RECTO DOBLE MF JIC 9/16" UNF</t>
+  </si>
+  <si>
+    <t>SOL - 2661</t>
+  </si>
+  <si>
+    <t>MOTORES HCOS Y TOMAS</t>
+  </si>
+  <si>
+    <t>MOTORES HIDRÁULICOS Y TOMAS DE FUERZA - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2663</t>
+  </si>
+  <si>
+    <t>01121</t>
+  </si>
+  <si>
+    <t>XHX6-20-24N</t>
+  </si>
+  <si>
+    <t>ADAP RECTO HG JIC 1.5/8" x MF JIC 1.7/8" UNF</t>
+  </si>
+  <si>
+    <t>SOL - 2664</t>
+  </si>
+  <si>
+    <t>01122</t>
+  </si>
+  <si>
+    <t>F5OX-10-08P</t>
+  </si>
+  <si>
+    <t>ADAP MF 7/8" AS JIC 37° X MF 3/4" AS ORING</t>
+  </si>
+  <si>
+    <t>XHX6-12-10N</t>
+  </si>
+  <si>
+    <t>ADAP RECTO HG JIC 1.1/16" x MF JIC 7/8" UNF</t>
+  </si>
+  <si>
+    <t>TAPA-1/2" S3000</t>
+  </si>
+  <si>
+    <t>TAPA HEMBRA 1/2" NPT SERIE 3000</t>
   </si>
 </sst>
 </file>
@@ -564,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -693,7 +768,7 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
@@ -702,7 +777,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
@@ -861,7 +936,7 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
@@ -870,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
         <v>22</v>
@@ -1085,7 +1160,7 @@
         <v>44</v>
       </c>
       <c r="E10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -1094,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I10" t="s">
         <v>22</v>
@@ -1141,7 +1216,7 @@
         <v>44</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -1150,7 +1225,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I11" t="s">
         <v>22</v>
@@ -1197,7 +1272,7 @@
         <v>44</v>
       </c>
       <c r="E12">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1206,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
@@ -1253,7 +1328,7 @@
         <v>44</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1262,7 +1337,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
@@ -1309,7 +1384,7 @@
         <v>44</v>
       </c>
       <c r="E14">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1318,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
@@ -1365,7 +1440,7 @@
         <v>44</v>
       </c>
       <c r="E15">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1374,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
@@ -1409,19 +1484,19 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
         <v>21</v>
       </c>
       <c r="E16">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
@@ -1430,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
@@ -1465,19 +1540,19 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" t="s">
         <v>59</v>
       </c>
-      <c r="C17" t="s">
-        <v>57</v>
-      </c>
       <c r="D17" t="s">
         <v>21</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F17" t="s">
         <v>21</v>
@@ -1486,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
@@ -1521,19 +1596,19 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
         <v>21</v>
       </c>
       <c r="E18">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
         <v>21</v>
@@ -1542,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I18" t="s">
         <v>22</v>
@@ -1572,6 +1647,454 @@
         <v>21</v>
       </c>
       <c r="R18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19">
+        <v>40</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>40</v>
+      </c>
+      <c r="I19" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" t="s">
+        <v>45</v>
+      </c>
+      <c r="K19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" t="s">
+        <v>25</v>
+      </c>
+      <c r="M19" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" t="s">
+        <v>21</v>
+      </c>
+      <c r="O19" t="s">
+        <v>21</v>
+      </c>
+      <c r="P19" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>21</v>
+      </c>
+      <c r="R19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20">
+        <v>100</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>100</v>
+      </c>
+      <c r="I20" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" t="s">
+        <v>67</v>
+      </c>
+      <c r="K20" t="s">
+        <v>68</v>
+      </c>
+      <c r="L20" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20" t="s">
+        <v>69</v>
+      </c>
+      <c r="N20" t="s">
+        <v>21</v>
+      </c>
+      <c r="O20" t="s">
+        <v>21</v>
+      </c>
+      <c r="P20" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>21</v>
+      </c>
+      <c r="R20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21">
+        <v>100</v>
+      </c>
+      <c r="F21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>100</v>
+      </c>
+      <c r="I21" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" t="s">
+        <v>67</v>
+      </c>
+      <c r="K21" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" t="s">
+        <v>25</v>
+      </c>
+      <c r="M21" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" t="s">
+        <v>21</v>
+      </c>
+      <c r="O21" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>21</v>
+      </c>
+      <c r="R21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="F22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>4</v>
+      </c>
+      <c r="I22" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" t="s">
+        <v>67</v>
+      </c>
+      <c r="K22" t="s">
+        <v>33</v>
+      </c>
+      <c r="L22" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" t="s">
+        <v>34</v>
+      </c>
+      <c r="N22" t="s">
+        <v>21</v>
+      </c>
+      <c r="O22" t="s">
+        <v>21</v>
+      </c>
+      <c r="P22" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>21</v>
+      </c>
+      <c r="R22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23">
+        <v>30</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>30</v>
+      </c>
+      <c r="I23" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" t="s">
+        <v>67</v>
+      </c>
+      <c r="K23" t="s">
+        <v>33</v>
+      </c>
+      <c r="L23" t="s">
+        <v>25</v>
+      </c>
+      <c r="M23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N23" t="s">
+        <v>21</v>
+      </c>
+      <c r="O23" t="s">
+        <v>21</v>
+      </c>
+      <c r="P23" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>21</v>
+      </c>
+      <c r="R23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24">
+        <v>30</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>30</v>
+      </c>
+      <c r="I24" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" t="s">
+        <v>67</v>
+      </c>
+      <c r="K24" t="s">
+        <v>33</v>
+      </c>
+      <c r="L24" t="s">
+        <v>25</v>
+      </c>
+      <c r="M24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O24" t="s">
+        <v>21</v>
+      </c>
+      <c r="P24" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>21</v>
+      </c>
+      <c r="R24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25">
+        <v>50</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>50</v>
+      </c>
+      <c r="I25" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" t="s">
+        <v>67</v>
+      </c>
+      <c r="K25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L25" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25" t="s">
+        <v>46</v>
+      </c>
+      <c r="N25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O25" t="s">
+        <v>21</v>
+      </c>
+      <c r="P25" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26">
+        <v>30</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>30</v>
+      </c>
+      <c r="I26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" t="s">
+        <v>67</v>
+      </c>
+      <c r="K26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M26" t="s">
+        <v>46</v>
+      </c>
+      <c r="N26" t="s">
+        <v>21</v>
+      </c>
+      <c r="O26" t="s">
+        <v>21</v>
+      </c>
+      <c r="P26" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>21</v>
+      </c>
+      <c r="R26" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{430E501A-83F0-4EE9-82F7-4E3BE36CAA1E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{69393761-0A1F-4E07-84ED-35447ED1A98F}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="72">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -134,16 +134,52 @@
     <t>Deposito NQN</t>
   </si>
   <si>
-    <t>MA-310</t>
-  </si>
-  <si>
-    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
-  </si>
-  <si>
-    <t>SOL - 2493</t>
-  </si>
-  <si>
-    <t>2026-08</t>
+    <t>SA-WLA632-3306F</t>
+  </si>
+  <si>
+    <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
+  </si>
+  <si>
+    <t>SOL - 2537</t>
+  </si>
+  <si>
+    <t>01049</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>Deposito Nqn 2</t>
+  </si>
+  <si>
+    <t>313-1135-194</t>
+  </si>
+  <si>
+    <t>EJE POSTIZO P50 Z14</t>
+  </si>
+  <si>
+    <t>313-2825-000</t>
+  </si>
+  <si>
+    <t>ENGRANAJE P50 DE 2 1/2"</t>
+  </si>
+  <si>
+    <t>313-5037-202</t>
+  </si>
+  <si>
+    <t>TROMPA P50 DE 5" X 4</t>
+  </si>
+  <si>
+    <t>313-8225-100</t>
+  </si>
+  <si>
+    <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
+  </si>
+  <si>
+    <t>391-2884-021P</t>
+  </si>
+  <si>
+    <t>SELLO GOMA SQUARE GASKET 50-25</t>
   </si>
   <si>
     <t>FILT-D-AB-2</t>
@@ -152,52 +188,7 @@
     <t>FILTRO AIRE RESP DESECANTE</t>
   </si>
   <si>
-    <t>313-1135-194</t>
-  </si>
-  <si>
-    <t>EJE POSTIZO P50 Z14</t>
-  </si>
-  <si>
-    <t>SOL - 2537</t>
-  </si>
-  <si>
-    <t>01049</t>
-  </si>
-  <si>
-    <t>2026-09</t>
-  </si>
-  <si>
-    <t>Deposito Nqn 2</t>
-  </si>
-  <si>
-    <t>313-2825-000</t>
-  </si>
-  <si>
-    <t>ENGRANAJE P50 DE 2 1/2"</t>
-  </si>
-  <si>
-    <t>313-5037-202</t>
-  </si>
-  <si>
-    <t>TROMPA P50 DE 5" X 4</t>
-  </si>
-  <si>
-    <t>313-8225-100</t>
-  </si>
-  <si>
-    <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
-  </si>
-  <si>
-    <t>391-2884-021P</t>
-  </si>
-  <si>
-    <t>SELLO GOMA SQUARE GASKET 50-25</t>
-  </si>
-  <si>
-    <t>SA-WLA632-3306F</t>
-  </si>
-  <si>
-    <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
+    <t>SOL - 2564</t>
   </si>
   <si>
     <t>FILT-10MZ10</t>
@@ -206,9 +197,6 @@
     <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 10"</t>
   </si>
   <si>
-    <t>SOL - 2564</t>
-  </si>
-  <si>
     <t>FILT-MZ10</t>
   </si>
   <si>
@@ -221,67 +209,34 @@
     <t>ELEMENTO FILTRO HIDRAULICO 3MIC SPIN-ON LARGO 7"</t>
   </si>
   <si>
-    <t>2-212-N90</t>
-  </si>
-  <si>
-    <t>ORING 2-212 D90 DI 21.82 X DE 28.88 ESP 3.53</t>
-  </si>
-  <si>
-    <t>SOL - 2659</t>
+    <t>F6X-06P</t>
+  </si>
+  <si>
+    <t>ADAP RECTO HG JIC 9/16" UNF x MF 1/4" NPT</t>
+  </si>
+  <si>
+    <t>SOL - 2661</t>
   </si>
   <si>
     <t>2026-10</t>
   </si>
   <si>
-    <t>HIDROIL SRL</t>
-  </si>
-  <si>
-    <t>Deposito</t>
-  </si>
-  <si>
     <t>HTX-06P</t>
   </si>
   <si>
     <t>ADAP RECTO DOBLE MF JIC 9/16" UNF</t>
   </si>
   <si>
-    <t>SOL - 2661</t>
-  </si>
-  <si>
-    <t>MOTORES HCOS Y TOMAS</t>
-  </si>
-  <si>
-    <t>MOTORES HIDRÁULICOS Y TOMAS DE FUERZA - GENERICO</t>
-  </si>
-  <si>
-    <t>SOL - 2663</t>
-  </si>
-  <si>
-    <t>01121</t>
-  </si>
-  <si>
-    <t>XHX6-20-24N</t>
-  </si>
-  <si>
-    <t>ADAP RECTO HG JIC 1.5/8" x MF JIC 1.7/8" UNF</t>
+    <t>F5OX-10-08P</t>
+  </si>
+  <si>
+    <t>ADAP MF 7/8" AS JIC 37° X MF 3/4" AS ORING</t>
   </si>
   <si>
     <t>SOL - 2664</t>
   </si>
   <si>
     <t>01122</t>
-  </si>
-  <si>
-    <t>F5OX-10-08P</t>
-  </si>
-  <si>
-    <t>ADAP MF 7/8" AS JIC 37° X MF 3/4" AS ORING</t>
-  </si>
-  <si>
-    <t>XHX6-12-10N</t>
-  </si>
-  <si>
-    <t>ADAP RECTO HG JIC 1.1/16" x MF JIC 7/8" UNF</t>
   </si>
   <si>
     <t>TAPA-1/2" S3000</t>
@@ -639,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1045,10 +1000,10 @@
         <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -1057,22 +1012,22 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
       </c>
       <c r="J8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K8" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L8" t="s">
         <v>25</v>
       </c>
       <c r="M8" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="N8" t="s">
         <v>21</v>
@@ -1092,19 +1047,19 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
         <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -1113,22 +1068,22 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
       </c>
       <c r="J9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L9" t="s">
         <v>25</v>
       </c>
       <c r="M9" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="N9" t="s">
         <v>21</v>
@@ -1148,19 +1103,19 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -1169,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I10" t="s">
         <v>22</v>
       </c>
       <c r="J10" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K10" t="s">
         <v>33</v>
@@ -1184,7 +1139,7 @@
         <v>25</v>
       </c>
       <c r="M10" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="N10" t="s">
         <v>21</v>
@@ -1204,16 +1159,16 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>6</v>
@@ -1231,7 +1186,7 @@
         <v>22</v>
       </c>
       <c r="J11" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K11" t="s">
         <v>33</v>
@@ -1240,7 +1195,7 @@
         <v>25</v>
       </c>
       <c r="M11" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="N11" t="s">
         <v>21</v>
@@ -1260,19 +1215,19 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E12">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1281,13 +1236,13 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
       </c>
       <c r="J12" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K12" t="s">
         <v>33</v>
@@ -1296,7 +1251,7 @@
         <v>25</v>
       </c>
       <c r="M12" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="N12" t="s">
         <v>21</v>
@@ -1316,19 +1271,19 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E13">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1337,13 +1292,13 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
       </c>
       <c r="J13" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K13" t="s">
         <v>33</v>
@@ -1352,7 +1307,7 @@
         <v>25</v>
       </c>
       <c r="M13" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="N13" t="s">
         <v>21</v>
@@ -1372,19 +1327,19 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" t="s">
         <v>53</v>
       </c>
-      <c r="B14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" t="s">
-        <v>43</v>
-      </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1393,22 +1348,22 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
       </c>
       <c r="J14" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K14" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L14" t="s">
         <v>25</v>
       </c>
       <c r="M14" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N14" t="s">
         <v>21</v>
@@ -1428,19 +1383,19 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
         <v>55</v>
       </c>
-      <c r="B15" t="s">
-        <v>56</v>
-      </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1449,22 +1404,22 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
       </c>
       <c r="J15" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K15" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L15" t="s">
         <v>25</v>
       </c>
       <c r="M15" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N15" t="s">
         <v>21</v>
@@ -1484,19 +1439,19 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s">
         <v>57</v>
       </c>
-      <c r="B16" t="s">
-        <v>58</v>
-      </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
         <v>21</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
@@ -1505,13 +1460,13 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
       </c>
       <c r="J16" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K16" t="s">
         <v>24</v>
@@ -1540,19 +1495,19 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
         <v>21</v>
       </c>
       <c r="E17">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
         <v>21</v>
@@ -1561,13 +1516,13 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
       </c>
       <c r="J17" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K17" t="s">
         <v>24</v>
@@ -1596,34 +1551,34 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" t="s">
         <v>62</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18">
+        <v>100</v>
+      </c>
+      <c r="F18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>100</v>
+      </c>
+      <c r="I18" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" t="s">
         <v>63</v>
-      </c>
-      <c r="C18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>10</v>
-      </c>
-      <c r="I18" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" t="s">
-        <v>45</v>
       </c>
       <c r="K18" t="s">
         <v>24</v>
@@ -1652,19 +1607,19 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s">
         <v>21</v>
       </c>
       <c r="E19">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="F19" t="s">
         <v>21</v>
@@ -1673,13 +1628,13 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
       </c>
       <c r="J19" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="K19" t="s">
         <v>24</v>
@@ -1708,19 +1663,19 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E20">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -1729,22 +1684,22 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
       </c>
       <c r="J20" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="K20" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="L20" t="s">
         <v>25</v>
       </c>
       <c r="M20" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="N20" t="s">
         <v>21</v>
@@ -1770,13 +1725,13 @@
         <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="E21">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F21" t="s">
         <v>21</v>
@@ -1785,22 +1740,22 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
       </c>
       <c r="J21" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="K21" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L21" t="s">
         <v>25</v>
       </c>
       <c r="M21" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="N21" t="s">
         <v>21</v>
@@ -1815,286 +1770,6 @@
         <v>21</v>
       </c>
       <c r="R21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22">
-        <v>4</v>
-      </c>
-      <c r="F22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>4</v>
-      </c>
-      <c r="I22" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" t="s">
-        <v>67</v>
-      </c>
-      <c r="K22" t="s">
-        <v>33</v>
-      </c>
-      <c r="L22" t="s">
-        <v>25</v>
-      </c>
-      <c r="M22" t="s">
-        <v>34</v>
-      </c>
-      <c r="N22" t="s">
-        <v>21</v>
-      </c>
-      <c r="O22" t="s">
-        <v>21</v>
-      </c>
-      <c r="P22" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>21</v>
-      </c>
-      <c r="R22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>77</v>
-      </c>
-      <c r="B23" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" t="s">
-        <v>80</v>
-      </c>
-      <c r="E23">
-        <v>30</v>
-      </c>
-      <c r="F23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>30</v>
-      </c>
-      <c r="I23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J23" t="s">
-        <v>67</v>
-      </c>
-      <c r="K23" t="s">
-        <v>33</v>
-      </c>
-      <c r="L23" t="s">
-        <v>25</v>
-      </c>
-      <c r="M23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N23" t="s">
-        <v>21</v>
-      </c>
-      <c r="O23" t="s">
-        <v>21</v>
-      </c>
-      <c r="P23" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>21</v>
-      </c>
-      <c r="R23" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>81</v>
-      </c>
-      <c r="B24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24" t="s">
-        <v>80</v>
-      </c>
-      <c r="E24">
-        <v>30</v>
-      </c>
-      <c r="F24" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>30</v>
-      </c>
-      <c r="I24" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" t="s">
-        <v>67</v>
-      </c>
-      <c r="K24" t="s">
-        <v>33</v>
-      </c>
-      <c r="L24" t="s">
-        <v>25</v>
-      </c>
-      <c r="M24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O24" t="s">
-        <v>21</v>
-      </c>
-      <c r="P24" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>21</v>
-      </c>
-      <c r="R24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>83</v>
-      </c>
-      <c r="B25" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" t="s">
-        <v>80</v>
-      </c>
-      <c r="E25">
-        <v>50</v>
-      </c>
-      <c r="F25" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>50</v>
-      </c>
-      <c r="I25" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" t="s">
-        <v>67</v>
-      </c>
-      <c r="K25" t="s">
-        <v>33</v>
-      </c>
-      <c r="L25" t="s">
-        <v>25</v>
-      </c>
-      <c r="M25" t="s">
-        <v>46</v>
-      </c>
-      <c r="N25" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" t="s">
-        <v>21</v>
-      </c>
-      <c r="P25" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>21</v>
-      </c>
-      <c r="R25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" t="s">
-        <v>80</v>
-      </c>
-      <c r="E26">
-        <v>30</v>
-      </c>
-      <c r="F26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>30</v>
-      </c>
-      <c r="I26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" t="s">
-        <v>67</v>
-      </c>
-      <c r="K26" t="s">
-        <v>33</v>
-      </c>
-      <c r="L26" t="s">
-        <v>25</v>
-      </c>
-      <c r="M26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N26" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" t="s">
-        <v>21</v>
-      </c>
-      <c r="P26" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>21</v>
-      </c>
-      <c r="R26" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69393761-0A1F-4E07-84ED-35447ED1A98F}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{774AB161-0DFD-4396-84D3-AE85CA9FBC20}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="65">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -209,40 +209,19 @@
     <t>ELEMENTO FILTRO HIDRAULICO 3MIC SPIN-ON LARGO 7"</t>
   </si>
   <si>
-    <t>F6X-06P</t>
-  </si>
-  <si>
-    <t>ADAP RECTO HG JIC 9/16" UNF x MF 1/4" NPT</t>
-  </si>
-  <si>
-    <t>SOL - 2661</t>
+    <t>MOTORES HCOS Y TOMAS</t>
+  </si>
+  <si>
+    <t>MOTORES HIDRÁULICOS Y TOMAS DE FUERZA - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2675</t>
+  </si>
+  <si>
+    <t>01129</t>
   </si>
   <si>
     <t>2026-10</t>
-  </si>
-  <si>
-    <t>HTX-06P</t>
-  </si>
-  <si>
-    <t>ADAP RECTO DOBLE MF JIC 9/16" UNF</t>
-  </si>
-  <si>
-    <t>F5OX-10-08P</t>
-  </si>
-  <si>
-    <t>ADAP MF 7/8" AS JIC 37° X MF 3/4" AS ORING</t>
-  </si>
-  <si>
-    <t>SOL - 2664</t>
-  </si>
-  <si>
-    <t>01122</t>
-  </si>
-  <si>
-    <t>TAPA-1/2" S3000</t>
-  </si>
-  <si>
-    <t>TAPA HEMBRA 1/2" NPT SERIE 3000</t>
   </si>
 </sst>
 </file>
@@ -594,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1560,10 +1539,10 @@
         <v>62</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="E18">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F18" t="s">
         <v>21</v>
@@ -1572,22 +1551,22 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I18" t="s">
         <v>22</v>
       </c>
       <c r="J18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K18" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L18" t="s">
         <v>25</v>
       </c>
       <c r="M18" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="N18" t="s">
         <v>21</v>
@@ -1602,174 +1581,6 @@
         <v>21</v>
       </c>
       <c r="R18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" t="s">
-        <v>62</v>
-      </c>
-      <c r="D19" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19">
-        <v>100</v>
-      </c>
-      <c r="F19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>100</v>
-      </c>
-      <c r="I19" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" t="s">
-        <v>63</v>
-      </c>
-      <c r="K19" t="s">
-        <v>24</v>
-      </c>
-      <c r="L19" t="s">
-        <v>25</v>
-      </c>
-      <c r="M19" t="s">
-        <v>26</v>
-      </c>
-      <c r="N19" t="s">
-        <v>21</v>
-      </c>
-      <c r="O19" t="s">
-        <v>21</v>
-      </c>
-      <c r="P19" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>21</v>
-      </c>
-      <c r="R19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>66</v>
-      </c>
-      <c r="B20" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20">
-        <v>30</v>
-      </c>
-      <c r="F20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>30</v>
-      </c>
-      <c r="I20" t="s">
-        <v>22</v>
-      </c>
-      <c r="J20" t="s">
-        <v>63</v>
-      </c>
-      <c r="K20" t="s">
-        <v>33</v>
-      </c>
-      <c r="L20" t="s">
-        <v>25</v>
-      </c>
-      <c r="M20" t="s">
-        <v>40</v>
-      </c>
-      <c r="N20" t="s">
-        <v>21</v>
-      </c>
-      <c r="O20" t="s">
-        <v>21</v>
-      </c>
-      <c r="P20" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>21</v>
-      </c>
-      <c r="R20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21">
-        <v>30</v>
-      </c>
-      <c r="F21" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>30</v>
-      </c>
-      <c r="I21" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" t="s">
-        <v>63</v>
-      </c>
-      <c r="K21" t="s">
-        <v>33</v>
-      </c>
-      <c r="L21" t="s">
-        <v>25</v>
-      </c>
-      <c r="M21" t="s">
-        <v>40</v>
-      </c>
-      <c r="N21" t="s">
-        <v>21</v>
-      </c>
-      <c r="O21" t="s">
-        <v>21</v>
-      </c>
-      <c r="P21" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>21</v>
-      </c>
-      <c r="R21" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{774AB161-0DFD-4396-84D3-AE85CA9FBC20}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{70B05614-CF3F-4B60-B0E5-6EB8932302DC}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="60">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -182,46 +182,31 @@
     <t>SELLO GOMA SQUARE GASKET 50-25</t>
   </si>
   <si>
-    <t>FILT-D-AB-2</t>
-  </si>
-  <si>
-    <t>FILTRO AIRE RESP DESECANTE</t>
-  </si>
-  <si>
-    <t>SOL - 2564</t>
-  </si>
-  <si>
-    <t>FILT-10MZ10</t>
-  </si>
-  <si>
-    <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 10"</t>
-  </si>
-  <si>
-    <t>FILT-MZ10</t>
-  </si>
-  <si>
-    <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 7"</t>
-  </si>
-  <si>
-    <t>FILT-MZ3</t>
-  </si>
-  <si>
-    <t>ELEMENTO FILTRO HIDRAULICO 3MIC SPIN-ON LARGO 7"</t>
-  </si>
-  <si>
-    <t>MOTORES HCOS Y TOMAS</t>
-  </si>
-  <si>
-    <t>MOTORES HIDRÁULICOS Y TOMAS DE FUERZA - GENERICO</t>
-  </si>
-  <si>
-    <t>SOL - 2675</t>
-  </si>
-  <si>
-    <t>01129</t>
+    <t>VALVULA HIDRAULICA</t>
+  </si>
+  <si>
+    <t>VALVULA HIDRAULICA - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2679</t>
+  </si>
+  <si>
+    <t>01131</t>
   </si>
   <si>
     <t>2026-10</t>
+  </si>
+  <si>
+    <t>MEDICION Y CONTROL</t>
+  </si>
+  <si>
+    <t>MEDICION Y CONTROL - INSTRUMENTOS Y ELEMENTOS AUXILIARES - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2680</t>
+  </si>
+  <si>
+    <t>01132</t>
   </si>
 </sst>
 </file>
@@ -573,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -646,7 +631,7 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
@@ -655,7 +640,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
         <v>22</v>
@@ -702,7 +687,7 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
@@ -711,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
@@ -814,7 +799,7 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
@@ -823,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I5" t="s">
         <v>22</v>
@@ -870,7 +855,7 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
@@ -879,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I6" t="s">
         <v>22</v>
@@ -1315,10 +1300,10 @@
         <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="E14">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1327,22 +1312,22 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
       </c>
       <c r="J14" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="K14" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L14" t="s">
         <v>25</v>
       </c>
       <c r="M14" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="N14" t="s">
         <v>21</v>
@@ -1362,19 +1347,19 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
         <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="E15">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1383,22 +1368,22 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
       </c>
       <c r="J15" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="K15" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L15" t="s">
         <v>25</v>
       </c>
       <c r="M15" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="N15" t="s">
         <v>21</v>
@@ -1418,19 +1403,19 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
         <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="E16">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
@@ -1439,22 +1424,22 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
       </c>
       <c r="J16" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="K16" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L16" t="s">
         <v>25</v>
       </c>
       <c r="M16" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="N16" t="s">
         <v>21</v>
@@ -1474,19 +1459,19 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
         <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F17" t="s">
         <v>21</v>
@@ -1495,22 +1480,22 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
       </c>
       <c r="J17" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="K17" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L17" t="s">
         <v>25</v>
       </c>
       <c r="M17" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="N17" t="s">
         <v>21</v>
@@ -1530,16 +1515,16 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1557,7 +1542,7 @@
         <v>22</v>
       </c>
       <c r="J18" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="K18" t="s">
         <v>33</v>
@@ -1581,6 +1566,1630 @@
         <v>21</v>
       </c>
       <c r="R18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" t="s">
+        <v>55</v>
+      </c>
+      <c r="K19" t="s">
+        <v>33</v>
+      </c>
+      <c r="L19" t="s">
+        <v>25</v>
+      </c>
+      <c r="M19" t="s">
+        <v>34</v>
+      </c>
+      <c r="N19" t="s">
+        <v>21</v>
+      </c>
+      <c r="O19" t="s">
+        <v>21</v>
+      </c>
+      <c r="P19" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>21</v>
+      </c>
+      <c r="R19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" t="s">
+        <v>55</v>
+      </c>
+      <c r="K20" t="s">
+        <v>33</v>
+      </c>
+      <c r="L20" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20" t="s">
+        <v>34</v>
+      </c>
+      <c r="N20" t="s">
+        <v>21</v>
+      </c>
+      <c r="O20" t="s">
+        <v>21</v>
+      </c>
+      <c r="P20" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>21</v>
+      </c>
+      <c r="R20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" t="s">
+        <v>55</v>
+      </c>
+      <c r="K21" t="s">
+        <v>33</v>
+      </c>
+      <c r="L21" t="s">
+        <v>25</v>
+      </c>
+      <c r="M21" t="s">
+        <v>34</v>
+      </c>
+      <c r="N21" t="s">
+        <v>21</v>
+      </c>
+      <c r="O21" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>21</v>
+      </c>
+      <c r="R21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" t="s">
+        <v>55</v>
+      </c>
+      <c r="K22" t="s">
+        <v>33</v>
+      </c>
+      <c r="L22" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" t="s">
+        <v>34</v>
+      </c>
+      <c r="N22" t="s">
+        <v>21</v>
+      </c>
+      <c r="O22" t="s">
+        <v>21</v>
+      </c>
+      <c r="P22" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>21</v>
+      </c>
+      <c r="R22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" t="s">
+        <v>55</v>
+      </c>
+      <c r="K23" t="s">
+        <v>33</v>
+      </c>
+      <c r="L23" t="s">
+        <v>25</v>
+      </c>
+      <c r="M23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N23" t="s">
+        <v>21</v>
+      </c>
+      <c r="O23" t="s">
+        <v>21</v>
+      </c>
+      <c r="P23" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>21</v>
+      </c>
+      <c r="R23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" t="s">
+        <v>54</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" t="s">
+        <v>55</v>
+      </c>
+      <c r="K24" t="s">
+        <v>33</v>
+      </c>
+      <c r="L24" t="s">
+        <v>25</v>
+      </c>
+      <c r="M24" t="s">
+        <v>34</v>
+      </c>
+      <c r="N24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O24" t="s">
+        <v>21</v>
+      </c>
+      <c r="P24" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>21</v>
+      </c>
+      <c r="R24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" t="s">
+        <v>55</v>
+      </c>
+      <c r="K25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L25" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25" t="s">
+        <v>34</v>
+      </c>
+      <c r="N25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O25" t="s">
+        <v>21</v>
+      </c>
+      <c r="P25" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" t="s">
+        <v>54</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" t="s">
+        <v>55</v>
+      </c>
+      <c r="K26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M26" t="s">
+        <v>34</v>
+      </c>
+      <c r="N26" t="s">
+        <v>21</v>
+      </c>
+      <c r="O26" t="s">
+        <v>21</v>
+      </c>
+      <c r="P26" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>21</v>
+      </c>
+      <c r="R26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" t="s">
+        <v>54</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" t="s">
+        <v>55</v>
+      </c>
+      <c r="K27" t="s">
+        <v>33</v>
+      </c>
+      <c r="L27" t="s">
+        <v>25</v>
+      </c>
+      <c r="M27" t="s">
+        <v>34</v>
+      </c>
+      <c r="N27" t="s">
+        <v>21</v>
+      </c>
+      <c r="O27" t="s">
+        <v>21</v>
+      </c>
+      <c r="P27" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>21</v>
+      </c>
+      <c r="R27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" t="s">
+        <v>55</v>
+      </c>
+      <c r="K28" t="s">
+        <v>33</v>
+      </c>
+      <c r="L28" t="s">
+        <v>25</v>
+      </c>
+      <c r="M28" t="s">
+        <v>34</v>
+      </c>
+      <c r="N28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O28" t="s">
+        <v>21</v>
+      </c>
+      <c r="P28" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>21</v>
+      </c>
+      <c r="R28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" t="s">
+        <v>53</v>
+      </c>
+      <c r="D29" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" t="s">
+        <v>55</v>
+      </c>
+      <c r="K29" t="s">
+        <v>33</v>
+      </c>
+      <c r="L29" t="s">
+        <v>25</v>
+      </c>
+      <c r="M29" t="s">
+        <v>34</v>
+      </c>
+      <c r="N29" t="s">
+        <v>21</v>
+      </c>
+      <c r="O29" t="s">
+        <v>21</v>
+      </c>
+      <c r="P29" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>21</v>
+      </c>
+      <c r="R29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" t="s">
+        <v>54</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" t="s">
+        <v>55</v>
+      </c>
+      <c r="K30" t="s">
+        <v>33</v>
+      </c>
+      <c r="L30" t="s">
+        <v>25</v>
+      </c>
+      <c r="M30" t="s">
+        <v>34</v>
+      </c>
+      <c r="N30" t="s">
+        <v>21</v>
+      </c>
+      <c r="O30" t="s">
+        <v>21</v>
+      </c>
+      <c r="P30" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>21</v>
+      </c>
+      <c r="R30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" t="s">
+        <v>54</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31" t="s">
+        <v>22</v>
+      </c>
+      <c r="J31" t="s">
+        <v>55</v>
+      </c>
+      <c r="K31" t="s">
+        <v>33</v>
+      </c>
+      <c r="L31" t="s">
+        <v>25</v>
+      </c>
+      <c r="M31" t="s">
+        <v>34</v>
+      </c>
+      <c r="N31" t="s">
+        <v>21</v>
+      </c>
+      <c r="O31" t="s">
+        <v>21</v>
+      </c>
+      <c r="P31" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>21</v>
+      </c>
+      <c r="R31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D32" t="s">
+        <v>54</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" t="s">
+        <v>55</v>
+      </c>
+      <c r="K32" t="s">
+        <v>33</v>
+      </c>
+      <c r="L32" t="s">
+        <v>25</v>
+      </c>
+      <c r="M32" t="s">
+        <v>34</v>
+      </c>
+      <c r="N32" t="s">
+        <v>21</v>
+      </c>
+      <c r="O32" t="s">
+        <v>21</v>
+      </c>
+      <c r="P32" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>21</v>
+      </c>
+      <c r="R32" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" t="s">
+        <v>55</v>
+      </c>
+      <c r="K33" t="s">
+        <v>33</v>
+      </c>
+      <c r="L33" t="s">
+        <v>25</v>
+      </c>
+      <c r="M33" t="s">
+        <v>34</v>
+      </c>
+      <c r="N33" t="s">
+        <v>21</v>
+      </c>
+      <c r="O33" t="s">
+        <v>21</v>
+      </c>
+      <c r="P33" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>21</v>
+      </c>
+      <c r="R33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" t="s">
+        <v>54</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34" t="s">
+        <v>22</v>
+      </c>
+      <c r="J34" t="s">
+        <v>55</v>
+      </c>
+      <c r="K34" t="s">
+        <v>33</v>
+      </c>
+      <c r="L34" t="s">
+        <v>25</v>
+      </c>
+      <c r="M34" t="s">
+        <v>34</v>
+      </c>
+      <c r="N34" t="s">
+        <v>21</v>
+      </c>
+      <c r="O34" t="s">
+        <v>21</v>
+      </c>
+      <c r="P34" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>21</v>
+      </c>
+      <c r="R34" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35" t="s">
+        <v>22</v>
+      </c>
+      <c r="J35" t="s">
+        <v>55</v>
+      </c>
+      <c r="K35" t="s">
+        <v>33</v>
+      </c>
+      <c r="L35" t="s">
+        <v>25</v>
+      </c>
+      <c r="M35" t="s">
+        <v>34</v>
+      </c>
+      <c r="N35" t="s">
+        <v>21</v>
+      </c>
+      <c r="O35" t="s">
+        <v>21</v>
+      </c>
+      <c r="P35" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>21</v>
+      </c>
+      <c r="R35" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36" t="s">
+        <v>22</v>
+      </c>
+      <c r="J36" t="s">
+        <v>55</v>
+      </c>
+      <c r="K36" t="s">
+        <v>33</v>
+      </c>
+      <c r="L36" t="s">
+        <v>25</v>
+      </c>
+      <c r="M36" t="s">
+        <v>34</v>
+      </c>
+      <c r="N36" t="s">
+        <v>21</v>
+      </c>
+      <c r="O36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P36" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>21</v>
+      </c>
+      <c r="R36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" t="s">
+        <v>53</v>
+      </c>
+      <c r="D37" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37" t="s">
+        <v>22</v>
+      </c>
+      <c r="J37" t="s">
+        <v>55</v>
+      </c>
+      <c r="K37" t="s">
+        <v>33</v>
+      </c>
+      <c r="L37" t="s">
+        <v>25</v>
+      </c>
+      <c r="M37" t="s">
+        <v>34</v>
+      </c>
+      <c r="N37" t="s">
+        <v>21</v>
+      </c>
+      <c r="O37" t="s">
+        <v>21</v>
+      </c>
+      <c r="P37" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R37" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>22</v>
+      </c>
+      <c r="J38" t="s">
+        <v>55</v>
+      </c>
+      <c r="K38" t="s">
+        <v>33</v>
+      </c>
+      <c r="L38" t="s">
+        <v>25</v>
+      </c>
+      <c r="M38" t="s">
+        <v>34</v>
+      </c>
+      <c r="N38" t="s">
+        <v>21</v>
+      </c>
+      <c r="O38" t="s">
+        <v>21</v>
+      </c>
+      <c r="P38" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>21</v>
+      </c>
+      <c r="R38" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" t="s">
+        <v>53</v>
+      </c>
+      <c r="D39" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39" t="s">
+        <v>22</v>
+      </c>
+      <c r="J39" t="s">
+        <v>55</v>
+      </c>
+      <c r="K39" t="s">
+        <v>33</v>
+      </c>
+      <c r="L39" t="s">
+        <v>25</v>
+      </c>
+      <c r="M39" t="s">
+        <v>34</v>
+      </c>
+      <c r="N39" t="s">
+        <v>21</v>
+      </c>
+      <c r="O39" t="s">
+        <v>21</v>
+      </c>
+      <c r="P39" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>21</v>
+      </c>
+      <c r="R39" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" t="s">
+        <v>54</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40" t="s">
+        <v>22</v>
+      </c>
+      <c r="J40" t="s">
+        <v>55</v>
+      </c>
+      <c r="K40" t="s">
+        <v>33</v>
+      </c>
+      <c r="L40" t="s">
+        <v>25</v>
+      </c>
+      <c r="M40" t="s">
+        <v>34</v>
+      </c>
+      <c r="N40" t="s">
+        <v>21</v>
+      </c>
+      <c r="O40" t="s">
+        <v>21</v>
+      </c>
+      <c r="P40" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>21</v>
+      </c>
+      <c r="R40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" t="s">
+        <v>54</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41" t="s">
+        <v>22</v>
+      </c>
+      <c r="J41" t="s">
+        <v>55</v>
+      </c>
+      <c r="K41" t="s">
+        <v>33</v>
+      </c>
+      <c r="L41" t="s">
+        <v>25</v>
+      </c>
+      <c r="M41" t="s">
+        <v>34</v>
+      </c>
+      <c r="N41" t="s">
+        <v>21</v>
+      </c>
+      <c r="O41" t="s">
+        <v>21</v>
+      </c>
+      <c r="P41" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>21</v>
+      </c>
+      <c r="R41" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" t="s">
+        <v>52</v>
+      </c>
+      <c r="C42" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" t="s">
+        <v>54</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42" t="s">
+        <v>22</v>
+      </c>
+      <c r="J42" t="s">
+        <v>55</v>
+      </c>
+      <c r="K42" t="s">
+        <v>33</v>
+      </c>
+      <c r="L42" t="s">
+        <v>25</v>
+      </c>
+      <c r="M42" t="s">
+        <v>34</v>
+      </c>
+      <c r="N42" t="s">
+        <v>21</v>
+      </c>
+      <c r="O42" t="s">
+        <v>21</v>
+      </c>
+      <c r="P42" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>21</v>
+      </c>
+      <c r="R42" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43" t="s">
+        <v>22</v>
+      </c>
+      <c r="J43" t="s">
+        <v>55</v>
+      </c>
+      <c r="K43" t="s">
+        <v>33</v>
+      </c>
+      <c r="L43" t="s">
+        <v>25</v>
+      </c>
+      <c r="M43" t="s">
+        <v>34</v>
+      </c>
+      <c r="N43" t="s">
+        <v>21</v>
+      </c>
+      <c r="O43" t="s">
+        <v>21</v>
+      </c>
+      <c r="P43" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>21</v>
+      </c>
+      <c r="R43" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D44" t="s">
+        <v>54</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44" t="s">
+        <v>22</v>
+      </c>
+      <c r="J44" t="s">
+        <v>55</v>
+      </c>
+      <c r="K44" t="s">
+        <v>33</v>
+      </c>
+      <c r="L44" t="s">
+        <v>25</v>
+      </c>
+      <c r="M44" t="s">
+        <v>34</v>
+      </c>
+      <c r="N44" t="s">
+        <v>21</v>
+      </c>
+      <c r="O44" t="s">
+        <v>21</v>
+      </c>
+      <c r="P44" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>21</v>
+      </c>
+      <c r="R44" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" t="s">
+        <v>54</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45" t="s">
+        <v>22</v>
+      </c>
+      <c r="J45" t="s">
+        <v>55</v>
+      </c>
+      <c r="K45" t="s">
+        <v>33</v>
+      </c>
+      <c r="L45" t="s">
+        <v>25</v>
+      </c>
+      <c r="M45" t="s">
+        <v>34</v>
+      </c>
+      <c r="N45" t="s">
+        <v>21</v>
+      </c>
+      <c r="O45" t="s">
+        <v>21</v>
+      </c>
+      <c r="P45" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>21</v>
+      </c>
+      <c r="R45" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" t="s">
+        <v>54</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" t="s">
+        <v>55</v>
+      </c>
+      <c r="K46" t="s">
+        <v>33</v>
+      </c>
+      <c r="L46" t="s">
+        <v>25</v>
+      </c>
+      <c r="M46" t="s">
+        <v>34</v>
+      </c>
+      <c r="N46" t="s">
+        <v>21</v>
+      </c>
+      <c r="O46" t="s">
+        <v>21</v>
+      </c>
+      <c r="P46" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>21</v>
+      </c>
+      <c r="R46" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" t="s">
+        <v>58</v>
+      </c>
+      <c r="D47" t="s">
+        <v>59</v>
+      </c>
+      <c r="E47">
+        <v>5</v>
+      </c>
+      <c r="F47" t="s">
+        <v>21</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>5</v>
+      </c>
+      <c r="I47" t="s">
+        <v>22</v>
+      </c>
+      <c r="J47" t="s">
+        <v>55</v>
+      </c>
+      <c r="K47" t="s">
+        <v>33</v>
+      </c>
+      <c r="L47" t="s">
+        <v>25</v>
+      </c>
+      <c r="M47" t="s">
+        <v>34</v>
+      </c>
+      <c r="N47" t="s">
+        <v>21</v>
+      </c>
+      <c r="O47" t="s">
+        <v>21</v>
+      </c>
+      <c r="P47" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>21</v>
+      </c>
+      <c r="R47" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AD2C158-3D19-4192-870C-7ECD43EC7C65}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7253F25-23D7-4174-B6DA-D1142AD61A24}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="61">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -175,10 +175,10 @@
     <t>SELLO GOMA SQUARE GASKET 50-25</t>
   </si>
   <si>
-    <t>6601-16-16P</t>
-  </si>
-  <si>
-    <t>ACOPLE RAPIDO HEMBRA C/ROSCA HEMBRA DE 1" NPT</t>
+    <t>6601-06-06P</t>
+  </si>
+  <si>
+    <t>ACOPLE RAPIDO HEMBRA C/ROSCA HEMBRA DE 3/8" NPT</t>
   </si>
   <si>
     <t>SOL - 2691</t>
@@ -190,10 +190,19 @@
     <t>2026-10</t>
   </si>
   <si>
-    <t>6602-16-16P</t>
-  </si>
-  <si>
-    <t>ACOPLE RAPIDO MACHO C/ROSCA HEMBRA DE 1" NPT</t>
+    <t>6602-06-06P</t>
+  </si>
+  <si>
+    <t>ACOPLE RAPIDO MACHO C/ROSCA HEMBRA DE 3/8" NPT</t>
+  </si>
+  <si>
+    <t>TERMINAL PARA PRENSAR</t>
+  </si>
+  <si>
+    <t>TERMINAL PARA PRENSAR - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2695</t>
   </si>
 </sst>
 </file>
@@ -545,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1388,6 +1397,62 @@
         <v>27</v>
       </c>
     </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" t="s">
+        <v>55</v>
+      </c>
+      <c r="K16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" t="s">
+        <v>26</v>
+      </c>
+      <c r="N16" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" t="s">
+        <v>21</v>
+      </c>
+      <c r="P16" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>21</v>
+      </c>
+      <c r="R16" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,19 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7253F25-23D7-4174-B6DA-D1142AD61A24}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F39D07CB-D4A3-4605-876D-9000510C7CC3}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="51">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -127,82 +134,52 @@
     <t>Deposito NQN</t>
   </si>
   <si>
+    <t>313-2825-000</t>
+  </si>
+  <si>
+    <t>ENGRANAJE P50 DE 2 1/2"</t>
+  </si>
+  <si>
+    <t>SOL - 2537</t>
+  </si>
+  <si>
+    <t>01049</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>Deposito Nqn 2</t>
+  </si>
+  <si>
+    <t>313-5037-202</t>
+  </si>
+  <si>
+    <t>TROMPA P50 DE 5" X 4</t>
+  </si>
+  <si>
+    <t>313-8225-100</t>
+  </si>
+  <si>
+    <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
+  </si>
+  <si>
+    <t>391-2884-021P</t>
+  </si>
+  <si>
+    <t>SELLO GOMA SQUARE GASKET 50-25</t>
+  </si>
+  <si>
+    <t>313-1135-194</t>
+  </si>
+  <si>
+    <t>EJE POSTIZO P50 Z14</t>
+  </si>
+  <si>
     <t>SA-WLA632-3306F</t>
   </si>
   <si>
     <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
-  </si>
-  <si>
-    <t>SOL - 2537</t>
-  </si>
-  <si>
-    <t>01049</t>
-  </si>
-  <si>
-    <t>2026-09</t>
-  </si>
-  <si>
-    <t>Deposito Nqn 2</t>
-  </si>
-  <si>
-    <t>313-1135-194</t>
-  </si>
-  <si>
-    <t>EJE POSTIZO P50 Z14</t>
-  </si>
-  <si>
-    <t>313-2825-000</t>
-  </si>
-  <si>
-    <t>ENGRANAJE P50 DE 2 1/2"</t>
-  </si>
-  <si>
-    <t>313-5037-202</t>
-  </si>
-  <si>
-    <t>TROMPA P50 DE 5" X 4</t>
-  </si>
-  <si>
-    <t>313-8225-100</t>
-  </si>
-  <si>
-    <t>CUERPO P50 PARA ENGRANAJE DE 2 1/2"</t>
-  </si>
-  <si>
-    <t>391-2884-021P</t>
-  </si>
-  <si>
-    <t>SELLO GOMA SQUARE GASKET 50-25</t>
-  </si>
-  <si>
-    <t>6601-06-06P</t>
-  </si>
-  <si>
-    <t>ACOPLE RAPIDO HEMBRA C/ROSCA HEMBRA DE 3/8" NPT</t>
-  </si>
-  <si>
-    <t>SOL - 2691</t>
-  </si>
-  <si>
-    <t>01139</t>
-  </si>
-  <si>
-    <t>2026-10</t>
-  </si>
-  <si>
-    <t>6602-06-06P</t>
-  </si>
-  <si>
-    <t>ACOPLE RAPIDO MACHO C/ROSCA HEMBRA DE 3/8" NPT</t>
-  </si>
-  <si>
-    <t>TERMINAL PARA PRENSAR</t>
-  </si>
-  <si>
-    <t>TERMINAL PARA PRENSAR - GENERICO</t>
-  </si>
-  <si>
-    <t>SOL - 2695</t>
   </si>
 </sst>
 </file>
@@ -554,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -683,7 +660,7 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
@@ -692,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
@@ -795,7 +772,7 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
@@ -804,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I5" t="s">
         <v>22</v>
@@ -963,7 +940,7 @@
         <v>38</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -972,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
@@ -1019,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -1028,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
@@ -1075,7 +1052,7 @@
         <v>38</v>
       </c>
       <c r="E10">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -1084,7 +1061,7 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I10" t="s">
         <v>22</v>
@@ -1131,7 +1108,7 @@
         <v>38</v>
       </c>
       <c r="E11">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -1140,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="I11" t="s">
         <v>22</v>
@@ -1187,7 +1164,7 @@
         <v>38</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1196,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
@@ -1243,7 +1220,7 @@
         <v>38</v>
       </c>
       <c r="E13">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1252,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
@@ -1282,174 +1259,6 @@
         <v>21</v>
       </c>
       <c r="R13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14">
-        <v>25</v>
-      </c>
-      <c r="F14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>25</v>
-      </c>
-      <c r="I14" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" t="s">
-        <v>55</v>
-      </c>
-      <c r="K14" t="s">
-        <v>33</v>
-      </c>
-      <c r="L14" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" t="s">
-        <v>40</v>
-      </c>
-      <c r="N14" t="s">
-        <v>21</v>
-      </c>
-      <c r="O14" t="s">
-        <v>21</v>
-      </c>
-      <c r="P14" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>21</v>
-      </c>
-      <c r="R14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15">
-        <v>25</v>
-      </c>
-      <c r="F15" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>25</v>
-      </c>
-      <c r="I15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" t="s">
-        <v>55</v>
-      </c>
-      <c r="K15" t="s">
-        <v>33</v>
-      </c>
-      <c r="L15" t="s">
-        <v>25</v>
-      </c>
-      <c r="M15" t="s">
-        <v>40</v>
-      </c>
-      <c r="N15" t="s">
-        <v>21</v>
-      </c>
-      <c r="O15" t="s">
-        <v>21</v>
-      </c>
-      <c r="P15" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>21</v>
-      </c>
-      <c r="R15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" t="s">
-        <v>55</v>
-      </c>
-      <c r="K16" t="s">
-        <v>24</v>
-      </c>
-      <c r="L16" t="s">
-        <v>25</v>
-      </c>
-      <c r="M16" t="s">
-        <v>26</v>
-      </c>
-      <c r="N16" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" t="s">
-        <v>21</v>
-      </c>
-      <c r="P16" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>21</v>
-      </c>
-      <c r="R16" t="s">
         <v>27</v>
       </c>
     </row>
